--- a/research/traditional_assets/database/data/ireland/ireland_computer_services.xlsx
+++ b/research/traditional_assets/database/data/ireland/ireland_computer_services.xlsx
@@ -650,10 +650,10 @@
         <v>0.2837746656270617</v>
       </c>
       <c r="X2">
-        <v>0.09835390250312426</v>
+        <v>0.09832935931252934</v>
       </c>
       <c r="Y2">
-        <v>0.1854207631239375</v>
+        <v>0.1854453063145324</v>
       </c>
       <c r="Z2">
         <v>10.52877053350388</v>
@@ -662,10 +662,10 @@
         <v>1.26781339537581</v>
       </c>
       <c r="AB2">
-        <v>0.09670449194500774</v>
+        <v>0.09668081081461077</v>
       </c>
       <c r="AC2">
-        <v>1.171108903430802</v>
+        <v>1.171132584561199</v>
       </c>
       <c r="AD2">
         <v>5153.8</v>
@@ -787,10 +787,10 @@
         <v>0.2837746656270617</v>
       </c>
       <c r="X3">
-        <v>0.09835390250312426</v>
+        <v>0.09832935931252934</v>
       </c>
       <c r="Y3">
-        <v>0.1854207631239375</v>
+        <v>0.1854453063145324</v>
       </c>
       <c r="Z3">
         <v>10.52877053350388</v>
@@ -799,10 +799,10 @@
         <v>1.26781339537581</v>
       </c>
       <c r="AB3">
-        <v>0.09670449194500774</v>
+        <v>0.09668081081461077</v>
       </c>
       <c r="AC3">
-        <v>1.171108903430802</v>
+        <v>1.171132584561199</v>
       </c>
       <c r="AD3">
         <v>5153.8</v>
@@ -1139,7 +1139,7 @@
         <v>147.034899328859</v>
       </c>
       <c r="F2">
-        <v>9.259983704069731</v>
+        <v>9.49050925761596</v>
       </c>
       <c r="G2">
         <v>0.662032023981992</v>
@@ -1157,13 +1157,13 @@
         <v>220037.6</v>
       </c>
       <c r="L2">
-        <v>208081.51427662</v>
+        <v>208560.670747299</v>
       </c>
       <c r="M2">
         <v>219741.491661361</v>
       </c>
       <c r="N2">
-        <v>220299.697526143</v>
+        <v>220778.853996822</v>
       </c>
       <c r="O2">
         <v>8009.99166136052</v>
@@ -1172,16 +1172,16 @@
         <v>20524.2832495224</v>
       </c>
       <c r="Q2">
-        <v>0.0967044919450077</v>
+        <v>0.0966808108146108</v>
       </c>
       <c r="R2">
-        <v>0.09657550771912569</v>
+        <v>0.0964417397451615</v>
       </c>
       <c r="S2">
         <v>0.0513945395797173</v>
       </c>
       <c r="T2">
-        <v>0.0504320395797173</v>
+        <v>0.0492070395797173</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="W2">
-        <v>0.0983539025031243</v>
+        <v>0.0983293593125293</v>
       </c>
       <c r="X2">
-        <v>0.101139147425221</v>
+        <v>0.101113303497788</v>
       </c>
       <c r="Y2">
         <v>1.02389498584627</v>
@@ -1236,7 +1236,7 @@
         <v>220037.6</v>
       </c>
       <c r="AK2">
-        <v>0.05132743418963755</v>
+        <v>0.05130346377183671</v>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
@@ -1424,13 +1424,13 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>0.0967316047099379</v>
+        <v>0.09670781914840654</v>
       </c>
       <c r="C2">
-        <v>227930.6151898209</v>
+        <v>227931.011307795</v>
       </c>
       <c r="D2">
-        <v>219624.5151898209</v>
+        <v>219624.911307795</v>
       </c>
       <c r="E2">
         <v>-8009.991661360522</v>
@@ -1475,19 +1475,19 @@
         <v>0</v>
       </c>
       <c r="S2">
-        <v>0.0967316047099379</v>
+        <v>0.09670781914840654</v>
       </c>
       <c r="T2">
         <v>0.9922881498763956</v>
       </c>
       <c r="U2">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V2">
         <v>0.125</v>
       </c>
       <c r="W2">
-        <v>0.05043203957971733</v>
+        <v>0.04920703957971734</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -1506,13 +1506,13 @@
         <v>0.01</v>
       </c>
       <c r="B3">
-        <v>0.09671426059984765</v>
+        <v>0.09667825477026819</v>
       </c>
       <c r="C3">
-        <v>225724.9550856161</v>
+        <v>225778.1552153249</v>
       </c>
       <c r="D3">
-        <v>219699.3310022297</v>
+        <v>219752.5311319384</v>
       </c>
       <c r="E3">
         <v>-5729.515744746916</v>
@@ -1539,37 +1539,37 @@
         <v>10954.1</v>
       </c>
       <c r="M3">
-        <v>131.4389162139994</v>
+        <v>128.2462499307404</v>
       </c>
       <c r="N3">
-        <v>10822.661083786</v>
+        <v>10825.85375006926</v>
       </c>
       <c r="O3">
-        <v>1352.83263547325</v>
+        <v>1353.231718758657</v>
       </c>
       <c r="P3">
-        <v>9469.82844831275</v>
+        <v>9472.622031310601</v>
       </c>
       <c r="Q3">
-        <v>10614.82844831275</v>
+        <v>10617.6220313106</v>
       </c>
       <c r="R3">
         <v>0.0101010101010101</v>
       </c>
       <c r="S3">
-        <v>0.09718175778186917</v>
+        <v>0.09715776199441517</v>
       </c>
       <c r="T3">
         <v>1.001058373423283</v>
       </c>
       <c r="U3">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V3">
         <v>0.125</v>
       </c>
       <c r="W3">
-        <v>0.05043203957971733</v>
+        <v>0.04920703957971734</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>83.33985333662761</v>
+        <v>85.41458331854363</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1588,13 +1588,13 @@
         <v>0.02</v>
       </c>
       <c r="B4">
-        <v>0.0966969164897574</v>
+        <v>0.09664869039212985</v>
       </c>
       <c r="C4">
-        <v>223519.3459712856</v>
+        <v>223625.4475239524</v>
       </c>
       <c r="D4">
-        <v>219774.1978045128</v>
+        <v>219880.2993571796</v>
       </c>
       <c r="E4">
         <v>-3449.039828133311</v>
@@ -1621,37 +1621,37 @@
         <v>10954.1</v>
       </c>
       <c r="M4">
-        <v>262.8778324279989</v>
+        <v>256.4924998614808</v>
       </c>
       <c r="N4">
-        <v>10691.222167572</v>
+        <v>10697.60750013852</v>
       </c>
       <c r="O4">
-        <v>1336.4027709465</v>
+        <v>1337.200937517315</v>
       </c>
       <c r="P4">
-        <v>9354.819396625498</v>
+        <v>9360.406562621203</v>
       </c>
       <c r="Q4">
-        <v>10499.8193966255</v>
+        <v>10505.4065626212</v>
       </c>
       <c r="R4">
         <v>0.02040816326530612</v>
       </c>
       <c r="S4">
-        <v>0.09764109765118678</v>
+        <v>0.09761688734748522</v>
       </c>
       <c r="T4">
         <v>1.010007581124188</v>
       </c>
       <c r="U4">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V4">
         <v>0.125</v>
       </c>
       <c r="W4">
-        <v>0.05043203957971733</v>
+        <v>0.04920703957971734</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>41.66992666831381</v>
+        <v>42.70729165927182</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1670,13 +1670,13 @@
         <v>0.03</v>
       </c>
       <c r="B5">
-        <v>0.09667957237966716</v>
+        <v>0.09661912601399153</v>
       </c>
       <c r="C5">
-        <v>221313.7878989744</v>
+        <v>221472.8884926779</v>
       </c>
       <c r="D5">
-        <v>219849.1156488152</v>
+        <v>220008.2162425187</v>
       </c>
       <c r="E5">
         <v>-1168.563911519706</v>
@@ -1703,37 +1703,37 @@
         <v>10954.1</v>
       </c>
       <c r="M5">
-        <v>394.3167486419983</v>
+        <v>384.7387497922212</v>
       </c>
       <c r="N5">
-        <v>10559.783251358</v>
+        <v>10569.36125020778</v>
       </c>
       <c r="O5">
-        <v>1319.97290641975</v>
+        <v>1321.170156275972</v>
       </c>
       <c r="P5">
-        <v>9239.810344938251</v>
+        <v>9248.191093931806</v>
       </c>
       <c r="Q5">
-        <v>10384.81034493825</v>
+        <v>10393.19109393181</v>
       </c>
       <c r="R5">
         <v>0.03092783505154639</v>
       </c>
       <c r="S5">
-        <v>0.09810990844564499</v>
+        <v>0.09808547920268042</v>
       </c>
       <c r="T5">
         <v>1.019141308571504</v>
       </c>
       <c r="U5">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V5">
         <v>0.125</v>
       </c>
       <c r="W5">
-        <v>0.05043203957971733</v>
+        <v>0.04920703957971734</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>27.7799511122092</v>
+        <v>28.47152777284789</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1752,13 +1752,13 @@
         <v>0.04</v>
       </c>
       <c r="B6">
-        <v>0.09666222826957689</v>
+        <v>0.09658956163585318</v>
       </c>
       <c r="C6">
-        <v>219108.2809208991</v>
+        <v>219320.4783811045</v>
       </c>
       <c r="D6">
-        <v>219924.0845873535</v>
+        <v>220136.282047559</v>
       </c>
       <c r="E6">
         <v>1111.9120050939</v>
@@ -1785,37 +1785,37 @@
         <v>10954.1</v>
       </c>
       <c r="M6">
-        <v>525.7556648559978</v>
+        <v>512.9849997229617</v>
       </c>
       <c r="N6">
-        <v>10428.344335144</v>
+        <v>10441.11500027704</v>
       </c>
       <c r="O6">
-        <v>1303.543041893</v>
+        <v>1305.13937503463</v>
       </c>
       <c r="P6">
-        <v>9124.801293250999</v>
+        <v>9135.975625242409</v>
       </c>
       <c r="Q6">
-        <v>10269.801293251</v>
+        <v>10280.97562524241</v>
       </c>
       <c r="R6">
         <v>0.04166666666666667</v>
       </c>
       <c r="S6">
-        <v>0.09858848613165438</v>
+        <v>0.09856383338819218</v>
       </c>
       <c r="T6">
         <v>1.028465322007306</v>
       </c>
       <c r="U6">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V6">
         <v>0.125</v>
       </c>
       <c r="W6">
-        <v>0.05043203957971733</v>
+        <v>0.04920703957971734</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>20.8349633341569</v>
+        <v>21.35364582963591</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1834,13 +1834,13 @@
         <v>0.05</v>
       </c>
       <c r="B7">
-        <v>0.09664488415948665</v>
+        <v>0.09655999725771486</v>
       </c>
       <c r="C7">
-        <v>216902.8250893469</v>
+        <v>217168.2174494402</v>
       </c>
       <c r="D7">
-        <v>219999.1046724149</v>
+        <v>220264.4970325082</v>
       </c>
       <c r="E7">
         <v>3392.387921707505</v>
@@ -1867,37 +1867,37 @@
         <v>10954.1</v>
       </c>
       <c r="M7">
-        <v>657.1945810699972</v>
+        <v>641.231249653702</v>
       </c>
       <c r="N7">
-        <v>10296.90541893</v>
+        <v>10312.8687503463</v>
       </c>
       <c r="O7">
-        <v>1287.11317736625</v>
+        <v>1289.108593793287</v>
       </c>
       <c r="P7">
-        <v>9009.792241563751</v>
+        <v>9023.760156553009</v>
       </c>
       <c r="Q7">
-        <v>10154.79224156375</v>
+        <v>10168.76015655301</v>
       </c>
       <c r="R7">
         <v>0.05263157894736843</v>
       </c>
       <c r="S7">
-        <v>0.09907713913736925</v>
+        <v>0.09905225818813579</v>
       </c>
       <c r="T7">
         <v>1.037985630462809</v>
       </c>
       <c r="U7">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V7">
         <v>0.125</v>
       </c>
       <c r="W7">
-        <v>0.05043203957971733</v>
+        <v>0.04920703957971734</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>16.66797066732552</v>
+        <v>17.08291666370873</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1916,13 +1916,13 @@
         <v>0.06</v>
       </c>
       <c r="B8">
-        <v>0.09662754004939639</v>
+        <v>0.09653043287957651</v>
       </c>
       <c r="C8">
-        <v>214697.4204566767</v>
+        <v>215016.1059584994</v>
       </c>
       <c r="D8">
-        <v>220074.1759563583</v>
+        <v>220392.861458181</v>
       </c>
       <c r="E8">
         <v>5672.863838321109</v>
@@ -1949,37 +1949,37 @@
         <v>10954.1</v>
       </c>
       <c r="M8">
-        <v>788.6334972839966</v>
+        <v>769.4774995844424</v>
       </c>
       <c r="N8">
-        <v>10165.466502716</v>
+        <v>10184.62250041556</v>
       </c>
       <c r="O8">
-        <v>1270.6833128395</v>
+        <v>1273.077812551945</v>
       </c>
       <c r="P8">
-        <v>8894.783189876502</v>
+        <v>8911.544687863612</v>
       </c>
       <c r="Q8">
-        <v>10039.7831898765</v>
+        <v>10056.54468786361</v>
       </c>
       <c r="R8">
         <v>0.06382978723404255</v>
       </c>
       <c r="S8">
-        <v>0.09957618901554613</v>
+        <v>0.09955107500509945</v>
       </c>
       <c r="T8">
         <v>1.047708498672684</v>
       </c>
       <c r="U8">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V8">
         <v>0.125</v>
       </c>
       <c r="W8">
-        <v>0.05043203957971733</v>
+        <v>0.04920703957971734</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>13.8899755561046</v>
+        <v>14.23576388642394</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1998,13 +1998,13 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="B9">
-        <v>0.09661019593930614</v>
+        <v>0.09650086850143819</v>
       </c>
       <c r="C9">
-        <v>212492.067075319</v>
+        <v>212864.1441697049</v>
       </c>
       <c r="D9">
-        <v>220149.2984916142</v>
+        <v>220521.3755860002</v>
       </c>
       <c r="E9">
         <v>7953.339754934716</v>
@@ -2031,37 +2031,37 @@
         <v>10954.1</v>
       </c>
       <c r="M9">
-        <v>920.0724134979961</v>
+        <v>897.7237495151828</v>
       </c>
       <c r="N9">
-        <v>10034.027586502</v>
+        <v>10056.37625048482</v>
       </c>
       <c r="O9">
-        <v>1254.25344831275</v>
+        <v>1257.047031310602</v>
       </c>
       <c r="P9">
-        <v>8779.774138189252</v>
+        <v>8799.329219174215</v>
       </c>
       <c r="Q9">
-        <v>9924.774138189252</v>
+        <v>9944.329219174215</v>
       </c>
       <c r="R9">
         <v>0.07526881720430109</v>
       </c>
       <c r="S9">
-        <v>0.1000859711491677</v>
+        <v>0.1000606190654387</v>
       </c>
       <c r="T9">
         <v>1.057640460822556</v>
       </c>
       <c r="U9">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V9">
         <v>0.125</v>
       </c>
       <c r="W9">
-        <v>0.05043203957971733</v>
+        <v>0.04920703957971734</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>11.90569333380395</v>
+        <v>12.20208333122052</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2080,13 +2080,13 @@
         <v>0.08</v>
       </c>
       <c r="B10">
-        <v>0.09659285182921593</v>
+        <v>0.09647130412329986</v>
       </c>
       <c r="C10">
-        <v>210286.7649977755</v>
+        <v>210712.3323450899</v>
       </c>
       <c r="D10">
-        <v>220224.4723306843</v>
+        <v>220650.0396779987</v>
       </c>
       <c r="E10">
         <v>10233.81567154832</v>
@@ -2113,37 +2113,37 @@
         <v>10954.1</v>
       </c>
       <c r="M10">
-        <v>1051.511329711996</v>
+        <v>1025.969999445923</v>
       </c>
       <c r="N10">
-        <v>9902.588670288003</v>
+        <v>9928.130000554076</v>
       </c>
       <c r="O10">
-        <v>1237.823583786</v>
+        <v>1241.01625006926</v>
       </c>
       <c r="P10">
-        <v>8664.765086502002</v>
+        <v>8687.113750484816</v>
       </c>
       <c r="Q10">
-        <v>9809.765086502002</v>
+        <v>9832.113750484816</v>
       </c>
       <c r="R10">
         <v>0.08695652173913043</v>
       </c>
       <c r="S10">
-        <v>0.1006068355030854</v>
+        <v>0.1005812401705679</v>
       </c>
       <c r="T10">
         <v>1.067788335193078</v>
       </c>
       <c r="U10">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V10">
         <v>0.125</v>
       </c>
       <c r="W10">
-        <v>0.05043203957971733</v>
+        <v>0.04920703957971734</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>10.41748166707845</v>
+        <v>10.67682291481796</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2162,13 +2162,13 @@
         <v>0.09</v>
       </c>
       <c r="B11">
-        <v>0.09657550771912567</v>
+        <v>0.09644173974516151</v>
       </c>
       <c r="C11">
-        <v>208081.5142766204</v>
+        <v>208560.6707472992</v>
       </c>
       <c r="D11">
-        <v>220299.6975261428</v>
+        <v>220778.8539968217</v>
       </c>
       <c r="E11">
         <v>12514.29158816192</v>
@@ -2195,37 +2195,37 @@
         <v>10954.1</v>
       </c>
       <c r="M11">
-        <v>1182.950245925995</v>
+        <v>1154.216249376664</v>
       </c>
       <c r="N11">
-        <v>9771.149754074004</v>
+        <v>9799.883750623336</v>
       </c>
       <c r="O11">
-        <v>1221.39371925925</v>
+        <v>1224.985468827917</v>
       </c>
       <c r="P11">
-        <v>8549.756034814753</v>
+        <v>8574.898281795418</v>
       </c>
       <c r="Q11">
-        <v>9694.756034814753</v>
+        <v>9719.898281795418</v>
       </c>
       <c r="R11">
         <v>0.0989010989010989</v>
       </c>
       <c r="S11">
-        <v>0.101139147425221</v>
+        <v>0.1011133034977879</v>
       </c>
       <c r="T11">
         <v>1.078159239769545</v>
       </c>
       <c r="U11">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V11">
         <v>0.125</v>
       </c>
       <c r="W11">
-        <v>0.05043203957971733</v>
+        <v>0.04920703957971734</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>9.259983704069734</v>
+        <v>9.490509257615962</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2244,13 +2244,13 @@
         <v>0.1</v>
       </c>
       <c r="B12">
-        <v>0.09665441360903541</v>
+        <v>0.09654342536702318</v>
       </c>
       <c r="C12">
-        <v>205459.2205619728</v>
+        <v>205837.7722921953</v>
       </c>
       <c r="D12">
-        <v>219957.8797281088</v>
+        <v>220336.4314583314</v>
       </c>
       <c r="E12">
         <v>14794.76750477553</v>
@@ -2277,37 +2277,37 @@
         <v>10954.1</v>
       </c>
       <c r="M12">
-        <v>1339.474397222744</v>
+        <v>1316.669638056608</v>
       </c>
       <c r="N12">
-        <v>9614.625602777254</v>
+        <v>9637.43036194339</v>
       </c>
       <c r="O12">
-        <v>1201.828200347157</v>
+        <v>1204.678795242924</v>
       </c>
       <c r="P12">
-        <v>8412.797402430097</v>
+        <v>8432.751566700466</v>
       </c>
       <c r="Q12">
-        <v>9557.797402430097</v>
+        <v>9577.751566700466</v>
       </c>
       <c r="R12">
         <v>0.1111111111111111</v>
       </c>
       <c r="S12">
-        <v>0.1016832885011819</v>
+        <v>0.1016571904545016</v>
       </c>
       <c r="T12">
         <v>1.088760608892156</v>
       </c>
       <c r="U12">
-        <v>0.0587366166625341</v>
+        <v>0.05773661666253409</v>
       </c>
       <c r="V12">
         <v>0.125</v>
       </c>
       <c r="W12">
-        <v>0.05139453957971733</v>
+        <v>0.05051953957971733</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>8.177909202827724</v>
+        <v>8.319550845091367</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2326,13 +2326,13 @@
         <v>0.11</v>
       </c>
       <c r="B13">
-        <v>0.09664669449894515</v>
+        <v>0.09652698598888484</v>
       </c>
       <c r="C13">
-        <v>203212.136768595</v>
+        <v>203628.7020355826</v>
       </c>
       <c r="D13">
-        <v>219991.2718513446</v>
+        <v>220407.8371183323</v>
       </c>
       <c r="E13">
         <v>17075.24342138914</v>
@@ -2359,37 +2359,37 @@
         <v>10954.1</v>
       </c>
       <c r="M13">
-        <v>1473.421836945018</v>
+        <v>1448.336601862269</v>
       </c>
       <c r="N13">
-        <v>9480.678163054979</v>
+        <v>9505.763398137729</v>
       </c>
       <c r="O13">
-        <v>1185.084770381872</v>
+        <v>1188.220424767216</v>
       </c>
       <c r="P13">
-        <v>8295.593392673107</v>
+        <v>8317.542973370513</v>
       </c>
       <c r="Q13">
-        <v>9440.593392673107</v>
+        <v>9462.542973370513</v>
       </c>
       <c r="R13">
         <v>0.1235955056179775</v>
       </c>
       <c r="S13">
-        <v>0.1022396574664902</v>
+        <v>0.1022132995900179</v>
       </c>
       <c r="T13">
         <v>1.099600211028759</v>
       </c>
       <c r="U13">
-        <v>0.0587366166625341</v>
+        <v>0.05773661666253409</v>
       </c>
       <c r="V13">
         <v>0.125</v>
       </c>
       <c r="W13">
-        <v>0.05139453957971733</v>
+        <v>0.05051953957971733</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>7.434462911661568</v>
+        <v>7.563228040992152</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2408,13 +2408,13 @@
         <v>0.12</v>
       </c>
       <c r="B14">
-        <v>0.09663897538885491</v>
+        <v>0.09651054661074651</v>
       </c>
       <c r="C14">
-        <v>200965.0631153694</v>
+        <v>201419.678075637</v>
       </c>
       <c r="D14">
-        <v>220024.6741147326</v>
+        <v>220479.2890750003</v>
       </c>
       <c r="E14">
         <v>19355.71933800274</v>
@@ -2441,37 +2441,37 @@
         <v>10954.1</v>
       </c>
       <c r="M14">
-        <v>1607.369276667293</v>
+        <v>1580.003565667929</v>
       </c>
       <c r="N14">
-        <v>9346.730723332706</v>
+        <v>9374.096434332068</v>
       </c>
       <c r="O14">
-        <v>1168.341340416588</v>
+        <v>1171.762054291509</v>
       </c>
       <c r="P14">
-        <v>8178.389382916118</v>
+        <v>8202.33438004056</v>
       </c>
       <c r="Q14">
-        <v>9323.389382916117</v>
+        <v>9347.33438004056</v>
       </c>
       <c r="R14">
         <v>0.1363636363636364</v>
       </c>
       <c r="S14">
-        <v>0.10280867118101</v>
+        <v>0.1027820475695232</v>
       </c>
       <c r="T14">
         <v>1.110686167759375</v>
       </c>
       <c r="U14">
-        <v>0.0587366166625341</v>
+        <v>0.05773661666253409</v>
       </c>
       <c r="V14">
         <v>0.125</v>
       </c>
       <c r="W14">
-        <v>0.05139453957971733</v>
+        <v>0.05051953957971733</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
@@ -2479,7 +2479,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>6.814924335689772</v>
+        <v>6.93295903757614</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2490,13 +2490,13 @@
         <v>0.13</v>
       </c>
       <c r="B15">
-        <v>0.09688150627876467</v>
+        <v>0.09668748223260819</v>
       </c>
       <c r="C15">
-        <v>197639.9277142852</v>
+        <v>198372.5963375409</v>
       </c>
       <c r="D15">
-        <v>218980.0146302621</v>
+        <v>219712.6832535178</v>
       </c>
       <c r="E15">
         <v>21636.19525461634</v>
@@ -2523,37 +2523,37 @@
         <v>10954.1</v>
       </c>
       <c r="M15">
-        <v>1806.538327604716</v>
+        <v>1762.069047230751</v>
       </c>
       <c r="N15">
-        <v>9147.561672395283</v>
+        <v>9192.030952769248</v>
       </c>
       <c r="O15">
-        <v>1143.44520904941</v>
+        <v>1149.003869096156</v>
       </c>
       <c r="P15">
-        <v>8004.116463345872</v>
+        <v>8043.027083673092</v>
       </c>
       <c r="Q15">
-        <v>9149.116463345872</v>
+        <v>9188.027083673092</v>
       </c>
       <c r="R15">
         <v>0.1494252873563219</v>
       </c>
       <c r="S15">
-        <v>0.1033907656705763</v>
+        <v>0.1033638702152241</v>
       </c>
       <c r="T15">
         <v>1.122026974070005</v>
       </c>
       <c r="U15">
-        <v>0.0609366166625341</v>
+        <v>0.05943661666253409</v>
       </c>
       <c r="V15">
         <v>0.125</v>
       </c>
       <c r="W15">
-        <v>0.05331953957971734</v>
+        <v>0.05200703957971733</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -2561,7 +2561,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>6.063585716735944</v>
+        <v>6.21661223617505</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2572,13 +2572,13 @@
         <v>0.14</v>
       </c>
       <c r="B16">
-        <v>0.09707678716867441</v>
+        <v>0.09668591785446984</v>
       </c>
       <c r="C16">
-        <v>194525.4952553326</v>
+        <v>196098.8750149857</v>
       </c>
       <c r="D16">
-        <v>218146.058087923</v>
+        <v>219719.4378475762</v>
       </c>
       <c r="E16">
         <v>23916.67117122995</v>
@@ -2605,45 +2605,45 @@
         <v>10954.1</v>
       </c>
       <c r="M16">
-        <v>1993.392808592426</v>
+        <v>1897.612820094655</v>
       </c>
       <c r="N16">
-        <v>8960.707191407571</v>
+        <v>9056.487179905344</v>
       </c>
       <c r="O16">
-        <v>1120.088398925946</v>
+        <v>1132.060897488168</v>
       </c>
       <c r="P16">
-        <v>7840.618792481625</v>
+        <v>7924.426282417176</v>
       </c>
       <c r="Q16">
-        <v>8985.618792481626</v>
+        <v>9069.426282417175</v>
       </c>
       <c r="R16">
         <v>0.1627906976744186</v>
       </c>
       <c r="S16">
-        <v>0.1039863972412953</v>
+        <v>0.1039592236201272</v>
       </c>
       <c r="T16">
         <v>1.133631520062278</v>
       </c>
       <c r="U16">
-        <v>0.0624366166625341</v>
+        <v>0.05943661666253409</v>
       </c>
       <c r="V16">
         <v>0.125</v>
       </c>
       <c r="W16">
-        <v>0.05463203957971734</v>
+        <v>0.05200703957971733</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y16">
-        <v>5.495203932101521</v>
+        <v>5.772568505019689</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2654,13 +2654,13 @@
         <v>0.15</v>
       </c>
       <c r="B17">
-        <v>0.09710144305858415</v>
+        <v>0.09678935347633151</v>
       </c>
       <c r="C17">
-        <v>192140.176572672</v>
+        <v>193372.6821959327</v>
       </c>
       <c r="D17">
-        <v>218041.2153218761</v>
+        <v>219273.7209451368</v>
       </c>
       <c r="E17">
         <v>26197.14708784355</v>
@@ -2687,37 +2687,37 @@
         <v>10954.1</v>
       </c>
       <c r="M17">
-        <v>2135.778009206171</v>
+        <v>2060.522303957922</v>
       </c>
       <c r="N17">
-        <v>8818.321990793827</v>
+        <v>8893.577696042077</v>
       </c>
       <c r="O17">
-        <v>1102.290248849228</v>
+        <v>1111.69721200526</v>
       </c>
       <c r="P17">
-        <v>7716.031741944599</v>
+        <v>7781.880484036818</v>
       </c>
       <c r="Q17">
-        <v>8861.0317419446</v>
+        <v>8926.880484036818</v>
       </c>
       <c r="R17">
         <v>0.1764705882352941</v>
       </c>
       <c r="S17">
-        <v>0.1045960436725018</v>
+        <v>0.1045685853404399</v>
       </c>
       <c r="T17">
         <v>1.145509114195545</v>
       </c>
       <c r="U17">
-        <v>0.0624366166625341</v>
+        <v>0.0602366166625341</v>
       </c>
       <c r="V17">
         <v>0.125</v>
       </c>
       <c r="W17">
-        <v>0.05463203957971734</v>
+        <v>0.05270703957971733</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -2725,7 +2725,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>5.128857003294755</v>
+        <v>5.316176378658453</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2736,13 +2736,13 @@
         <v>0.16</v>
       </c>
       <c r="B18">
-        <v>0.09712609894849392</v>
+        <v>0.09679478909819317</v>
       </c>
       <c r="C18">
-        <v>189754.9586181692</v>
+        <v>191068.833518056</v>
       </c>
       <c r="D18">
-        <v>217936.4732839869</v>
+        <v>219250.3481838736</v>
       </c>
       <c r="E18">
         <v>28477.62300445716</v>
@@ -2769,37 +2769,37 @@
         <v>10954.1</v>
       </c>
       <c r="M18">
-        <v>2278.163209819916</v>
+        <v>2197.890457555117</v>
       </c>
       <c r="N18">
-        <v>8675.936790180083</v>
+        <v>8756.209542444882</v>
       </c>
       <c r="O18">
-        <v>1084.49209877251</v>
+        <v>1094.52619280561</v>
       </c>
       <c r="P18">
-        <v>7591.444691407572</v>
+        <v>7661.683349639272</v>
       </c>
       <c r="Q18">
-        <v>8736.444691407572</v>
+        <v>8806.683349639272</v>
       </c>
       <c r="R18">
         <v>0.1904761904761905</v>
       </c>
       <c r="S18">
-        <v>0.1052202054949276</v>
+        <v>0.1051924556731409</v>
       </c>
       <c r="T18">
         <v>1.157669508189128</v>
       </c>
       <c r="U18">
-        <v>0.0624366166625341</v>
+        <v>0.0602366166625341</v>
       </c>
       <c r="V18">
         <v>0.125</v>
       </c>
       <c r="W18">
-        <v>0.05463203957971734</v>
+        <v>0.05270703957971733</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -2807,7 +2807,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>4.808303440588832</v>
+        <v>4.983915354992298</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2818,13 +2818,13 @@
         <v>0.17</v>
       </c>
       <c r="B19">
-        <v>0.09715075483840366</v>
+        <v>0.09680022472005483</v>
       </c>
       <c r="C19">
-        <v>187369.8412467315</v>
+        <v>188764.9898223334</v>
       </c>
       <c r="D19">
-        <v>217831.8318291628</v>
+        <v>219226.9804047647</v>
       </c>
       <c r="E19">
         <v>30758.09892107077</v>
@@ -2851,37 +2851,37 @@
         <v>10954.1</v>
       </c>
       <c r="M19">
-        <v>2420.548410433661</v>
+        <v>2335.258611152312</v>
       </c>
       <c r="N19">
-        <v>8533.551589566337</v>
+        <v>8618.841388847686</v>
       </c>
       <c r="O19">
-        <v>1066.693948695792</v>
+        <v>1077.355173605961</v>
       </c>
       <c r="P19">
-        <v>7466.857640870545</v>
+        <v>7541.486215241725</v>
       </c>
       <c r="Q19">
-        <v>8611.857640870545</v>
+        <v>8686.486215241726</v>
       </c>
       <c r="R19">
         <v>0.2048192771084338</v>
       </c>
       <c r="S19">
-        <v>0.1058594073612671</v>
+        <v>0.1058313590259071</v>
       </c>
       <c r="T19">
         <v>1.170122923724725</v>
       </c>
       <c r="U19">
-        <v>0.0624366166625341</v>
+        <v>0.0602366166625341</v>
       </c>
       <c r="V19">
         <v>0.125</v>
       </c>
       <c r="W19">
-        <v>0.05463203957971734</v>
+        <v>0.05270703957971733</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>4.525462061730664</v>
+        <v>4.690743863522163</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2900,13 +2900,13 @@
         <v>0.18</v>
       </c>
       <c r="B20">
-        <v>0.09717541072831343</v>
+        <v>0.09680566034191651</v>
       </c>
       <c r="C20">
-        <v>184984.8243135443</v>
+        <v>186461.1511071721</v>
       </c>
       <c r="D20">
-        <v>217727.2908125892</v>
+        <v>219203.617606217</v>
       </c>
       <c r="E20">
         <v>33038.57483768437</v>
@@ -2933,37 +2933,37 @@
         <v>10954.1</v>
       </c>
       <c r="M20">
-        <v>2562.933611047406</v>
+        <v>2472.626764749506</v>
       </c>
       <c r="N20">
-        <v>8391.166388952593</v>
+        <v>8481.473235250493</v>
       </c>
       <c r="O20">
-        <v>1048.895798619074</v>
+        <v>1060.184154406312</v>
       </c>
       <c r="P20">
-        <v>7342.270590333519</v>
+        <v>7421.289080844181</v>
       </c>
       <c r="Q20">
-        <v>8487.270590333519</v>
+        <v>8566.289080844181</v>
       </c>
       <c r="R20">
         <v>0.2195121951219512</v>
       </c>
       <c r="S20">
-        <v>0.1065141995170296</v>
+        <v>0.1064858453872773</v>
       </c>
       <c r="T20">
         <v>1.182880081102655</v>
       </c>
       <c r="U20">
-        <v>0.0624366166625341</v>
+        <v>0.0602366166625341</v>
       </c>
       <c r="V20">
         <v>0.125</v>
       </c>
       <c r="W20">
-        <v>0.05463203957971734</v>
+        <v>0.05270703957971733</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>4.274047502745628</v>
+        <v>4.430146982215378</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2982,13 +2982,13 @@
         <v>0.19</v>
       </c>
       <c r="B21">
-        <v>0.09743281661822317</v>
+        <v>0.09697734596377817</v>
       </c>
       <c r="C21">
-        <v>181618.9091216797</v>
+        <v>183445.3086197776</v>
       </c>
       <c r="D21">
-        <v>216641.8515373382</v>
+        <v>218468.2510354361</v>
       </c>
       <c r="E21">
         <v>35319.05075429798</v>
@@ -3015,37 +3015,37 @@
         <v>10954.1</v>
       </c>
       <c r="M21">
-        <v>2765.979471043072</v>
+        <v>2653.32396076236</v>
       </c>
       <c r="N21">
-        <v>8188.120528956926</v>
+        <v>8300.776039237639</v>
       </c>
       <c r="O21">
-        <v>1023.515066119616</v>
+        <v>1037.597004904705</v>
       </c>
       <c r="P21">
-        <v>7164.60546283731</v>
+        <v>7263.179034332934</v>
       </c>
       <c r="Q21">
-        <v>8309.605462837309</v>
+        <v>8408.179034332934</v>
       </c>
       <c r="R21">
         <v>0.2345679012345679</v>
       </c>
       <c r="S21">
-        <v>0.1071851593803418</v>
+        <v>0.1071564919057184</v>
       </c>
       <c r="T21">
         <v>1.195952230020779</v>
       </c>
       <c r="U21">
-        <v>0.0638366166625341</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V21">
         <v>0.125</v>
       </c>
       <c r="W21">
-        <v>0.05585703957971733</v>
+        <v>0.05358203957971733</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>3.960296927246941</v>
+        <v>4.128444231458506</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3064,13 +3064,13 @@
         <v>0.2</v>
       </c>
       <c r="B22">
-        <v>0.09746972250813292</v>
+        <v>0.09699153158563983</v>
       </c>
       <c r="C22">
-        <v>179183.6934477271</v>
+        <v>181104.2932369287</v>
       </c>
       <c r="D22">
-        <v>216487.1117799992</v>
+        <v>218407.7115692008</v>
       </c>
       <c r="E22">
         <v>37599.52667091158</v>
@@ -3097,37 +3097,37 @@
         <v>10954.1</v>
       </c>
       <c r="M22">
-        <v>2911.557337940076</v>
+        <v>2792.972590276168</v>
       </c>
       <c r="N22">
-        <v>8042.542662059923</v>
+        <v>8161.12740972383</v>
       </c>
       <c r="O22">
-        <v>1005.31783275749</v>
+        <v>1020.140926215479</v>
       </c>
       <c r="P22">
-        <v>7037.224829302432</v>
+        <v>7140.986483508352</v>
       </c>
       <c r="Q22">
-        <v>8182.224829302432</v>
+        <v>8285.986483508352</v>
       </c>
       <c r="R22">
         <v>0.25</v>
       </c>
       <c r="S22">
-        <v>0.1078728932402368</v>
+        <v>0.1078439045871205</v>
       </c>
       <c r="T22">
         <v>1.209351182661857</v>
       </c>
       <c r="U22">
-        <v>0.0638366166625341</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V22">
         <v>0.125</v>
       </c>
       <c r="W22">
-        <v>0.05585703957971733</v>
+        <v>0.05358203957971733</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3135,7 +3135,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>3.762282080884594</v>
+        <v>3.92202201988558</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3146,13 +3146,13 @@
         <v>0.21</v>
       </c>
       <c r="B23">
-        <v>0.09750662839804265</v>
+        <v>0.09700571720750149</v>
       </c>
       <c r="C23">
-        <v>176748.6986664774</v>
+        <v>178763.3113968176</v>
       </c>
       <c r="D23">
-        <v>216332.5929153631</v>
+        <v>218347.2056457033</v>
       </c>
       <c r="E23">
         <v>39880.00258752518</v>
@@ -3179,37 +3179,37 @@
         <v>10954.1</v>
       </c>
       <c r="M23">
-        <v>3057.135204837079</v>
+        <v>2932.621219789976</v>
       </c>
       <c r="N23">
-        <v>7896.964795162919</v>
+        <v>8021.478780210022</v>
       </c>
       <c r="O23">
-        <v>987.1205993953649</v>
+        <v>1002.684847526253</v>
       </c>
       <c r="P23">
-        <v>6909.844195767555</v>
+        <v>7018.79393268377</v>
       </c>
       <c r="Q23">
-        <v>8054.844195767555</v>
+        <v>8163.79393268377</v>
       </c>
       <c r="R23">
         <v>0.2658227848101266</v>
       </c>
       <c r="S23">
-        <v>0.1085780380839266</v>
+        <v>0.1085487201212163</v>
       </c>
       <c r="T23">
         <v>1.223089349293848</v>
       </c>
       <c r="U23">
-        <v>0.0638366166625341</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V23">
         <v>0.125</v>
       </c>
       <c r="W23">
-        <v>0.05585703957971733</v>
+        <v>0.05358203957971733</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3217,7 +3217,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>3.583125791318662</v>
+        <v>3.735259066557696</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3228,13 +3228,13 @@
         <v>0.22</v>
       </c>
       <c r="B24">
-        <v>0.09754353428795241</v>
+        <v>0.09701990282936318</v>
       </c>
       <c r="C24">
-        <v>174313.9243052775</v>
+        <v>176422.3630715747</v>
       </c>
       <c r="D24">
-        <v>216178.2944707768</v>
+        <v>218286.733237074</v>
       </c>
       <c r="E24">
         <v>42160.47850413879</v>
@@ -3261,37 +3261,37 @@
         <v>10954.1</v>
       </c>
       <c r="M24">
-        <v>3202.713071734084</v>
+        <v>3072.269849303786</v>
       </c>
       <c r="N24">
-        <v>7751.386928265914</v>
+        <v>7881.830150696213</v>
       </c>
       <c r="O24">
-        <v>968.9233660332393</v>
+        <v>985.2287688370266</v>
       </c>
       <c r="P24">
-        <v>6782.463562232675</v>
+        <v>6896.601381859185</v>
       </c>
       <c r="Q24">
-        <v>7927.463562232675</v>
+        <v>8041.601381859185</v>
       </c>
       <c r="R24">
         <v>0.282051282051282</v>
       </c>
       <c r="S24">
-        <v>0.1093012635646341</v>
+        <v>0.109271607848494</v>
       </c>
       <c r="T24">
         <v>1.237179776608711</v>
       </c>
       <c r="U24">
-        <v>0.0638366166625341</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V24">
         <v>0.125</v>
       </c>
       <c r="W24">
-        <v>0.05585703957971733</v>
+        <v>0.05358203957971733</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>3.420256437167812</v>
+        <v>3.565474563532345</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3310,13 +3310,13 @@
         <v>0.23</v>
       </c>
       <c r="B25">
-        <v>0.09758044017786217</v>
+        <v>0.09703408845122483</v>
       </c>
       <c r="C25">
-        <v>171879.3698928223</v>
+        <v>174081.4482333618</v>
       </c>
       <c r="D25">
-        <v>216024.2159749352</v>
+        <v>218226.2943154747</v>
       </c>
       <c r="E25">
         <v>44440.9544207524</v>
@@ -3343,37 +3343,37 @@
         <v>10954.1</v>
       </c>
       <c r="M25">
-        <v>3348.290938631088</v>
+        <v>3211.918478817594</v>
       </c>
       <c r="N25">
-        <v>7605.809061368911</v>
+        <v>7742.181521182405</v>
       </c>
       <c r="O25">
-        <v>950.7261326711139</v>
+        <v>967.7726901478006</v>
       </c>
       <c r="P25">
-        <v>6655.082928697797</v>
+        <v>6774.408831034604</v>
       </c>
       <c r="Q25">
-        <v>7800.082928697797</v>
+        <v>7919.408831034604</v>
       </c>
       <c r="R25">
         <v>0.2987012987012987</v>
       </c>
       <c r="S25">
-        <v>0.1100432741227626</v>
+        <v>0.1100132718803764</v>
       </c>
       <c r="T25">
         <v>1.251636189048635</v>
       </c>
       <c r="U25">
-        <v>0.0638366166625341</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V25">
         <v>0.125</v>
       </c>
       <c r="W25">
-        <v>0.05585703957971733</v>
+        <v>0.05358203957971733</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3381,7 +3381,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>3.271549635551821</v>
+        <v>3.410453930335287</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3392,13 +3392,13 @@
         <v>0.24</v>
       </c>
       <c r="B26">
-        <v>0.09761734606777193</v>
+        <v>0.0970482740730865</v>
       </c>
       <c r="C26">
-        <v>169445.0349591493</v>
+        <v>171740.5668543708</v>
       </c>
       <c r="D26">
-        <v>215870.3569578759</v>
+        <v>218165.8888530973</v>
       </c>
       <c r="E26">
         <v>46721.430337366</v>
@@ -3425,37 +3425,37 @@
         <v>10954.1</v>
       </c>
       <c r="M26">
-        <v>3493.868805528091</v>
+        <v>3351.567108331402</v>
       </c>
       <c r="N26">
-        <v>7460.231194471908</v>
+        <v>7602.532891668597</v>
       </c>
       <c r="O26">
-        <v>932.5288993089885</v>
+        <v>950.3166114585746</v>
       </c>
       <c r="P26">
-        <v>6527.702295162919</v>
+        <v>6652.216280210022</v>
       </c>
       <c r="Q26">
-        <v>7672.702295162919</v>
+        <v>7797.216280210022</v>
       </c>
       <c r="R26">
         <v>0.3157894736842105</v>
       </c>
       <c r="S26">
-        <v>0.110804811274526</v>
+        <v>0.110774453386782</v>
       </c>
       <c r="T26">
         <v>1.266473033394873</v>
       </c>
       <c r="U26">
-        <v>0.0638366166625341</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V26">
         <v>0.125</v>
       </c>
       <c r="W26">
-        <v>0.05585703957971733</v>
+        <v>0.05358203957971733</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3463,7 +3463,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>3.135235067403829</v>
+        <v>3.268351683237984</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3474,13 +3474,13 @@
         <v>0.25</v>
       </c>
       <c r="B27">
-        <v>0.09765425195768165</v>
+        <v>0.09706245969494816</v>
       </c>
       <c r="C27">
-        <v>167010.9190356341</v>
+        <v>169399.7189068246</v>
       </c>
       <c r="D27">
-        <v>215716.7169509742</v>
+        <v>218105.5168221647</v>
       </c>
       <c r="E27">
         <v>49001.90625397961</v>
@@ -3507,37 +3507,37 @@
         <v>10954.1</v>
       </c>
       <c r="M27">
-        <v>3639.446672425095</v>
+        <v>3491.21573784521</v>
       </c>
       <c r="N27">
-        <v>7314.653327574904</v>
+        <v>7462.884262154788</v>
       </c>
       <c r="O27">
-        <v>914.331665946863</v>
+        <v>932.8605327693485</v>
       </c>
       <c r="P27">
-        <v>6400.321661628042</v>
+        <v>6530.02372938544</v>
       </c>
       <c r="Q27">
-        <v>7545.321661628042</v>
+        <v>7675.02372938544</v>
       </c>
       <c r="R27">
         <v>0.3333333333333333</v>
       </c>
       <c r="S27">
-        <v>0.1115866560836698</v>
+        <v>0.1115559330666918</v>
       </c>
       <c r="T27">
         <v>1.281705526923677</v>
       </c>
       <c r="U27">
-        <v>0.0638366166625341</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V27">
         <v>0.125</v>
       </c>
       <c r="W27">
-        <v>0.05585703957971733</v>
+        <v>0.05358203957971733</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3545,7 +3545,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>3.009825664707676</v>
+        <v>3.137617615908464</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3556,13 +3556,13 @@
         <v>0.26</v>
       </c>
       <c r="B28">
-        <v>0.09828265784759142</v>
+        <v>0.09707664531680983</v>
       </c>
       <c r="C28">
-        <v>162147.5393362576</v>
+        <v>167058.9043629769</v>
       </c>
       <c r="D28">
-        <v>213133.8131682113</v>
+        <v>218045.1781949306</v>
       </c>
       <c r="E28">
         <v>51282.38217059321</v>
@@ -3589,45 +3589,45 @@
         <v>10954.1</v>
       </c>
       <c r="M28">
-        <v>3939.184711285178</v>
+        <v>3630.864367359019</v>
       </c>
       <c r="N28">
-        <v>7014.915288714821</v>
+        <v>7323.235632640979</v>
       </c>
       <c r="O28">
-        <v>876.8644110893526</v>
+        <v>915.4044540801224</v>
       </c>
       <c r="P28">
-        <v>6138.050877625468</v>
+        <v>6407.831178560857</v>
       </c>
       <c r="Q28">
-        <v>7283.050877625468</v>
+        <v>7552.831178560857</v>
       </c>
       <c r="R28">
         <v>0.3513513513513514</v>
       </c>
       <c r="S28">
-        <v>0.1123896318336012</v>
+        <v>0.1123585338190315</v>
       </c>
       <c r="T28">
         <v>1.297349709466774</v>
       </c>
       <c r="U28">
-        <v>0.06643661666253409</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V28">
         <v>0.125</v>
       </c>
       <c r="W28">
-        <v>0.05813203957971733</v>
+        <v>0.05358203957971733</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y28">
-        <v>2.780803847206792</v>
+        <v>3.0169400152966</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3638,13 +3638,13 @@
         <v>0.27</v>
       </c>
       <c r="B29">
-        <v>0.09834231373750117</v>
+        <v>0.09768145593867149</v>
       </c>
       <c r="C29">
-        <v>159625.0739374539</v>
+        <v>162236.5560676486</v>
       </c>
       <c r="D29">
-        <v>212891.8236860213</v>
+        <v>215503.305816216</v>
       </c>
       <c r="E29">
         <v>53562.85808720682</v>
@@ -3671,37 +3671,37 @@
         <v>10954.1</v>
       </c>
       <c r="M29">
-        <v>4090.691815565377</v>
+        <v>3924.445121244245</v>
       </c>
       <c r="N29">
-        <v>6863.408184434622</v>
+        <v>7029.654878755753</v>
       </c>
       <c r="O29">
-        <v>857.9260230543277</v>
+        <v>878.7068598444691</v>
       </c>
       <c r="P29">
-        <v>6005.482161380294</v>
+        <v>6150.948018911284</v>
       </c>
       <c r="Q29">
-        <v>7150.482161380294</v>
+        <v>7295.948018911284</v>
       </c>
       <c r="R29">
         <v>0.3698630136986302</v>
       </c>
       <c r="S29">
-        <v>0.1132146069191473</v>
+        <v>0.1131831236330792</v>
       </c>
       <c r="T29">
         <v>1.313422499750777</v>
       </c>
       <c r="U29">
-        <v>0.06643661666253409</v>
+        <v>0.06373661666253409</v>
       </c>
       <c r="V29">
         <v>0.125</v>
       </c>
       <c r="W29">
-        <v>0.05813203957971733</v>
+        <v>0.05576953957971733</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3709,7 +3709,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>2.677811112125059</v>
+        <v>2.791248102999845</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3720,13 +3720,13 @@
         <v>0.28</v>
       </c>
       <c r="B30">
-        <v>0.09840196962741093</v>
+        <v>0.09771751656053317</v>
       </c>
       <c r="C30">
-        <v>157103.1574191583</v>
+        <v>159806.3968892804</v>
       </c>
       <c r="D30">
-        <v>212650.3830843392</v>
+        <v>215353.6225544614</v>
       </c>
       <c r="E30">
         <v>55843.33400382043</v>
@@ -3753,37 +3753,37 @@
         <v>10954.1</v>
       </c>
       <c r="M30">
-        <v>4242.198919845576</v>
+        <v>4069.794940549588</v>
       </c>
       <c r="N30">
-        <v>6711.901080154423</v>
+        <v>6884.305059450411</v>
       </c>
       <c r="O30">
-        <v>838.9876350193028</v>
+        <v>860.5381324313014</v>
       </c>
       <c r="P30">
-        <v>5872.91344513512</v>
+        <v>6023.76692701911</v>
       </c>
       <c r="Q30">
-        <v>7017.91344513512</v>
+        <v>7168.76692701911</v>
       </c>
       <c r="R30">
         <v>0.388888888888889</v>
       </c>
       <c r="S30">
-        <v>0.1140624979792918</v>
+        <v>0.1140306187197393</v>
       </c>
       <c r="T30">
         <v>1.329941756431558</v>
       </c>
       <c r="U30">
-        <v>0.06643661666253409</v>
+        <v>0.06373661666253409</v>
       </c>
       <c r="V30">
         <v>0.125</v>
       </c>
       <c r="W30">
-        <v>0.05813203957971733</v>
+        <v>0.05576953957971733</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>2.582175000977736</v>
+        <v>2.691560670749851</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3802,13 +3802,13 @@
         <v>0.29</v>
       </c>
       <c r="B31">
-        <v>0.09914675051732066</v>
+        <v>0.09775357718239482</v>
       </c>
       <c r="C31">
-        <v>151853.8419759127</v>
+        <v>157376.4454991646</v>
       </c>
       <c r="D31">
-        <v>209681.5435577072</v>
+        <v>215204.1470809591</v>
       </c>
       <c r="E31">
         <v>58123.80992043402</v>
@@ -3835,45 +3835,45 @@
         <v>10954.1</v>
       </c>
       <c r="M31">
-        <v>4572.267288396621</v>
+        <v>4215.144759854929</v>
       </c>
       <c r="N31">
-        <v>6381.832711603378</v>
+        <v>6738.955240145069</v>
       </c>
       <c r="O31">
-        <v>797.7290889504222</v>
+        <v>842.3694050181336</v>
       </c>
       <c r="P31">
-        <v>5584.103622652956</v>
+        <v>5896.585835126935</v>
       </c>
       <c r="Q31">
-        <v>6729.103622652956</v>
+        <v>7041.585835126935</v>
       </c>
       <c r="R31">
         <v>0.4084507042253521</v>
       </c>
       <c r="S31">
-        <v>0.1149342732946516</v>
+        <v>0.1149019869074321</v>
       </c>
       <c r="T31">
         <v>1.346926344286445</v>
       </c>
       <c r="U31">
-        <v>0.06913661666253409</v>
+        <v>0.06373661666253409</v>
       </c>
       <c r="V31">
         <v>0.125</v>
       </c>
       <c r="W31">
-        <v>0.06049453957971733</v>
+        <v>0.05576953957971733</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y31">
-        <v>2.395769824699231</v>
+        <v>2.598748233827443</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3884,13 +3884,13 @@
         <v>0.3</v>
       </c>
       <c r="B32">
-        <v>0.09923003140723044</v>
+        <v>0.09778963780425648</v>
       </c>
       <c r="C32">
-        <v>149246.5373997378</v>
+        <v>154946.7014649279</v>
       </c>
       <c r="D32">
-        <v>209354.714898146</v>
+        <v>215054.878963336</v>
       </c>
       <c r="E32">
         <v>60404.28583704762</v>
@@ -3917,45 +3917,45 @@
         <v>10954.1</v>
       </c>
       <c r="M32">
-        <v>4729.931677651676</v>
+        <v>4360.494579160272</v>
       </c>
       <c r="N32">
-        <v>6224.168322348322</v>
+        <v>6593.605420839726</v>
       </c>
       <c r="O32">
-        <v>778.0210402935403</v>
+        <v>824.2006776049658</v>
       </c>
       <c r="P32">
-        <v>5446.147282054782</v>
+        <v>5769.404743234761</v>
       </c>
       <c r="Q32">
-        <v>6591.147282054782</v>
+        <v>6914.404743234761</v>
       </c>
       <c r="R32">
         <v>0.4285714285714286</v>
       </c>
       <c r="S32">
-        <v>0.1158309564761646</v>
+        <v>0.115798251329059</v>
       </c>
       <c r="T32">
         <v>1.364396206080044</v>
       </c>
       <c r="U32">
-        <v>0.06913661666253409</v>
+        <v>0.06373661666253409</v>
       </c>
       <c r="V32">
         <v>0.125</v>
       </c>
       <c r="W32">
-        <v>0.06049453957971733</v>
+        <v>0.05576953957971733</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y32">
-        <v>2.31591083054259</v>
+        <v>2.512123292699861</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3966,13 +3966,13 @@
         <v>0.31</v>
       </c>
       <c r="B33">
-        <v>0.1005881872971402</v>
+        <v>0.09877507342611816</v>
       </c>
       <c r="C33">
-        <v>141776.3234547932</v>
+        <v>148665.8018645004</v>
       </c>
       <c r="D33">
-        <v>204164.976869815</v>
+        <v>211054.4552795221</v>
       </c>
       <c r="E33">
         <v>62684.76175366123</v>
@@ -3999,45 +3999,45 @@
         <v>10954.1</v>
       </c>
       <c r="M33">
-        <v>5219.861407957335</v>
+        <v>4753.276035418191</v>
       </c>
       <c r="N33">
-        <v>5734.238592042663</v>
+        <v>6200.823964581808</v>
       </c>
       <c r="O33">
-        <v>716.7798240053329</v>
+        <v>775.1029955727259</v>
       </c>
       <c r="P33">
-        <v>5017.458768037331</v>
+        <v>5425.720969009081</v>
       </c>
       <c r="Q33">
-        <v>6162.458768037331</v>
+        <v>6570.720969009081</v>
       </c>
       <c r="R33">
         <v>0.4492753623188406</v>
       </c>
       <c r="S33">
-        <v>0.116753630474533</v>
+        <v>0.1167204944295736</v>
       </c>
       <c r="T33">
         <v>1.382372440679254</v>
       </c>
       <c r="U33">
-        <v>0.0738366166625341</v>
+        <v>0.0672366166625341</v>
       </c>
       <c r="V33">
         <v>0.125</v>
       </c>
       <c r="W33">
-        <v>0.06460703957971733</v>
+        <v>0.05883203957971733</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y33">
-        <v>2.09854230675573</v>
+        <v>2.304536895896108</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4048,13 +4048,13 @@
         <v>0.32</v>
       </c>
       <c r="B34">
-        <v>0.1007125931870499</v>
+        <v>0.09962575904797981</v>
       </c>
       <c r="C34">
-        <v>139033.3065405368</v>
+        <v>143049.7298743397</v>
       </c>
       <c r="D34">
-        <v>203702.4358721721</v>
+        <v>207718.859205975</v>
       </c>
       <c r="E34">
         <v>64965.23767027485</v>
@@ -4081,37 +4081,37 @@
         <v>10954.1</v>
       </c>
       <c r="M34">
-        <v>5388.244034020476</v>
+        <v>5110.938162560261</v>
       </c>
       <c r="N34">
-        <v>5565.855965979523</v>
+        <v>5843.161837439738</v>
       </c>
       <c r="O34">
-        <v>695.7319957474404</v>
+        <v>730.3952296799672</v>
       </c>
       <c r="P34">
-        <v>4870.123970232083</v>
+        <v>5112.766607759771</v>
       </c>
       <c r="Q34">
-        <v>6015.123970232083</v>
+        <v>6257.766607759771</v>
       </c>
       <c r="R34">
         <v>0.4705882352941177</v>
       </c>
       <c r="S34">
-        <v>0.1177034419434417</v>
+        <v>0.1176698623271622</v>
       </c>
       <c r="T34">
         <v>1.400877388060794</v>
       </c>
       <c r="U34">
-        <v>0.0738366166625341</v>
+        <v>0.07003661666253409</v>
       </c>
       <c r="V34">
         <v>0.125</v>
       </c>
       <c r="W34">
-        <v>0.06460703957971733</v>
+        <v>0.06128203957971733</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4119,7 +4119,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>2.032962859669613</v>
+        <v>2.143266001581337</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4130,13 +4130,13 @@
         <v>0.33</v>
       </c>
       <c r="B35">
-        <v>0.1035223740769597</v>
+        <v>0.09971694466984148</v>
       </c>
       <c r="C35">
-        <v>126837.1052107829</v>
+        <v>140417.9548723443</v>
       </c>
       <c r="D35">
-        <v>193786.7104590319</v>
+        <v>207367.5601205933</v>
       </c>
       <c r="E35">
         <v>67245.71358688847</v>
@@ -4163,45 +4163,45 @@
         <v>10954.1</v>
       </c>
       <c r="M35">
-        <v>6256.504718892331</v>
+        <v>5270.654980140269</v>
       </c>
       <c r="N35">
-        <v>4697.595281107668</v>
+        <v>5683.44501985973</v>
       </c>
       <c r="O35">
-        <v>587.1994101384585</v>
+        <v>710.4306274824662</v>
       </c>
       <c r="P35">
-        <v>4110.395870969209</v>
+        <v>4973.014392377263</v>
       </c>
       <c r="Q35">
-        <v>5255.395870969209</v>
+        <v>6118.014392377263</v>
       </c>
       <c r="R35">
         <v>0.4925373134328359</v>
       </c>
       <c r="S35">
-        <v>0.1186816059935119</v>
+        <v>0.1186475695649773</v>
       </c>
       <c r="T35">
         <v>1.419934721931335</v>
       </c>
       <c r="U35">
-        <v>0.08313661666253409</v>
+        <v>0.07003661666253409</v>
       </c>
       <c r="V35">
         <v>0.125</v>
       </c>
       <c r="W35">
-        <v>0.07274453957971733</v>
+        <v>0.06128203957971733</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y35">
-        <v>1.750833810917247</v>
+        <v>2.078318546987964</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4212,13 +4212,13 @@
         <v>0.34</v>
       </c>
       <c r="B36">
-        <v>0.1051264049668694</v>
+        <v>0.09980813029170314</v>
       </c>
       <c r="C36">
-        <v>119317.1432709748</v>
+        <v>137787.3661149158</v>
       </c>
       <c r="D36">
-        <v>188547.2244358374</v>
+        <v>207017.4472797784</v>
       </c>
       <c r="E36">
         <v>69526.18950350207</v>
@@ -4245,45 +4245,45 @@
         <v>10954.1</v>
       </c>
       <c r="M36">
-        <v>6810.515822454831</v>
+        <v>5430.371797720277</v>
       </c>
       <c r="N36">
-        <v>4143.584177545167</v>
+        <v>5523.728202279722</v>
       </c>
       <c r="O36">
-        <v>517.9480221931459</v>
+        <v>690.4660252849652</v>
       </c>
       <c r="P36">
-        <v>3625.636155352021</v>
+        <v>4833.262176994756</v>
       </c>
       <c r="Q36">
-        <v>4770.636155352022</v>
+        <v>5978.262176994756</v>
       </c>
       <c r="R36">
         <v>0.5151515151515152</v>
       </c>
       <c r="S36">
-        <v>0.1196894113784326</v>
+        <v>0.1196549042948474</v>
       </c>
       <c r="T36">
         <v>1.43956955076765</v>
       </c>
       <c r="U36">
-        <v>0.08783661666253409</v>
+        <v>0.07003661666253409</v>
       </c>
       <c r="V36">
         <v>0.125</v>
       </c>
       <c r="W36">
-        <v>0.07685703957971733</v>
+        <v>0.06128203957971733</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y36">
-        <v>1.608409742457896</v>
+        <v>2.017191530900083</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4294,13 +4294,13 @@
         <v>0.35</v>
       </c>
       <c r="B37">
-        <v>0.1053733108567792</v>
+        <v>0.1022880659135648</v>
       </c>
       <c r="C37">
-        <v>116255.2197636564</v>
+        <v>126418.422863599</v>
       </c>
       <c r="D37">
-        <v>187765.7768451326</v>
+        <v>197928.9799450752</v>
       </c>
       <c r="E37">
         <v>71806.66542011568</v>
@@ -4327,45 +4327,45 @@
         <v>10954.1</v>
       </c>
       <c r="M37">
-        <v>7010.825111350561</v>
+        <v>6212.658540535801</v>
       </c>
       <c r="N37">
-        <v>3943.274888649437</v>
+        <v>4741.441459464198</v>
       </c>
       <c r="O37">
-        <v>492.9093610811797</v>
+        <v>592.6801824330247</v>
       </c>
       <c r="P37">
-        <v>3450.365527568258</v>
+        <v>4148.761277031173</v>
       </c>
       <c r="Q37">
-        <v>4595.365527568258</v>
+        <v>5293.761277031173</v>
       </c>
       <c r="R37">
         <v>0.5384615384615385</v>
       </c>
       <c r="S37">
-        <v>0.1207282261598125</v>
+        <v>0.1206932339394827</v>
       </c>
       <c r="T37">
         <v>1.459808528183544</v>
       </c>
       <c r="U37">
-        <v>0.08783661666253409</v>
+        <v>0.07783661666253411</v>
       </c>
       <c r="V37">
         <v>0.125</v>
       </c>
       <c r="W37">
-        <v>0.07685703957971733</v>
+        <v>0.06810703957971734</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y37">
-        <v>1.56245517838767</v>
+        <v>1.763190416554791</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4376,13 +4376,13 @@
         <v>0.36</v>
       </c>
       <c r="B38">
-        <v>0.1056202167466889</v>
+        <v>0.1036760015354265</v>
       </c>
       <c r="C38">
-        <v>113199.7470525167</v>
+        <v>119391.3736769512</v>
       </c>
       <c r="D38">
-        <v>186990.7800506064</v>
+        <v>193182.406675041</v>
       </c>
       <c r="E38">
         <v>74087.14133672927</v>
@@ -4409,37 +4409,37 @@
         <v>10954.1</v>
       </c>
       <c r="M38">
-        <v>7211.13440024629</v>
+        <v>6710.341888957943</v>
       </c>
       <c r="N38">
-        <v>3742.965599753708</v>
+        <v>4243.758111042055</v>
       </c>
       <c r="O38">
-        <v>467.8706999692135</v>
+        <v>530.4697638802569</v>
       </c>
       <c r="P38">
-        <v>3275.094899784495</v>
+        <v>3713.288347161798</v>
       </c>
       <c r="Q38">
-        <v>4420.094899784495</v>
+        <v>4858.288347161799</v>
       </c>
       <c r="R38">
         <v>0.5625</v>
       </c>
       <c r="S38">
-        <v>0.1217995039031105</v>
+        <v>0.1217640113855129</v>
       </c>
       <c r="T38">
         <v>1.480679973643684</v>
       </c>
       <c r="U38">
-        <v>0.08783661666253409</v>
+        <v>0.0817366166625341</v>
       </c>
       <c r="V38">
         <v>0.125</v>
       </c>
       <c r="W38">
-        <v>0.07685703957971733</v>
+        <v>0.07151953957971734</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4447,7 +4447,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>1.519053645654679</v>
+        <v>1.632420550438015</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4458,13 +4458,13 @@
         <v>0.37</v>
       </c>
       <c r="B39">
-        <v>0.122176029824714</v>
+        <v>0.1038695621572882</v>
       </c>
       <c r="C39">
-        <v>70385.81569265883</v>
+        <v>116466.9716589582</v>
       </c>
       <c r="D39">
-        <v>146457.3246073622</v>
+        <v>192538.4805736615</v>
       </c>
       <c r="E39">
         <v>76367.61725334288</v>
@@ -4491,45 +4491,45 @@
         <v>10954.1</v>
       </c>
       <c r="M39">
-        <v>11545.94652596249</v>
+        <v>6896.740274762331</v>
       </c>
       <c r="N39">
-        <v>-591.84652596249</v>
+        <v>4057.359725237668</v>
       </c>
       <c r="O39">
-        <v>-73.98081574531125</v>
+        <v>507.1699656547084</v>
       </c>
       <c r="P39">
-        <v>-517.8657102171787</v>
+        <v>3550.189759582959</v>
       </c>
       <c r="Q39">
-        <v>627.1342897828213</v>
+        <v>4695.18975958296</v>
       </c>
       <c r="R39">
         <v>0.5873015873015873</v>
       </c>
       <c r="S39">
-        <v>0.1230964533871748</v>
+        <v>0.1228687817663377</v>
       </c>
       <c r="T39">
-        <v>1.505948127108605</v>
+        <v>1.502214004673988</v>
       </c>
       <c r="U39">
-        <v>0.1368366166625341</v>
+        <v>0.0817366166625341</v>
       </c>
       <c r="V39">
-        <v>0.1185924858495615</v>
+        <v>0.125</v>
       </c>
       <c r="W39">
-        <v>0.1206088221372807</v>
+        <v>0.07151953957971734</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y39">
-        <v>0.9487398867964918</v>
+        <v>1.588301076101853</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4540,13 +4540,13 @@
         <v>0.38</v>
       </c>
       <c r="B40">
-        <v>0.1230863959913393</v>
+        <v>0.1040631227791498</v>
       </c>
       <c r="C40">
-        <v>66380.20055242362</v>
+        <v>113546.8481186941</v>
       </c>
       <c r="D40">
-        <v>144732.1853837406</v>
+        <v>191898.8329500111</v>
       </c>
       <c r="E40">
         <v>78648.09316995648</v>
@@ -4573,45 +4573,45 @@
         <v>10954.1</v>
       </c>
       <c r="M40">
-        <v>11857.99913477229</v>
+        <v>7083.138660566718</v>
       </c>
       <c r="N40">
-        <v>-903.8991347722877</v>
+        <v>3870.96133943328</v>
       </c>
       <c r="O40">
-        <v>-112.987391846536</v>
+        <v>483.87016742916</v>
       </c>
       <c r="P40">
-        <v>-790.9117429257517</v>
+        <v>3387.09117200412</v>
       </c>
       <c r="Q40">
-        <v>354.0882570742483</v>
+        <v>4532.09117200412</v>
       </c>
       <c r="R40">
         <v>0.6129032258064516</v>
       </c>
       <c r="S40">
-        <v>0.1243431703772906</v>
+        <v>0.1240091899013826</v>
       </c>
       <c r="T40">
-        <v>1.530237613029712</v>
+        <v>1.524442681866559</v>
       </c>
       <c r="U40">
-        <v>0.1368366166625341</v>
+        <v>0.0817366166625341</v>
       </c>
       <c r="V40">
-        <v>0.1154716309587835</v>
+        <v>0.125</v>
       </c>
       <c r="W40">
-        <v>0.1210358693616294</v>
+        <v>0.07151953957971734</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y40">
-        <v>0.9237730476702682</v>
+        <v>1.54650367936233</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4622,13 +4622,13 @@
         <v>0.39</v>
       </c>
       <c r="B41">
-        <v>0.1239967621579647</v>
+        <v>0.1042566834010115</v>
       </c>
       <c r="C41">
-        <v>62414.75353011463</v>
+        <v>110630.9605557247</v>
       </c>
       <c r="D41">
-        <v>143047.2142780452</v>
+        <v>191263.4213036553</v>
       </c>
       <c r="E41">
         <v>80928.56908657009</v>
@@ -4655,45 +4655,45 @@
         <v>10954.1</v>
       </c>
       <c r="M41">
-        <v>12170.05174358208</v>
+        <v>7269.537046371105</v>
       </c>
       <c r="N41">
-        <v>-1215.951743582084</v>
+        <v>3684.562953628893</v>
       </c>
       <c r="O41">
-        <v>-151.9939679477604</v>
+        <v>460.5703692036117</v>
       </c>
       <c r="P41">
-        <v>-1063.957775634323</v>
+        <v>3223.992584425282</v>
       </c>
       <c r="Q41">
-        <v>81.04222436567693</v>
+        <v>4368.992584425281</v>
       </c>
       <c r="R41">
         <v>0.639344262295082</v>
       </c>
       <c r="S41">
-        <v>0.1256307633342953</v>
+        <v>0.1251869884670848</v>
       </c>
       <c r="T41">
-        <v>1.555323475538395</v>
+        <v>1.547400168147412</v>
       </c>
       <c r="U41">
-        <v>0.1368366166625341</v>
+        <v>0.0817366166625341</v>
       </c>
       <c r="V41">
-        <v>0.1125108199085583</v>
+        <v>0.125</v>
       </c>
       <c r="W41">
-        <v>0.1214410167283193</v>
+        <v>0.07151953957971734</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y41">
-        <v>0.9000865592684666</v>
+        <v>1.50684973886586</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4704,13 +4704,13 @@
         <v>0.4</v>
       </c>
       <c r="B42">
-        <v>0.12490712832459</v>
+        <v>0.1094202440228731</v>
       </c>
       <c r="C42">
-        <v>58488.08785959666</v>
+        <v>92827.11961883512</v>
       </c>
       <c r="D42">
-        <v>141401.0245241409</v>
+        <v>175740.0562833793</v>
       </c>
       <c r="E42">
         <v>83209.0450031837</v>
@@ -4737,45 +4737,45 @@
         <v>10954.1</v>
       </c>
       <c r="M42">
-        <v>12482.10435239188</v>
+        <v>8751.245752812021</v>
       </c>
       <c r="N42">
-        <v>-1528.004352391881</v>
+        <v>2202.854247187977</v>
       </c>
       <c r="O42">
-        <v>-191.0005440489851</v>
+        <v>275.3567808984972</v>
       </c>
       <c r="P42">
-        <v>-1337.003808342896</v>
+        <v>1927.49746628948</v>
       </c>
       <c r="Q42">
-        <v>-192.003808342896</v>
+        <v>3072.49746628948</v>
       </c>
       <c r="R42">
         <v>0.6666666666666667</v>
       </c>
       <c r="S42">
-        <v>0.1269612760565336</v>
+        <v>0.126404046984977</v>
       </c>
       <c r="T42">
-        <v>1.581245533464035</v>
+        <v>1.57112290397096</v>
       </c>
       <c r="U42">
-        <v>0.1368366166625341</v>
+        <v>0.0959366166625341</v>
       </c>
       <c r="V42">
-        <v>0.1096980494108444</v>
+        <v>0.125</v>
       </c>
       <c r="W42">
-        <v>0.1218259067266747</v>
+        <v>0.08394453957971734</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y42">
-        <v>0.8775843952867548</v>
+        <v>1.251718933442149</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4786,13 +4786,13 @@
         <v>0.41</v>
       </c>
       <c r="B43">
-        <v>0.1258174944912154</v>
+        <v>0.1205311292903624</v>
       </c>
       <c r="C43">
-        <v>54598.87988418218</v>
+        <v>64417.93909399948</v>
       </c>
       <c r="D43">
-        <v>139792.29246534</v>
+        <v>149611.3516751573</v>
       </c>
       <c r="E43">
         <v>85489.5209197973</v>
@@ -4819,37 +4819,37 @@
         <v>10954.1</v>
       </c>
       <c r="M43">
-        <v>12794.15696120168</v>
+        <v>11644.11295645343</v>
       </c>
       <c r="N43">
-        <v>-1840.056961201679</v>
+        <v>-690.0129564534363</v>
       </c>
       <c r="O43">
-        <v>-230.0071201502099</v>
+        <v>-86.25161955667954</v>
       </c>
       <c r="P43">
-        <v>-1610.049841051469</v>
+        <v>-603.7613368967568</v>
       </c>
       <c r="Q43">
-        <v>-465.049841051469</v>
+        <v>541.2386631032432</v>
       </c>
       <c r="R43">
         <v>0.6949152542372882</v>
       </c>
       <c r="S43">
-        <v>0.1283368909049494</v>
+        <v>0.1279244075136732</v>
       </c>
       <c r="T43">
-        <v>1.608046305217663</v>
+        <v>1.600757560520812</v>
       </c>
       <c r="U43">
-        <v>0.1368366166625341</v>
+        <v>0.1245366166625341</v>
       </c>
       <c r="V43">
-        <v>0.1070224872300921</v>
+        <v>0.1175926843994693</v>
       </c>
       <c r="W43">
-        <v>0.122192021603159</v>
+        <v>0.109892021603159</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4857,7 +4857,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.8561798978407364</v>
+        <v>0.9407414751957541</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4868,13 +4868,13 @@
         <v>0.42</v>
       </c>
       <c r="B44">
-        <v>0.1267278606578407</v>
+        <v>0.1213184954569877</v>
       </c>
       <c r="C44">
-        <v>50745.86550700679</v>
+        <v>60577.59475390552</v>
       </c>
       <c r="D44">
-        <v>138219.7540047782</v>
+        <v>148051.4832516769</v>
       </c>
       <c r="E44">
         <v>87769.99683641089</v>
@@ -4901,37 +4901,37 @@
         <v>10954.1</v>
       </c>
       <c r="M44">
-        <v>13106.20957001147</v>
+        <v>11928.11571148888</v>
       </c>
       <c r="N44">
-        <v>-2152.109570011473</v>
+        <v>-974.0157114888843</v>
       </c>
       <c r="O44">
-        <v>-269.0136962514341</v>
+        <v>-121.7519639361105</v>
       </c>
       <c r="P44">
-        <v>-1883.095873760039</v>
+        <v>-852.2637475527738</v>
       </c>
       <c r="Q44">
-        <v>-738.0958737600388</v>
+        <v>292.7362524472262</v>
       </c>
       <c r="R44">
         <v>0.7241379310344827</v>
       </c>
       <c r="S44">
-        <v>0.1297599407481382</v>
+        <v>0.1293403455742537</v>
       </c>
       <c r="T44">
-        <v>1.635771241514519</v>
+        <v>1.628356828805653</v>
       </c>
       <c r="U44">
-        <v>0.1368366166625341</v>
+        <v>0.1245366166625341</v>
       </c>
       <c r="V44">
-        <v>0.1044743327722327</v>
+        <v>0.1147928585804343</v>
       </c>
       <c r="W44">
-        <v>0.1225407024379061</v>
+        <v>0.1102407024379061</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4939,7 +4939,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.8357946621778619</v>
+        <v>0.9183428686434745</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4950,13 +4950,13 @@
         <v>0.43</v>
       </c>
       <c r="B45">
-        <v>0.127638226824466</v>
+        <v>0.1221058616236131</v>
       </c>
       <c r="C45">
-        <v>46927.8368783199</v>
+        <v>56769.4415874619</v>
       </c>
       <c r="D45">
-        <v>136682.2012927049</v>
+        <v>146523.8060018469</v>
       </c>
       <c r="E45">
         <v>90050.4727530245</v>
@@ -4983,37 +4983,37 @@
         <v>10954.1</v>
       </c>
       <c r="M45">
-        <v>13418.26217882127</v>
+        <v>12212.11846652433</v>
       </c>
       <c r="N45">
-        <v>-2464.162178821271</v>
+        <v>-1258.018466524334</v>
       </c>
       <c r="O45">
-        <v>-308.0202723526588</v>
+        <v>-157.2523083155418</v>
       </c>
       <c r="P45">
-        <v>-2156.141906468612</v>
+        <v>-1100.766158208792</v>
       </c>
       <c r="Q45">
-        <v>-1011.141906468612</v>
+        <v>44.23384179120762</v>
       </c>
       <c r="R45">
         <v>0.7543859649122806</v>
       </c>
       <c r="S45">
-        <v>0.1312329221647722</v>
+        <v>0.1308059656720477</v>
       </c>
       <c r="T45">
-        <v>1.664468982593721</v>
+        <v>1.65692449246891</v>
       </c>
       <c r="U45">
-        <v>0.1368366166625341</v>
+        <v>0.1245366166625341</v>
       </c>
       <c r="V45">
-        <v>0.1020446971263669</v>
+        <v>0.1121232572180986</v>
       </c>
       <c r="W45">
-        <v>0.122873165559409</v>
+        <v>0.110573165559409</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5021,7 +5021,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.8163575770109348</v>
+        <v>0.8969860577447889</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5032,13 +5032,13 @@
         <v>0.44</v>
       </c>
       <c r="B46">
-        <v>0.1667602831355959</v>
+        <v>0.1228932277902384</v>
       </c>
       <c r="C46">
-        <v>440.3813061766996</v>
+        <v>52992.49327297528</v>
       </c>
       <c r="D46">
-        <v>92475.22163717533</v>
+        <v>145027.3336039739</v>
       </c>
       <c r="E46">
         <v>92330.94866963812</v>
@@ -5065,45 +5065,45 @@
         <v>10954.1</v>
       </c>
       <c r="M46">
-        <v>22249.26062173285</v>
+        <v>12496.12122155978</v>
       </c>
       <c r="N46">
-        <v>-11295.16062173286</v>
+        <v>-1542.021221559786</v>
       </c>
       <c r="O46">
-        <v>-1411.895077716607</v>
+        <v>-192.7526526949732</v>
       </c>
       <c r="P46">
-        <v>-9883.265544016249</v>
+        <v>-1349.268568864813</v>
       </c>
       <c r="Q46">
-        <v>-8738.265544016249</v>
+        <v>-204.2685688648126</v>
       </c>
       <c r="R46">
         <v>0.7857142857142857</v>
       </c>
       <c r="S46">
-        <v>0.1342865281757583</v>
+        <v>0.1323239293447628</v>
       </c>
       <c r="T46">
-        <v>1.723961650777837</v>
+        <v>1.686512429834426</v>
       </c>
       <c r="U46">
-        <v>0.2217366166625341</v>
+        <v>0.1245366166625341</v>
       </c>
       <c r="V46">
-        <v>0.0615419327086545</v>
+        <v>0.1095750013722327</v>
       </c>
       <c r="W46">
-        <v>0.2080905167208437</v>
+        <v>0.1108905167208437</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y46">
-        <v>0.492335461669236</v>
+        <v>0.8766000109778618</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5114,13 +5114,13 @@
         <v>0.45</v>
       </c>
       <c r="B47">
-        <v>0.1685196493022212</v>
+        <v>0.1236805939568637</v>
       </c>
       <c r="C47">
-        <v>-3165.862546743112</v>
+        <v>49245.8033752651</v>
       </c>
       <c r="D47">
-        <v>91149.45370086913</v>
+        <v>143561.1196228773</v>
       </c>
       <c r="E47">
         <v>94611.42458625173</v>
@@ -5147,45 +5147,45 @@
         <v>10954.1</v>
       </c>
       <c r="M47">
-        <v>22754.92563586315</v>
+        <v>12780.12397659523</v>
       </c>
       <c r="N47">
-        <v>-11800.82563586315</v>
+        <v>-1826.023976595236</v>
       </c>
       <c r="O47">
-        <v>-1475.103204482893</v>
+        <v>-228.2529970744044</v>
       </c>
       <c r="P47">
-        <v>-10325.72243138025</v>
+        <v>-1597.770979520831</v>
       </c>
       <c r="Q47">
-        <v>-9180.722431380254</v>
+        <v>-452.7709795208311</v>
       </c>
       <c r="R47">
         <v>0.8181818181818181</v>
       </c>
       <c r="S47">
-        <v>0.1358953741425903</v>
+        <v>0.1338970916964858</v>
       </c>
       <c r="T47">
-        <v>1.755306408064707</v>
+        <v>1.717176292195052</v>
       </c>
       <c r="U47">
-        <v>0.2217366166625341</v>
+        <v>0.1245366166625341</v>
       </c>
       <c r="V47">
-        <v>0.06017433420401774</v>
+        <v>0.1071400013417387</v>
       </c>
       <c r="W47">
-        <v>0.2083937633862146</v>
+        <v>0.1111937633862146</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y47">
-        <v>0.4813946736321419</v>
+        <v>0.8571200107339093</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5196,13 +5196,13 @@
         <v>0.46</v>
       </c>
       <c r="B48">
-        <v>0.1702790154688466</v>
+        <v>0.1244679601234891</v>
       </c>
       <c r="C48">
-        <v>-6734.630022730649</v>
+        <v>45528.46334959783</v>
       </c>
       <c r="D48">
-        <v>89861.1621414952</v>
+        <v>142124.2555138237</v>
       </c>
       <c r="E48">
         <v>96891.90050286533</v>
@@ -5229,45 +5229,45 @@
         <v>10954.1</v>
       </c>
       <c r="M48">
-        <v>23260.59064999344</v>
+        <v>13064.12673163068</v>
       </c>
       <c r="N48">
-        <v>-12306.49064999344</v>
+        <v>-2110.026731630685</v>
       </c>
       <c r="O48">
-        <v>-1538.31133124918</v>
+        <v>-263.7533414538357</v>
       </c>
       <c r="P48">
-        <v>-10768.17931874426</v>
+        <v>-1846.27339017685</v>
       </c>
       <c r="Q48">
-        <v>-9623.17931874426</v>
+        <v>-701.2733901768497</v>
       </c>
       <c r="R48">
         <v>0.8518518518518519</v>
       </c>
       <c r="S48">
-        <v>0.1375638069970827</v>
+        <v>0.1355285193204947</v>
       </c>
       <c r="T48">
-        <v>1.787812082288127</v>
+        <v>1.748975853161627</v>
       </c>
       <c r="U48">
-        <v>0.2217366166625341</v>
+        <v>0.1245366166625341</v>
       </c>
       <c r="V48">
-        <v>0.05886619650393039</v>
+        <v>0.1048108708777878</v>
       </c>
       <c r="W48">
-        <v>0.2086838254139607</v>
+        <v>0.1114838254139607</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y48">
-        <v>0.4709295720314431</v>
+        <v>0.8384869670223025</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5278,13 +5278,13 @@
         <v>0.47</v>
       </c>
       <c r="B49">
-        <v>0.1720383816354719</v>
+        <v>0.1252553262901144</v>
       </c>
       <c r="C49">
-        <v>-10267.48803040994</v>
+        <v>41839.60066430108</v>
       </c>
       <c r="D49">
-        <v>88608.78005042952</v>
+        <v>140715.8687451405</v>
       </c>
       <c r="E49">
         <v>99172.37641947894</v>
@@ -5311,45 +5311,45 @@
         <v>10954.1</v>
       </c>
       <c r="M49">
-        <v>23766.25566412373</v>
+        <v>13348.12948666613</v>
       </c>
       <c r="N49">
-        <v>-12812.15566412373</v>
+        <v>-2394.029486666135</v>
       </c>
       <c r="O49">
-        <v>-1601.519458015467</v>
+        <v>-299.2536858332669</v>
       </c>
       <c r="P49">
-        <v>-11210.63620610827</v>
+        <v>-2094.775800832868</v>
       </c>
       <c r="Q49">
-        <v>-10065.63620610827</v>
+        <v>-949.7758008328683</v>
       </c>
       <c r="R49">
         <v>0.8867924528301887</v>
       </c>
       <c r="S49">
-        <v>0.1392951995819333</v>
+        <v>0.1372215102510701</v>
       </c>
       <c r="T49">
-        <v>1.821544385727526</v>
+        <v>1.781975397560904</v>
       </c>
       <c r="U49">
-        <v>0.2217366166625341</v>
+        <v>0.1245366166625341</v>
       </c>
       <c r="V49">
-        <v>0.05761372423788932</v>
+        <v>0.1025808523484732</v>
       </c>
       <c r="W49">
-        <v>0.2089615443766963</v>
+        <v>0.1117615443766963</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y49">
-        <v>0.4609097939031146</v>
+        <v>0.8206468187877854</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5360,13 +5360,13 @@
         <v>0.48</v>
       </c>
       <c r="B50">
-        <v>0.1737977478020973</v>
+        <v>0.1260426924567398</v>
       </c>
       <c r="C50">
-        <v>-13765.91732795107</v>
+        <v>38178.37703390722</v>
       </c>
       <c r="D50">
-        <v>87390.82666950197</v>
+        <v>139335.1210313603</v>
       </c>
       <c r="E50">
         <v>101452.8523360925</v>
@@ -5393,45 +5393,45 @@
         <v>10954.1</v>
       </c>
       <c r="M50">
-        <v>24271.92067825402</v>
+        <v>13632.13224170158</v>
       </c>
       <c r="N50">
-        <v>-13317.82067825402</v>
+        <v>-2678.032241701583</v>
       </c>
       <c r="O50">
-        <v>-1664.727584781753</v>
+        <v>-334.7540302126979</v>
       </c>
       <c r="P50">
-        <v>-11653.09309347227</v>
+        <v>-2343.278211488885</v>
       </c>
       <c r="Q50">
-        <v>-10508.09309347227</v>
+        <v>-1198.278211488885</v>
       </c>
       <c r="R50">
         <v>0.923076923076923</v>
       </c>
       <c r="S50">
-        <v>0.1410931841892782</v>
+        <v>0.1389796162174368</v>
       </c>
       <c r="T50">
-        <v>1.856574085453055</v>
+        <v>1.816244155206305</v>
       </c>
       <c r="U50">
-        <v>0.2217366166625341</v>
+        <v>0.1245366166625341</v>
       </c>
       <c r="V50">
-        <v>0.05641343831626663</v>
+        <v>0.10044375125788</v>
       </c>
       <c r="W50">
-        <v>0.2092276917159846</v>
+        <v>0.1120276917159846</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y50">
-        <v>0.4513075065301331</v>
+        <v>0.8035500100630401</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5442,13 +5442,13 @@
         <v>0.49</v>
       </c>
       <c r="B51">
-        <v>0.1755571139687226</v>
+        <v>0.1680839535647544</v>
       </c>
       <c r="C51">
-        <v>-17231.31836360518</v>
+        <v>-12005.55664664165</v>
       </c>
       <c r="D51">
-        <v>86205.90155046147</v>
+        <v>91431.663267425</v>
       </c>
       <c r="E51">
         <v>103733.3282527061</v>
@@ -5475,37 +5475,37 @@
         <v>10954.1</v>
       </c>
       <c r="M51">
-        <v>24777.58569238431</v>
+        <v>23101.43589367331</v>
       </c>
       <c r="N51">
-        <v>-13823.48569238431</v>
+        <v>-12147.33589367331</v>
       </c>
       <c r="O51">
-        <v>-1727.935711548039</v>
+        <v>-1518.416986709164</v>
       </c>
       <c r="P51">
-        <v>-12095.54998083627</v>
+        <v>-10628.91890696415</v>
       </c>
       <c r="Q51">
-        <v>-10950.54998083627</v>
+        <v>-9483.918906964149</v>
       </c>
       <c r="R51">
         <v>0.9607843137254901</v>
       </c>
       <c r="S51">
-        <v>0.1429616779969111</v>
+        <v>0.1427201870087381</v>
       </c>
       <c r="T51">
-        <v>1.892977498893311</v>
+        <v>1.889154842249519</v>
       </c>
       <c r="U51">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V51">
-        <v>0.05526214365675099</v>
+        <v>0.05927174857451149</v>
       </c>
       <c r="W51">
-        <v>0.2094829758985672</v>
+        <v>0.1944829758985672</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5513,7 +5513,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.4420971492540079</v>
+        <v>0.4741739885960919</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5524,13 +5524,13 @@
         <v>0.5</v>
       </c>
       <c r="B52">
-        <v>0.177316480135348</v>
+        <v>0.1696933197313797</v>
       </c>
       <c r="C52">
-        <v>-20665.01664744782</v>
+        <v>-15473.72392336986</v>
       </c>
       <c r="D52">
-        <v>85052.67918323244</v>
+        <v>90243.97190731039</v>
       </c>
       <c r="E52">
         <v>106013.8041693197</v>
@@ -5557,37 +5557,37 @@
         <v>10954.1</v>
       </c>
       <c r="M52">
-        <v>25283.25070651461</v>
+        <v>23572.8937690544</v>
       </c>
       <c r="N52">
-        <v>-14329.15070651461</v>
+        <v>-12618.7937690544</v>
       </c>
       <c r="O52">
-        <v>-1791.143838314326</v>
+        <v>-1577.3492211318</v>
       </c>
       <c r="P52">
-        <v>-12538.00686820028</v>
+        <v>-11041.4445479226</v>
       </c>
       <c r="Q52">
-        <v>-11393.00686820028</v>
+        <v>-9896.444547922598</v>
       </c>
       <c r="R52">
         <v>1</v>
       </c>
       <c r="S52">
-        <v>0.1449049115568493</v>
+        <v>0.1446585907489128</v>
       </c>
       <c r="T52">
-        <v>1.930837048871177</v>
+        <v>1.926937939094509</v>
       </c>
       <c r="U52">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V52">
-        <v>0.05415690078361596</v>
+        <v>0.05808631360302127</v>
       </c>
       <c r="W52">
-        <v>0.2097280487138465</v>
+        <v>0.1947280487138466</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.4332552062689278</v>
+        <v>0.4646905088241702</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5606,13 +5606,13 @@
         <v>0.51</v>
       </c>
       <c r="B53">
-        <v>0.1790758463019733</v>
+        <v>0.171302685898005</v>
       </c>
       <c r="C53">
-        <v>-24068.26769764994</v>
+        <v>-18911.43081149863</v>
       </c>
       <c r="D53">
-        <v>83929.90404964393</v>
+        <v>89086.74093579523</v>
       </c>
       <c r="E53">
         <v>108294.2800859334</v>
@@ -5639,37 +5639,37 @@
         <v>10954.1</v>
       </c>
       <c r="M53">
-        <v>25788.9157206449</v>
+        <v>24044.35164443549</v>
       </c>
       <c r="N53">
-        <v>-14834.8157206449</v>
+        <v>-13090.25164443549</v>
       </c>
       <c r="O53">
-        <v>-1854.351965080612</v>
+        <v>-1636.281455554436</v>
       </c>
       <c r="P53">
-        <v>-12980.46375556429</v>
+        <v>-11453.97018888105</v>
       </c>
       <c r="Q53">
-        <v>-11835.46375556429</v>
+        <v>-10308.97018888105</v>
       </c>
       <c r="R53">
         <v>1.040816326530612</v>
       </c>
       <c r="S53">
-        <v>0.1469274607722953</v>
+        <v>0.1466761130090947</v>
       </c>
       <c r="T53">
-        <v>1.970241886603242</v>
+        <v>1.966263203157662</v>
       </c>
       <c r="U53">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V53">
-        <v>0.05309500076825095</v>
+        <v>0.05694736627747183</v>
       </c>
       <c r="W53">
-        <v>0.2099635108304875</v>
+        <v>0.1949635108304875</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5677,7 +5677,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.4247600061460076</v>
+        <v>0.4555789302197747</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5688,13 +5688,13 @@
         <v>0.52</v>
       </c>
       <c r="B54">
-        <v>0.1808352124685986</v>
+        <v>0.1729120520646304</v>
       </c>
       <c r="C54">
-        <v>-27442.2616000807</v>
+        <v>-22319.83428830998</v>
       </c>
       <c r="D54">
-        <v>82836.38606382677</v>
+        <v>87958.81337559748</v>
       </c>
       <c r="E54">
         <v>110574.756002547</v>
@@ -5721,37 +5721,37 @@
         <v>10954.1</v>
       </c>
       <c r="M54">
-        <v>26294.58073477519</v>
+        <v>24515.80951981658</v>
       </c>
       <c r="N54">
-        <v>-15340.48073477519</v>
+        <v>-13561.70951981658</v>
       </c>
       <c r="O54">
-        <v>-1917.560091846899</v>
+        <v>-1695.213689977072</v>
       </c>
       <c r="P54">
-        <v>-13422.92064292829</v>
+        <v>-11866.4958298395</v>
       </c>
       <c r="Q54">
-        <v>-12277.92064292829</v>
+        <v>-10721.4958298395</v>
       </c>
       <c r="R54">
         <v>1.083333333333333</v>
       </c>
       <c r="S54">
-        <v>0.1490342828717181</v>
+        <v>0.1487776986967842</v>
       </c>
       <c r="T54">
-        <v>2.011288592574143</v>
+        <v>2.007227019890114</v>
       </c>
       <c r="U54">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V54">
-        <v>0.05207394306116921</v>
+        <v>0.05585222461828968</v>
       </c>
       <c r="W54">
-        <v>0.210189916711873</v>
+        <v>0.195189916711873</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5759,7 +5759,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.4165915444893536</v>
+        <v>0.4468177969463174</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5770,13 +5770,13 @@
         <v>0.53</v>
       </c>
       <c r="B55">
-        <v>0.182594578635224</v>
+        <v>0.1745214182312557</v>
       </c>
       <c r="C55">
-        <v>-30788.12721605397</v>
+        <v>-25700.03346969436</v>
       </c>
       <c r="D55">
-        <v>81770.99636446711</v>
+        <v>86859.09011082671</v>
       </c>
       <c r="E55">
         <v>112855.2319191606</v>
@@ -5803,37 +5803,37 @@
         <v>10954.1</v>
       </c>
       <c r="M55">
-        <v>26800.24574890548</v>
+        <v>24987.26739519766</v>
       </c>
       <c r="N55">
-        <v>-15846.14574890548</v>
+        <v>-14033.16739519767</v>
       </c>
       <c r="O55">
-        <v>-1980.768218613185</v>
+        <v>-1754.145924399708</v>
       </c>
       <c r="P55">
-        <v>-13865.37753029229</v>
+        <v>-12279.02147079796</v>
       </c>
       <c r="Q55">
-        <v>-12720.37753029229</v>
+        <v>-11134.02147079796</v>
       </c>
       <c r="R55">
         <v>1.127659574468085</v>
       </c>
       <c r="S55">
-        <v>0.1512307569753716</v>
+        <v>0.1509687135626732</v>
       </c>
       <c r="T55">
-        <v>2.054081966884231</v>
+        <v>2.049933977760116</v>
       </c>
       <c r="U55">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V55">
-        <v>0.05109141583359997</v>
+        <v>0.05479840905945402</v>
       </c>
       <c r="W55">
-        <v>0.210407778975093</v>
+        <v>0.195407778975093</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5841,7 +5841,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.4087313266687997</v>
+        <v>0.4383872724756321</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5852,13 +5852,13 @@
         <v>0.54</v>
       </c>
       <c r="B56">
-        <v>0.1843539448018493</v>
+        <v>0.176130784397881</v>
       </c>
       <c r="C56">
-        <v>-34106.93606949324</v>
+        <v>-29053.07318260548</v>
       </c>
       <c r="D56">
-        <v>80732.66342764144</v>
+        <v>85786.5263145292</v>
       </c>
       <c r="E56">
         <v>115135.7078357742</v>
@@ -5885,37 +5885,37 @@
         <v>10954.1</v>
       </c>
       <c r="M56">
-        <v>27305.91076303577</v>
+        <v>25458.72527057875</v>
       </c>
       <c r="N56">
-        <v>-16351.81076303577</v>
+        <v>-14504.62527057875</v>
       </c>
       <c r="O56">
-        <v>-2043.976345379472</v>
+        <v>-1813.078158822344</v>
       </c>
       <c r="P56">
-        <v>-14307.8344176563</v>
+        <v>-12691.54711175641</v>
       </c>
       <c r="Q56">
-        <v>-13162.8344176563</v>
+        <v>-11546.54711175641</v>
       </c>
       <c r="R56">
         <v>1.173913043478261</v>
       </c>
       <c r="S56">
-        <v>0.1535227299530971</v>
+        <v>0.1532549899444705</v>
       </c>
       <c r="T56">
-        <v>2.098735922686062</v>
+        <v>2.094497759885336</v>
       </c>
       <c r="U56">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V56">
-        <v>0.05014527850334812</v>
+        <v>0.05378362370650117</v>
       </c>
       <c r="W56">
-        <v>0.2106175722656012</v>
+        <v>0.1956175722656012</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5923,7 +5923,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.401162228026785</v>
+        <v>0.4302689896520094</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5934,13 +5934,13 @@
         <v>0.55</v>
       </c>
       <c r="B57">
-        <v>0.1861133109684747</v>
+        <v>0.1777401505645064</v>
       </c>
       <c r="C57">
-        <v>-37399.70594165364</v>
+        <v>-32379.94727606078</v>
       </c>
       <c r="D57">
-        <v>79720.36947209465</v>
+        <v>84740.12813768751</v>
       </c>
       <c r="E57">
         <v>117416.1837523878</v>
@@ -5967,37 +5967,37 @@
         <v>10954.1</v>
       </c>
       <c r="M57">
-        <v>27811.57577716606</v>
+        <v>25930.18314595984</v>
       </c>
       <c r="N57">
-        <v>-16857.47577716607</v>
+        <v>-14976.08314595984</v>
       </c>
       <c r="O57">
-        <v>-2107.184472145758</v>
+        <v>-1872.01039324498</v>
       </c>
       <c r="P57">
-        <v>-14750.29130502031</v>
+        <v>-13104.07275271486</v>
       </c>
       <c r="Q57">
-        <v>-13605.29130502031</v>
+        <v>-11959.07275271486</v>
       </c>
       <c r="R57">
         <v>1.222222222222223</v>
       </c>
       <c r="S57">
-        <v>0.1559165683964993</v>
+        <v>0.1556428786099032</v>
       </c>
       <c r="T57">
-        <v>2.145374498745753</v>
+        <v>2.141042154549455</v>
       </c>
       <c r="U57">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V57">
-        <v>0.04923354616692361</v>
+        <v>0.05280573963911024</v>
       </c>
       <c r="W57">
-        <v>0.2108197367091818</v>
+        <v>0.1958197367091818</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -6005,7 +6005,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.3938683693353888</v>
+        <v>0.4224459171128819</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6016,13 +6016,13 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1878726771351</v>
+        <v>0.1793495167311318</v>
       </c>
       <c r="C58">
-        <v>-40667.40419875077</v>
+        <v>-35681.6016927423</v>
       </c>
       <c r="D58">
-        <v>78733.14713161113</v>
+        <v>83718.94963761959</v>
       </c>
       <c r="E58">
         <v>119696.6596690014</v>
@@ -6049,37 +6049,37 @@
         <v>10954.1</v>
       </c>
       <c r="M58">
-        <v>28317.24079129636</v>
+        <v>26401.64102134093</v>
       </c>
       <c r="N58">
-        <v>-17363.14079129636</v>
+        <v>-15447.54102134093</v>
       </c>
       <c r="O58">
-        <v>-2170.392598912045</v>
+        <v>-1930.942627667616</v>
       </c>
       <c r="P58">
-        <v>-15192.74819238431</v>
+        <v>-13516.59839367331</v>
       </c>
       <c r="Q58">
-        <v>-14047.74819238431</v>
+        <v>-12371.59839367331</v>
       </c>
       <c r="R58">
         <v>1.272727272727273</v>
       </c>
       <c r="S58">
-        <v>0.1584192176782379</v>
+        <v>0.1581393076692191</v>
       </c>
       <c r="T58">
-        <v>2.194133010080883</v>
+        <v>2.189702203516488</v>
       </c>
       <c r="U58">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V58">
-        <v>0.04835437569965712</v>
+        <v>0.05186278000269755</v>
       </c>
       <c r="W58">
-        <v>0.2110146809940631</v>
+        <v>0.1960146809940631</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6087,7 +6087,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.3868350055972569</v>
+        <v>0.4149022400215805</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6098,13 +6098,13 @@
         <v>0.5700000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1896320433017253</v>
+        <v>0.1809588828977571</v>
       </c>
       <c r="C59">
-        <v>-43910.95087536678</v>
+        <v>-38958.93732115241</v>
       </c>
       <c r="D59">
-        <v>77770.07637160872</v>
+        <v>82722.08992582309</v>
       </c>
       <c r="E59">
         <v>121977.135585615</v>
@@ -6131,37 +6131,37 @@
         <v>10954.1</v>
       </c>
       <c r="M59">
-        <v>28822.90580542665</v>
+        <v>26873.09889672201</v>
       </c>
       <c r="N59">
-        <v>-17868.80580542665</v>
+        <v>-15918.99889672202</v>
       </c>
       <c r="O59">
-        <v>-2233.600725678331</v>
+        <v>-1989.874862090252</v>
       </c>
       <c r="P59">
-        <v>-15635.20507974832</v>
+        <v>-13929.12403463176</v>
       </c>
       <c r="Q59">
-        <v>-14490.20507974832</v>
+        <v>-12784.12403463176</v>
       </c>
       <c r="R59">
         <v>1.325581395348838</v>
       </c>
       <c r="S59">
-        <v>0.1610382692521504</v>
+        <v>0.1607518497080382</v>
       </c>
       <c r="T59">
-        <v>2.245159359152532</v>
+        <v>2.240625510575011</v>
       </c>
       <c r="U59">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V59">
-        <v>0.04750605331896138</v>
+        <v>0.0509529066693169</v>
       </c>
       <c r="W59">
-        <v>0.2112027851285977</v>
+        <v>0.1962027851285977</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6169,7 +6169,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.380048426551691</v>
+        <v>0.4076232533545352</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6180,13 +6180,13 @@
         <v>0.58</v>
       </c>
       <c r="B60">
-        <v>0.1913914094683507</v>
+        <v>0.1825682490643824</v>
       </c>
       <c r="C60">
-        <v>-47131.22153429188</v>
+        <v>-42212.81264639985</v>
       </c>
       <c r="D60">
-        <v>76830.2816292972</v>
+        <v>81748.69051718923</v>
       </c>
       <c r="E60">
         <v>124257.6115022286</v>
@@ -6213,37 +6213,37 @@
         <v>10954.1</v>
       </c>
       <c r="M60">
-        <v>29328.57081955694</v>
+        <v>27344.5567721031</v>
       </c>
       <c r="N60">
-        <v>-18374.47081955694</v>
+        <v>-16390.4567721031</v>
       </c>
       <c r="O60">
-        <v>-2296.808852444617</v>
+        <v>-2048.807096512887</v>
       </c>
       <c r="P60">
-        <v>-16077.66196711232</v>
+        <v>-14341.64967559021</v>
       </c>
       <c r="Q60">
-        <v>-14932.66196711232</v>
+        <v>-13196.64967559021</v>
       </c>
       <c r="R60">
         <v>1.380952380952381</v>
       </c>
       <c r="S60">
-        <v>0.1637820375676778</v>
+        <v>0.1634887985106105</v>
       </c>
       <c r="T60">
-        <v>2.298615534370449</v>
+        <v>2.293973737017272</v>
       </c>
       <c r="U60">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V60">
-        <v>0.04668698343415171</v>
+        <v>0.05007440827846662</v>
       </c>
       <c r="W60">
-        <v>0.2113844029136655</v>
+        <v>0.1963844029136655</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6251,7 +6251,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.3734958674732136</v>
+        <v>0.400595266227733</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6262,13 +6262,13 @@
         <v>0.59</v>
       </c>
       <c r="B61">
-        <v>0.193150775634976</v>
+        <v>0.1841776152310077</v>
       </c>
       <c r="C61">
-        <v>-50329.04992148724</v>
+        <v>-45444.04621600997</v>
       </c>
       <c r="D61">
-        <v>75912.92915871546</v>
+        <v>80797.93286419273</v>
       </c>
       <c r="E61">
         <v>126538.0874188422</v>
@@ -6295,37 +6295,37 @@
         <v>10954.1</v>
       </c>
       <c r="M61">
-        <v>29834.23583368723</v>
+        <v>27816.01464748419</v>
       </c>
       <c r="N61">
-        <v>-18880.13583368723</v>
+        <v>-16861.91464748419</v>
       </c>
       <c r="O61">
-        <v>-2360.016979210904</v>
+        <v>-2107.739330935524</v>
       </c>
       <c r="P61">
-        <v>-16520.11885447633</v>
+        <v>-14754.17531654867</v>
       </c>
       <c r="Q61">
-        <v>-15375.11885447633</v>
+        <v>-13609.17531654867</v>
       </c>
       <c r="R61">
         <v>1.439024390243902</v>
       </c>
       <c r="S61">
-        <v>0.1666596482400602</v>
+        <v>0.1663592570108693</v>
       </c>
       <c r="T61">
-        <v>2.354679327891679</v>
+        <v>2.349924315968913</v>
       </c>
       <c r="U61">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V61">
-        <v>0.04589567863018303</v>
+        <v>0.04922568949408582</v>
       </c>
       <c r="W61">
-        <v>0.2115598641636464</v>
+        <v>0.1965598641636463</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6333,7 +6333,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.3671654290414642</v>
+        <v>0.3938055159526865</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6344,13 +6344,13 @@
         <v>0.6</v>
       </c>
       <c r="B62">
-        <v>0.1949101418016014</v>
+        <v>0.1857869813976331</v>
       </c>
       <c r="C62">
-        <v>-53505.23043309059</v>
+        <v>-48653.41893564514</v>
       </c>
       <c r="D62">
-        <v>75017.2245637257</v>
+        <v>79869.03606117115</v>
       </c>
       <c r="E62">
         <v>128818.5633354558</v>
@@ -6377,37 +6377,37 @@
         <v>10954.1</v>
       </c>
       <c r="M62">
-        <v>30339.90084781752</v>
+        <v>28287.47252286528</v>
       </c>
       <c r="N62">
-        <v>-19385.80084781752</v>
+        <v>-17333.37252286528</v>
       </c>
       <c r="O62">
-        <v>-2423.22510597719</v>
+        <v>-2166.67156535816</v>
       </c>
       <c r="P62">
-        <v>-16962.57574184033</v>
+        <v>-15166.70095750712</v>
       </c>
       <c r="Q62">
-        <v>-15817.57574184033</v>
+        <v>-14021.70095750712</v>
       </c>
       <c r="R62">
         <v>1.5</v>
       </c>
       <c r="S62">
-        <v>0.1696811394460617</v>
+        <v>0.169373238436141</v>
       </c>
       <c r="T62">
-        <v>2.413546311088972</v>
+        <v>2.408672423868136</v>
       </c>
       <c r="U62">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V62">
-        <v>0.04513075065301331</v>
+        <v>0.04840526133585106</v>
       </c>
       <c r="W62">
-        <v>0.2117294767052945</v>
+        <v>0.1967294767052945</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6415,7 +6415,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.3610460052241066</v>
+        <v>0.3872420906868085</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6426,13 +6426,13 @@
         <v>0.61</v>
       </c>
       <c r="B63">
-        <v>0.1966695079682267</v>
+        <v>0.1873963475642584</v>
       </c>
       <c r="C63">
-        <v>-56660.52040980809</v>
+        <v>-51841.67620826791</v>
       </c>
       <c r="D63">
-        <v>74142.41050362182</v>
+        <v>78961.25470516201</v>
       </c>
       <c r="E63">
         <v>131099.0392520694</v>
@@ -6459,37 +6459,37 @@
         <v>10954.1</v>
       </c>
       <c r="M63">
-        <v>30845.56586194782</v>
+        <v>28758.93039824636</v>
       </c>
       <c r="N63">
-        <v>-19891.46586194782</v>
+        <v>-17804.83039824637</v>
       </c>
       <c r="O63">
-        <v>-2486.433232743477</v>
+        <v>-2225.603799780796</v>
       </c>
       <c r="P63">
-        <v>-17405.03262920434</v>
+        <v>-15579.22659846557</v>
       </c>
       <c r="Q63">
-        <v>-16260.03262920434</v>
+        <v>-14434.22659846557</v>
       </c>
       <c r="R63">
         <v>1.564102564102564</v>
       </c>
       <c r="S63">
-        <v>0.1728575789190376</v>
+        <v>0.1725417830114267</v>
       </c>
       <c r="T63">
-        <v>2.475432113937407</v>
+        <v>2.47043325524937</v>
       </c>
       <c r="U63">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V63">
-        <v>0.04439090228165243</v>
+        <v>0.04761173246149285</v>
       </c>
       <c r="W63">
-        <v>0.2118935281800033</v>
+        <v>0.1968935281800033</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6497,7 +6497,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.3551272182532195</v>
+        <v>0.3808938596919428</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6508,13 +6508,13 @@
         <v>0.62</v>
       </c>
       <c r="B64">
-        <v>0.1984288741348521</v>
+        <v>0.1890057137308838</v>
       </c>
       <c r="C64">
-        <v>-59795.64227261969</v>
+        <v>-55009.52992906312</v>
       </c>
       <c r="D64">
-        <v>73287.76455742381</v>
+        <v>78073.87690098038</v>
       </c>
       <c r="E64">
         <v>133379.515168683</v>
@@ -6541,37 +6541,37 @@
         <v>10954.1</v>
       </c>
       <c r="M64">
-        <v>31351.23087607811</v>
+        <v>29230.38827362745</v>
       </c>
       <c r="N64">
-        <v>-20397.13087607811</v>
+        <v>-18276.28827362745</v>
       </c>
       <c r="O64">
-        <v>-2549.641359509763</v>
+        <v>-2284.536034203431</v>
       </c>
       <c r="P64">
-        <v>-17847.48951656834</v>
+        <v>-15991.75223942402</v>
       </c>
       <c r="Q64">
-        <v>-16702.48951656834</v>
+        <v>-14846.75223942402</v>
       </c>
       <c r="R64">
         <v>1.631578947368421</v>
       </c>
       <c r="S64">
-        <v>0.1762011994169071</v>
+        <v>0.1758770930906748</v>
       </c>
       <c r="T64">
-        <v>2.540575064304181</v>
+        <v>2.535444656703302</v>
       </c>
       <c r="U64">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V64">
-        <v>0.04367491998678708</v>
+        <v>0.04684380129275909</v>
       </c>
       <c r="W64">
-        <v>0.212052287671657</v>
+        <v>0.197052287671657</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6579,7 +6579,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.3493993598942966</v>
+        <v>0.3747504103420728</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6590,13 +6590,13 @@
         <v>0.63</v>
       </c>
       <c r="B65">
-        <v>0.2001882403014774</v>
+        <v>0.1906150798975091</v>
       </c>
       <c r="C65">
-        <v>-62911.28551245786</v>
+        <v>-58157.66034733941</v>
       </c>
       <c r="D65">
-        <v>72452.59723419926</v>
+        <v>77206.22239931772</v>
       </c>
       <c r="E65">
         <v>135659.9910852966</v>
@@ -6623,37 +6623,37 @@
         <v>10954.1</v>
       </c>
       <c r="M65">
-        <v>31856.8958902084</v>
+        <v>29701.84614900854</v>
       </c>
       <c r="N65">
-        <v>-20902.7958902084</v>
+        <v>-18747.74614900854</v>
       </c>
       <c r="O65">
-        <v>-2612.84948627605</v>
+        <v>-2343.468268626068</v>
       </c>
       <c r="P65">
-        <v>-18289.94640393235</v>
+        <v>-16404.27788038248</v>
       </c>
       <c r="Q65">
-        <v>-17144.94640393235</v>
+        <v>-15259.27788038248</v>
       </c>
       <c r="R65">
         <v>1.702702702702703</v>
       </c>
       <c r="S65">
-        <v>0.1797255561579045</v>
+        <v>0.1793926902012336</v>
       </c>
       <c r="T65">
-        <v>2.609239255231321</v>
+        <v>2.603970187965553</v>
       </c>
       <c r="U65">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V65">
-        <v>0.0429816672885841</v>
+        <v>0.04610024889128672</v>
       </c>
       <c r="W65">
-        <v>0.2122060071794488</v>
+        <v>0.1972060071794488</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6661,7 +6661,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.3438533383086728</v>
+        <v>0.3688019911302938</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6672,13 +6672,13 @@
         <v>0.64</v>
       </c>
       <c r="B66">
-        <v>0.2019476064681028</v>
+        <v>0.1922244460641345</v>
       </c>
       <c r="C66">
-        <v>-66008.10854537533</v>
+        <v>-61286.71780564444</v>
       </c>
       <c r="D66">
-        <v>71636.25011789541</v>
+        <v>76357.64085762631</v>
       </c>
       <c r="E66">
         <v>137940.4670019102</v>
@@ -6705,37 +6705,37 @@
         <v>10954.1</v>
       </c>
       <c r="M66">
-        <v>32362.5609043387</v>
+        <v>30173.30402438963</v>
       </c>
       <c r="N66">
-        <v>-21408.4609043387</v>
+        <v>-19219.20402438963</v>
       </c>
       <c r="O66">
-        <v>-2676.057613042337</v>
+        <v>-2402.400503048704</v>
       </c>
       <c r="P66">
-        <v>-18732.40329129636</v>
+        <v>-16816.80352134093</v>
       </c>
       <c r="Q66">
-        <v>-17587.40329129636</v>
+        <v>-15671.80352134093</v>
       </c>
       <c r="R66">
         <v>1.777777777777778</v>
       </c>
       <c r="S66">
-        <v>0.1834457104956241</v>
+        <v>0.183103598262379</v>
       </c>
       <c r="T66">
-        <v>2.681718123432191</v>
+        <v>2.676302693186818</v>
       </c>
       <c r="U66">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V66">
-        <v>0.04231007873719997</v>
+        <v>0.04537993250236037</v>
       </c>
       <c r="W66">
-        <v>0.212354922952622</v>
+        <v>0.1973549229526219</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6743,7 +6743,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.3384806298975997</v>
+        <v>0.3630394600188829</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6754,13 +6754,13 @@
         <v>0.65</v>
       </c>
       <c r="B67">
-        <v>0.2037069726347281</v>
+        <v>0.1938338122307598</v>
       </c>
       <c r="C67">
-        <v>-69086.74044369393</v>
+        <v>-64397.3243654386</v>
       </c>
       <c r="D67">
-        <v>70838.09413619041</v>
+        <v>75527.51021444573</v>
       </c>
       <c r="E67">
         <v>140220.9429185238</v>
@@ -6787,37 +6787,37 @@
         <v>10954.1</v>
       </c>
       <c r="M67">
-        <v>32868.22591846898</v>
+        <v>30644.76189977072</v>
       </c>
       <c r="N67">
-        <v>-21914.12591846898</v>
+        <v>-19690.66189977072</v>
       </c>
       <c r="O67">
-        <v>-2739.265739808623</v>
+        <v>-2461.33273747134</v>
       </c>
       <c r="P67">
-        <v>-19174.86017866036</v>
+        <v>-17229.32916229938</v>
       </c>
       <c r="Q67">
-        <v>-18029.86017866036</v>
+        <v>-16084.32916229938</v>
       </c>
       <c r="R67">
         <v>1.857142857142857</v>
       </c>
       <c r="S67">
-        <v>0.1873784450812133</v>
+        <v>0.1870265582127326</v>
       </c>
       <c r="T67">
-        <v>2.758338641244539</v>
+        <v>2.752768484420728</v>
       </c>
       <c r="U67">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V67">
-        <v>0.04165915444893536</v>
+        <v>0.04468177969463175</v>
       </c>
       <c r="W67">
-        <v>0.2124992567020052</v>
+        <v>0.1974992567020052</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6825,7 +6825,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.3332732355914829</v>
+        <v>0.357454237557054</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6836,13 +6836,13 @@
         <v>0.66</v>
       </c>
       <c r="B68">
-        <v>0.2054663388013535</v>
+        <v>0.1954431783973852</v>
       </c>
       <c r="C68">
-        <v>-72147.78255270013</v>
+        <v>-67490.07532786684</v>
       </c>
       <c r="D68">
-        <v>70057.52794379783</v>
+        <v>74715.23516863112</v>
       </c>
       <c r="E68">
         <v>142501.4188351374</v>
@@ -6869,37 +6869,37 @@
         <v>10954.1</v>
       </c>
       <c r="M68">
-        <v>33373.89093259928</v>
+        <v>31116.21977515181</v>
       </c>
       <c r="N68">
-        <v>-22419.79093259928</v>
+        <v>-20162.11977515181</v>
       </c>
       <c r="O68">
-        <v>-2802.47386657491</v>
+        <v>-2520.264971893977</v>
       </c>
       <c r="P68">
-        <v>-19617.31706602437</v>
+        <v>-17641.85480325784</v>
       </c>
       <c r="Q68">
-        <v>-18472.31706602437</v>
+        <v>-16496.85480325784</v>
       </c>
       <c r="R68">
         <v>1.941176470588236</v>
       </c>
       <c r="S68">
-        <v>0.1915425169953667</v>
+        <v>0.1911802805131071</v>
       </c>
       <c r="T68">
-        <v>2.839466248339967</v>
+        <v>2.833732263374279</v>
       </c>
       <c r="U68">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V68">
-        <v>0.041027955139103</v>
+        <v>0.04400478303259187</v>
       </c>
       <c r="W68">
-        <v>0.2126392167014072</v>
+        <v>0.1976392167014072</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.3282236411128241</v>
+        <v>0.3520382642607349</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6918,13 +6918,13 @@
         <v>0.67</v>
       </c>
       <c r="B69">
-        <v>0.2072257049679788</v>
+        <v>0.1970525445640105</v>
       </c>
       <c r="C69">
-        <v>-75191.81000161878</v>
+        <v>-70565.54065744176</v>
       </c>
       <c r="D69">
-        <v>69293.97641149277</v>
+        <v>73920.24575566979</v>
       </c>
       <c r="E69">
         <v>144781.894751751</v>
@@ -6951,37 +6951,37 @@
         <v>10954.1</v>
       </c>
       <c r="M69">
-        <v>33879.55594672957</v>
+        <v>31587.6776505329</v>
       </c>
       <c r="N69">
-        <v>-22925.45594672957</v>
+        <v>-20633.5776505329</v>
       </c>
       <c r="O69">
-        <v>-2865.681993341196</v>
+        <v>-2579.197206316612</v>
       </c>
       <c r="P69">
-        <v>-20059.77395338837</v>
+        <v>-18054.38044421629</v>
       </c>
       <c r="Q69">
-        <v>-18914.77395338837</v>
+        <v>-16909.38044421629</v>
       </c>
       <c r="R69">
         <v>2.030303030303031</v>
       </c>
       <c r="S69">
-        <v>0.1959589569043172</v>
+        <v>0.1955857435589588</v>
       </c>
       <c r="T69">
-        <v>2.925510680107845</v>
+        <v>2.919602938021983</v>
       </c>
       <c r="U69">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V69">
-        <v>0.04041559759971342</v>
+        <v>0.04334799522613527</v>
       </c>
       <c r="W69">
-        <v>0.2127749987903792</v>
+        <v>0.1977749987903792</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6989,7 +6989,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.3233247807977073</v>
+        <v>0.3467839618090822</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7000,13 +7000,13 @@
         <v>0.68</v>
       </c>
       <c r="B70">
-        <v>0.2089850711346041</v>
+        <v>0.1986619107306359</v>
       </c>
       <c r="C70">
-        <v>-78219.3731168448</v>
+        <v>-73624.2663157941</v>
       </c>
       <c r="D70">
-        <v>68546.88921288037</v>
+        <v>73141.99601393107</v>
       </c>
       <c r="E70">
         <v>147062.3706683647</v>
@@ -7033,37 +7033,37 @@
         <v>10954.1</v>
       </c>
       <c r="M70">
-        <v>34385.22096085986</v>
+        <v>32059.13552591399</v>
       </c>
       <c r="N70">
-        <v>-23431.12096085987</v>
+        <v>-21105.03552591399</v>
       </c>
       <c r="O70">
-        <v>-2928.890120107483</v>
+        <v>-2638.129440739248</v>
       </c>
       <c r="P70">
-        <v>-20502.23084075238</v>
+        <v>-18466.90608517474</v>
       </c>
       <c r="Q70">
-        <v>-19357.23084075238</v>
+        <v>-17321.90608517474</v>
       </c>
       <c r="R70">
         <v>2.125</v>
       </c>
       <c r="S70">
-        <v>0.2006514243075771</v>
+        <v>0.2002665480451764</v>
       </c>
       <c r="T70">
-        <v>3.016932888861215</v>
+        <v>3.010840529835171</v>
       </c>
       <c r="U70">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V70">
-        <v>0.03982125057618821</v>
+        <v>0.04271052470810387</v>
       </c>
       <c r="W70">
-        <v>0.2129067872884992</v>
+        <v>0.1979067872884991</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7071,7 +7071,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.3185700046095057</v>
+        <v>0.3416841976648309</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7082,13 +7082,13 @@
         <v>0.6900000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2107444373012294</v>
+        <v>0.2002712768972612</v>
       </c>
       <c r="C71">
-        <v>-81230.99874472941</v>
+        <v>-76666.77551204815</v>
       </c>
       <c r="D71">
-        <v>67815.73950160935</v>
+        <v>72379.96273429062</v>
       </c>
       <c r="E71">
         <v>149342.8465849783</v>
@@ -7115,37 +7115,37 @@
         <v>10954.1</v>
       </c>
       <c r="M71">
-        <v>34890.88597499015</v>
+        <v>32530.59340129507</v>
       </c>
       <c r="N71">
-        <v>-23936.78597499015</v>
+        <v>-21576.49340129507</v>
       </c>
       <c r="O71">
-        <v>-2992.098246873769</v>
+        <v>-2697.061675161884</v>
       </c>
       <c r="P71">
-        <v>-20944.68772811638</v>
+        <v>-18879.43172613319</v>
       </c>
       <c r="Q71">
-        <v>-19799.68772811638</v>
+        <v>-17734.43172613319</v>
       </c>
       <c r="R71">
         <v>2.225806451612904</v>
       </c>
       <c r="S71">
-        <v>0.2056466315433055</v>
+        <v>0.2052493399176014</v>
       </c>
       <c r="T71">
-        <v>3.114253304630932</v>
+        <v>3.10796441789437</v>
       </c>
       <c r="U71">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V71">
-        <v>0.03924413100262027</v>
+        <v>0.04209153159639222</v>
       </c>
       <c r="W71">
-        <v>0.2130347558301518</v>
+        <v>0.1980347558301518</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7153,7 +7153,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.3139530480209621</v>
+        <v>0.3367322527711378</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7164,13 +7164,13 @@
         <v>0.7000000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2125038034678548</v>
+        <v>0.2018806430638865</v>
       </c>
       <c r="C72">
-        <v>-84227.19149060432</v>
+        <v>-79693.56987584096</v>
       </c>
       <c r="D72">
-        <v>67100.02267234806</v>
+        <v>71633.64428711143</v>
       </c>
       <c r="E72">
         <v>151623.3225015919</v>
@@ -7197,37 +7197,37 @@
         <v>10954.1</v>
       </c>
       <c r="M72">
-        <v>35396.55098912045</v>
+        <v>33002.05127667616</v>
       </c>
       <c r="N72">
-        <v>-24442.45098912045</v>
+        <v>-22047.95127667616</v>
       </c>
       <c r="O72">
-        <v>-3055.306373640056</v>
+        <v>-2755.99390958452</v>
       </c>
       <c r="P72">
-        <v>-21387.14461548039</v>
+        <v>-19291.95736709164</v>
       </c>
       <c r="Q72">
-        <v>-20242.14461548039</v>
+        <v>-18146.95736709164</v>
       </c>
       <c r="R72">
         <v>2.333333333333334</v>
       </c>
       <c r="S72">
-        <v>0.2109748525947489</v>
+        <v>0.2105643179148547</v>
       </c>
       <c r="T72">
-        <v>3.218061748118629</v>
+        <v>3.211563231824182</v>
       </c>
       <c r="U72">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V72">
-        <v>0.03868350055972569</v>
+        <v>0.04149022400215804</v>
       </c>
       <c r="W72">
-        <v>0.2131590681277573</v>
+        <v>0.1981590681277573</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7235,7 +7235,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.3094680044778055</v>
+        <v>0.3319217920172643</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7246,13 +7246,13 @@
         <v>0.71</v>
       </c>
       <c r="B73">
-        <v>0.2142631696344801</v>
+        <v>0.2034900092305119</v>
       </c>
       <c r="C73">
-        <v>-87208.43488016563</v>
+        <v>-82705.1305585111</v>
       </c>
       <c r="D73">
-        <v>66399.25519940032</v>
+        <v>70902.55952105485</v>
       </c>
       <c r="E73">
         <v>153903.7984182054</v>
@@ -7279,37 +7279,37 @@
         <v>10954.1</v>
       </c>
       <c r="M73">
-        <v>35902.21600325073</v>
+        <v>33473.50915205724</v>
       </c>
       <c r="N73">
-        <v>-24948.11600325073</v>
+        <v>-22519.40915205724</v>
       </c>
       <c r="O73">
-        <v>-3118.514500406342</v>
+        <v>-2814.926144007155</v>
       </c>
       <c r="P73">
-        <v>-21829.60150284439</v>
+        <v>-19704.48300805008</v>
       </c>
       <c r="Q73">
-        <v>-20684.60150284439</v>
+        <v>-18559.48300805008</v>
       </c>
       <c r="R73">
         <v>2.448275862068965</v>
       </c>
       <c r="S73">
-        <v>0.2166705371669816</v>
+        <v>0.2162458461188152</v>
       </c>
       <c r="T73">
-        <v>3.329029394605478</v>
+        <v>3.322306791542257</v>
       </c>
       <c r="U73">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V73">
-        <v>0.03813866252367323</v>
+        <v>0.04090585465001498</v>
       </c>
       <c r="W73">
-        <v>0.2132798786705006</v>
+        <v>0.1982798786705006</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7317,7 +7317,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.3051093001893858</v>
+        <v>0.3272468372001199</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7328,13 +7328,13 @@
         <v>0.72</v>
       </c>
       <c r="B74">
-        <v>0.2160225358011054</v>
+        <v>0.2050993753971372</v>
       </c>
       <c r="C74">
-        <v>-90175.19244883643</v>
+        <v>-85701.91926753745</v>
       </c>
       <c r="D74">
-        <v>65712.97354734314</v>
+        <v>70186.24672864212</v>
       </c>
       <c r="E74">
         <v>156184.2743348191</v>
@@ -7361,37 +7361,37 @@
         <v>10954.1</v>
       </c>
       <c r="M74">
-        <v>36407.88101738103</v>
+        <v>33944.96702743833</v>
       </c>
       <c r="N74">
-        <v>-25453.78101738103</v>
+        <v>-22990.86702743833</v>
       </c>
       <c r="O74">
-        <v>-3181.722627172629</v>
+        <v>-2873.858378429792</v>
       </c>
       <c r="P74">
-        <v>-22272.0583902084</v>
+        <v>-20117.00864900854</v>
       </c>
       <c r="Q74">
-        <v>-21127.0583902084</v>
+        <v>-18972.00864900854</v>
       </c>
       <c r="R74">
         <v>2.571428571428571</v>
       </c>
       <c r="S74">
-        <v>0.2227730563515167</v>
+        <v>0.2223331977659158</v>
       </c>
       <c r="T74">
-        <v>3.447923301555674</v>
+        <v>3.440960605525909</v>
       </c>
       <c r="U74">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V74">
-        <v>0.0376089588775111</v>
+        <v>0.04033771777987588</v>
       </c>
       <c r="W74">
-        <v>0.2133973333648344</v>
+        <v>0.1983973333648344</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7399,7 +7399,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.3008716710200887</v>
+        <v>0.3227017422390071</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7410,13 +7410,13 @@
         <v>0.73</v>
       </c>
       <c r="B75">
-        <v>0.2177819019677308</v>
+        <v>0.2067087415637625</v>
       </c>
       <c r="C75">
-        <v>-93127.90876426383</v>
+        <v>-88684.37923890007</v>
       </c>
       <c r="D75">
-        <v>65040.73314852933</v>
+        <v>69484.26267389308</v>
       </c>
       <c r="E75">
         <v>158464.7502514326</v>
@@ -7443,37 +7443,37 @@
         <v>10954.1</v>
       </c>
       <c r="M75">
-        <v>36913.54603151132</v>
+        <v>34416.42490281942</v>
       </c>
       <c r="N75">
-        <v>-25959.44603151132</v>
+        <v>-23462.32490281942</v>
       </c>
       <c r="O75">
-        <v>-3244.930753938915</v>
+        <v>-2932.790612852427</v>
       </c>
       <c r="P75">
-        <v>-22714.5152775724</v>
+        <v>-20529.53428996699</v>
       </c>
       <c r="Q75">
-        <v>-21569.5152775724</v>
+        <v>-19384.53428996699</v>
       </c>
       <c r="R75">
         <v>2.703703703703703</v>
       </c>
       <c r="S75">
-        <v>0.2293276139941654</v>
+        <v>0.2288714643498385</v>
       </c>
       <c r="T75">
-        <v>3.575624164576254</v>
+        <v>3.568403590915757</v>
       </c>
       <c r="U75">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V75">
-        <v>0.03709376766001095</v>
+        <v>0.03978514630343923</v>
       </c>
       <c r="W75">
-        <v>0.2135115701223372</v>
+        <v>0.1985115701223371</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7481,7 +7481,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.2967501412800876</v>
+        <v>0.3182811704275138</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7492,13 +7492,13 @@
         <v>0.74</v>
       </c>
       <c r="B76">
-        <v>0.2195412681343561</v>
+        <v>0.2083181077303879</v>
       </c>
       <c r="C76">
-        <v>-96067.01038669156</v>
+        <v>-91652.93615166823</v>
       </c>
       <c r="D76">
-        <v>64382.10744271523</v>
+        <v>68796.18167773855</v>
       </c>
       <c r="E76">
         <v>160745.2261680463</v>
@@ -7525,37 +7525,37 @@
         <v>10954.1</v>
       </c>
       <c r="M76">
-        <v>37419.21104564161</v>
+        <v>34887.88277820051</v>
       </c>
       <c r="N76">
-        <v>-26465.11104564161</v>
+        <v>-23933.78277820051</v>
       </c>
       <c r="O76">
-        <v>-3308.138880705202</v>
+        <v>-2991.722847275064</v>
       </c>
       <c r="P76">
-        <v>-23156.97216493641</v>
+        <v>-20942.05993092545</v>
       </c>
       <c r="Q76">
-        <v>-22011.97216493641</v>
+        <v>-19797.05993092545</v>
       </c>
       <c r="R76">
         <v>2.846153846153846</v>
       </c>
       <c r="S76">
-        <v>0.2363863683785564</v>
+        <v>0.2359126745171401</v>
       </c>
       <c r="T76">
-        <v>3.71314817090611</v>
+        <v>3.705649882874056</v>
       </c>
       <c r="U76">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V76">
-        <v>0.03659250052947025</v>
+        <v>0.03924750919123059</v>
       </c>
       <c r="W76">
-        <v>0.2136227193999074</v>
+        <v>0.1986227193999074</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.2927400042357621</v>
+        <v>0.3139800735298447</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7574,13 +7574,13 @@
         <v>0.75</v>
       </c>
       <c r="B77">
-        <v>0.2213006343009815</v>
+        <v>0.2099274738970132</v>
       </c>
       <c r="C77">
-        <v>-98992.90677156676</v>
+        <v>-94607.99898877894</v>
       </c>
       <c r="D77">
-        <v>63736.68697445361</v>
+        <v>68121.59475724143</v>
       </c>
       <c r="E77">
         <v>163025.7020846599</v>
@@ -7607,37 +7607,37 @@
         <v>10954.1</v>
       </c>
       <c r="M77">
-        <v>37924.8760597719</v>
+        <v>35359.3406535816</v>
       </c>
       <c r="N77">
-        <v>-26970.7760597719</v>
+        <v>-24405.2406535816</v>
       </c>
       <c r="O77">
-        <v>-3371.347007471488</v>
+        <v>-3050.6550816977</v>
       </c>
       <c r="P77">
-        <v>-23599.42905230042</v>
+        <v>-21354.5855718839</v>
       </c>
       <c r="Q77">
-        <v>-22454.42905230042</v>
+        <v>-20209.5855718839</v>
       </c>
       <c r="R77">
         <v>3</v>
       </c>
       <c r="S77">
-        <v>0.2440098231136987</v>
+        <v>0.2435171814978257</v>
       </c>
       <c r="T77">
-        <v>3.861674097742354</v>
+        <v>3.853875878189018</v>
       </c>
       <c r="U77">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V77">
-        <v>0.03610460052241065</v>
+        <v>0.03872420906868085</v>
       </c>
       <c r="W77">
-        <v>0.2137309046967424</v>
+        <v>0.1987309046967424</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.2888368041792853</v>
+        <v>0.3097936725494468</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7656,13 +7656,13 @@
         <v>0.76</v>
       </c>
       <c r="B78">
-        <v>0.2230600004676069</v>
+        <v>0.2115368400636385</v>
       </c>
       <c r="C78">
-        <v>-101905.9911183949</v>
+        <v>-97549.96084766569</v>
       </c>
       <c r="D78">
-        <v>63104.07854423905</v>
+        <v>67460.10881496831</v>
       </c>
       <c r="E78">
         <v>165306.1780012735</v>
@@ -7689,37 +7689,37 @@
         <v>10954.1</v>
       </c>
       <c r="M78">
-        <v>38430.5410739022</v>
+        <v>35830.79852896269</v>
       </c>
       <c r="N78">
-        <v>-27476.4410739022</v>
+        <v>-24876.69852896269</v>
       </c>
       <c r="O78">
-        <v>-3434.555134237775</v>
+        <v>-3109.587316120336</v>
       </c>
       <c r="P78">
-        <v>-24041.88593966443</v>
+        <v>-21767.11121284236</v>
       </c>
       <c r="Q78">
-        <v>-22896.88593966443</v>
+        <v>-20622.11121284236</v>
       </c>
       <c r="R78">
         <v>3.166666666666667</v>
       </c>
       <c r="S78">
-        <v>0.2522685657434361</v>
+        <v>0.2517553973935684</v>
       </c>
       <c r="T78">
-        <v>4.022577185148287</v>
+        <v>4.014454039780228</v>
       </c>
       <c r="U78">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V78">
-        <v>0.03562953998922103</v>
+        <v>0.03821468000198767</v>
       </c>
       <c r="W78">
-        <v>0.2138362430120818</v>
+        <v>0.1988362430120817</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7727,7 +7727,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.2850363199137683</v>
+        <v>0.3057174400159014</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7738,13 +7738,13 @@
         <v>0.77</v>
       </c>
       <c r="B79">
-        <v>0.2248193666342322</v>
+        <v>0.2131462062302639</v>
       </c>
       <c r="C79">
-        <v>-104806.6411695403</v>
+        <v>-100479.1997041113</v>
       </c>
       <c r="D79">
-        <v>62483.90440970733</v>
+        <v>66811.34587513632</v>
       </c>
       <c r="E79">
         <v>167586.6539178871</v>
@@ -7771,37 +7771,37 @@
         <v>10954.1</v>
       </c>
       <c r="M79">
-        <v>38936.20608803249</v>
+        <v>36302.25640434377</v>
       </c>
       <c r="N79">
-        <v>-27982.10608803249</v>
+        <v>-25348.15640434378</v>
       </c>
       <c r="O79">
-        <v>-3497.763261004062</v>
+        <v>-3168.519550542972</v>
       </c>
       <c r="P79">
-        <v>-24484.34282702843</v>
+        <v>-22179.6368538008</v>
       </c>
       <c r="Q79">
-        <v>-23339.34282702843</v>
+        <v>-21034.6368538008</v>
       </c>
       <c r="R79">
         <v>3.347826086956522</v>
       </c>
       <c r="S79">
-        <v>0.2612454599061942</v>
+        <v>0.260709979888941</v>
       </c>
       <c r="T79">
-        <v>4.197471845372124</v>
+        <v>4.188995519770672</v>
       </c>
       <c r="U79">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V79">
-        <v>0.03516681869065972</v>
+        <v>0.03771838545650732</v>
       </c>
       <c r="W79">
-        <v>0.2139388452672825</v>
+        <v>0.1989388452672824</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7809,7 +7809,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.2813345495252777</v>
+        <v>0.3017470836520585</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7820,13 +7820,13 @@
         <v>0.78</v>
       </c>
       <c r="B80">
-        <v>0.2265787328008575</v>
+        <v>0.2147555723968892</v>
       </c>
       <c r="C80">
-        <v>-107695.2199623821</v>
+        <v>-103396.0791324455</v>
       </c>
       <c r="D80">
-        <v>61875.80153347912</v>
+        <v>66174.94236341568</v>
       </c>
       <c r="E80">
         <v>169867.1298345007</v>
@@ -7853,37 +7853,37 @@
         <v>10954.1</v>
       </c>
       <c r="M80">
-        <v>39441.87110216278</v>
+        <v>36773.71427972486</v>
       </c>
       <c r="N80">
-        <v>-28487.77110216278</v>
+        <v>-25819.61427972486</v>
       </c>
       <c r="O80">
-        <v>-3560.971387770348</v>
+        <v>-3227.451784965608</v>
       </c>
       <c r="P80">
-        <v>-24926.79971439244</v>
+        <v>-22592.16249475925</v>
       </c>
       <c r="Q80">
-        <v>-23781.79971439244</v>
+        <v>-21447.16249475925</v>
       </c>
       <c r="R80">
         <v>3.545454545454546</v>
       </c>
       <c r="S80">
-        <v>0.2710384353564758</v>
+        <v>0.2704786153384383</v>
       </c>
       <c r="T80">
-        <v>4.388266020161767</v>
+        <v>4.379404407032975</v>
       </c>
       <c r="U80">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V80">
-        <v>0.03471596204077947</v>
+        <v>0.03723481641219312</v>
       </c>
       <c r="W80">
-        <v>0.2140388166954267</v>
+        <v>0.1990388166954267</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7891,7 +7891,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.2777276963262357</v>
+        <v>0.2978785312975449</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7902,13 +7902,13 @@
         <v>0.79</v>
       </c>
       <c r="B81">
-        <v>0.2283380989674829</v>
+        <v>0.2163649385635146</v>
       </c>
       <c r="C81">
-        <v>-110572.0765379738</v>
+        <v>-106300.94898497</v>
       </c>
       <c r="D81">
-        <v>61279.42087450106</v>
+        <v>65550.54842750485</v>
       </c>
       <c r="E81">
         <v>172147.6057511143</v>
@@ -7935,37 +7935,37 @@
         <v>10954.1</v>
       </c>
       <c r="M81">
-        <v>39947.53611629308</v>
+        <v>37245.17215510595</v>
       </c>
       <c r="N81">
-        <v>-28993.43611629308</v>
+        <v>-26291.07215510595</v>
       </c>
       <c r="O81">
-        <v>-3624.179514536635</v>
+        <v>-3286.384019388244</v>
       </c>
       <c r="P81">
-        <v>-25369.25660175645</v>
+        <v>-23004.68813571771</v>
       </c>
       <c r="Q81">
-        <v>-24224.25660175645</v>
+        <v>-21859.68813571771</v>
       </c>
       <c r="R81">
         <v>3.761904761904763</v>
       </c>
       <c r="S81">
-        <v>0.2817640751353557</v>
+        <v>0.2811775970212211</v>
       </c>
       <c r="T81">
-        <v>4.5972310687409</v>
+        <v>4.587947474034547</v>
       </c>
       <c r="U81">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V81">
-        <v>0.03427651948330124</v>
+        <v>0.03676348962216536</v>
       </c>
       <c r="W81">
-        <v>0.2141362572013395</v>
+        <v>0.1991362572013395</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7973,7 +7973,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.2742121558664099</v>
+        <v>0.2941079169773229</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7984,13 +7984,13 @@
         <v>0.8</v>
       </c>
       <c r="B82">
-        <v>0.2300974651341082</v>
+        <v>0.2179743047301399</v>
       </c>
       <c r="C82">
-        <v>-113437.5466091111</v>
+        <v>-109194.146033278</v>
       </c>
       <c r="D82">
-        <v>60694.42671997736</v>
+        <v>64937.82729581038</v>
       </c>
       <c r="E82">
         <v>174428.0816677279</v>
@@ -8017,37 +8017,37 @@
         <v>10954.1</v>
       </c>
       <c r="M82">
-        <v>40453.20113042337</v>
+        <v>37716.63003048704</v>
       </c>
       <c r="N82">
-        <v>-29499.10113042337</v>
+        <v>-26762.53003048704</v>
       </c>
       <c r="O82">
-        <v>-3687.387641302921</v>
+        <v>-3345.31625381088</v>
       </c>
       <c r="P82">
-        <v>-25811.71348912045</v>
+        <v>-23417.21377667616</v>
       </c>
       <c r="Q82">
-        <v>-24666.71348912045</v>
+        <v>-22272.21377667616</v>
       </c>
       <c r="R82">
         <v>4.000000000000001</v>
       </c>
       <c r="S82">
-        <v>0.2935622788921234</v>
+        <v>0.2929464768722821</v>
       </c>
       <c r="T82">
-        <v>4.827092622177944</v>
+        <v>4.817344847736273</v>
       </c>
       <c r="U82">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V82">
-        <v>0.03384806298975998</v>
+        <v>0.03630394600188829</v>
       </c>
       <c r="W82">
-        <v>0.2142312616946044</v>
+        <v>0.1992312616946044</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8055,7 +8055,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.2707845039180798</v>
+        <v>0.2904315680151064</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8066,13 +8066,13 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2318568313007335</v>
+        <v>0.2195836708967653</v>
       </c>
       <c r="C83">
-        <v>-116291.9531904969</v>
+        <v>-112075.9945739406</v>
       </c>
       <c r="D83">
-        <v>60120.49605520512</v>
+        <v>64336.45467176148</v>
       </c>
       <c r="E83">
         <v>176708.5575843415</v>
@@ -8099,37 +8099,37 @@
         <v>10954.1</v>
       </c>
       <c r="M83">
-        <v>40958.86614455366</v>
+        <v>38188.08790586813</v>
       </c>
       <c r="N83">
-        <v>-30004.76614455367</v>
+        <v>-27233.98790586813</v>
       </c>
       <c r="O83">
-        <v>-3750.595768069208</v>
+        <v>-3404.248488233517</v>
       </c>
       <c r="P83">
-        <v>-26254.17037648446</v>
+        <v>-23829.73941763462</v>
       </c>
       <c r="Q83">
-        <v>-25109.17037648446</v>
+        <v>-22684.73941763462</v>
       </c>
       <c r="R83">
         <v>4.263157894736843</v>
       </c>
       <c r="S83">
-        <v>0.3066023988338142</v>
+        <v>0.3059541861813497</v>
       </c>
       <c r="T83">
-        <v>5.081150128608363</v>
+        <v>5.070889313406605</v>
       </c>
       <c r="U83">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V83">
-        <v>0.03343018566889874</v>
+        <v>0.03585574913766745</v>
       </c>
       <c r="W83">
-        <v>0.2143239203979121</v>
+        <v>0.1993239203979122</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8137,7 +8137,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.2674414853511899</v>
+        <v>0.2868459931013395</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8148,13 +8148,13 @@
         <v>0.8200000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2336161974673589</v>
+        <v>0.2211930370633906</v>
       </c>
       <c r="C84">
-        <v>-119135.6071934875</v>
+        <v>-114946.8070008453</v>
       </c>
       <c r="D84">
-        <v>59557.31796882815</v>
+        <v>63746.11816147037</v>
       </c>
       <c r="E84">
         <v>178989.0335009551</v>
@@ -8181,37 +8181,37 @@
         <v>10954.1</v>
       </c>
       <c r="M84">
-        <v>41464.53115868395</v>
+        <v>38659.54578124922</v>
       </c>
       <c r="N84">
-        <v>-30510.43115868395</v>
+        <v>-27705.44578124922</v>
       </c>
       <c r="O84">
-        <v>-3813.803894835494</v>
+        <v>-3463.180722656152</v>
       </c>
       <c r="P84">
-        <v>-26696.62726384846</v>
+        <v>-24242.26505859307</v>
       </c>
       <c r="Q84">
-        <v>-25551.62726384846</v>
+        <v>-23097.26505859307</v>
       </c>
       <c r="R84">
         <v>4.555555555555557</v>
       </c>
       <c r="S84">
-        <v>0.3210914209912483</v>
+        <v>0.320407196524758</v>
       </c>
       <c r="T84">
-        <v>5.363436246864383</v>
+        <v>5.352605386373638</v>
       </c>
       <c r="U84">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V84">
-        <v>0.03302250047781462</v>
+        <v>0.03541848390428126</v>
       </c>
       <c r="W84">
-        <v>0.2144143191328466</v>
+        <v>0.1994143191328466</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8219,7 +8219,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.2641800038225169</v>
+        <v>0.2833478712342501</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8230,13 +8230,13 @@
         <v>0.8300000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2353755636339842</v>
+        <v>0.2228024032300159</v>
       </c>
       <c r="C85">
-        <v>-121968.8079877209</v>
+        <v>-117806.8843463132</v>
       </c>
       <c r="D85">
-        <v>59004.59309120832</v>
+        <v>63166.51673261606</v>
       </c>
       <c r="E85">
         <v>181269.5094175687</v>
@@ -8263,37 +8263,37 @@
         <v>10954.1</v>
       </c>
       <c r="M85">
-        <v>41970.19617281425</v>
+        <v>39131.00365663031</v>
       </c>
       <c r="N85">
-        <v>-31016.09617281425</v>
+        <v>-28176.90365663031</v>
       </c>
       <c r="O85">
-        <v>-3877.012021601781</v>
+        <v>-3522.112957078789</v>
       </c>
       <c r="P85">
-        <v>-27139.08415121247</v>
+        <v>-24654.79069955152</v>
       </c>
       <c r="Q85">
-        <v>-25994.08415121247</v>
+        <v>-23509.79069955152</v>
       </c>
       <c r="R85">
         <v>4.882352941176473</v>
       </c>
       <c r="S85">
-        <v>0.3372850339907335</v>
+        <v>0.3365605610262143</v>
       </c>
       <c r="T85">
-        <v>5.678932496679936</v>
+        <v>5.667464526748558</v>
       </c>
       <c r="U85">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V85">
-        <v>0.03262463902627467</v>
+        <v>0.03499175518254292</v>
       </c>
       <c r="W85">
-        <v>0.2145025395850115</v>
+        <v>0.1995025395850115</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8301,7 +8301,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.2609971122101974</v>
+        <v>0.2799340414603434</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8312,13 +8312,13 @@
         <v>0.84</v>
       </c>
       <c r="B86">
-        <v>0.2371349298006095</v>
+        <v>0.2244117693966413</v>
       </c>
       <c r="C86">
-        <v>-124791.8439317605</v>
+        <v>-120656.5167929609</v>
       </c>
       <c r="D86">
-        <v>58462.03306378235</v>
+        <v>62597.36020258195</v>
       </c>
       <c r="E86">
         <v>183549.9853341823</v>
@@ -8345,37 +8345,37 @@
         <v>10954.1</v>
       </c>
       <c r="M86">
-        <v>42475.86118694453</v>
+        <v>39602.46153201139</v>
       </c>
       <c r="N86">
-        <v>-31521.76118694453</v>
+        <v>-28648.36153201139</v>
       </c>
       <c r="O86">
-        <v>-3940.220148368066</v>
+        <v>-3581.045191501424</v>
       </c>
       <c r="P86">
-        <v>-27581.54103857647</v>
+        <v>-25067.31634050997</v>
       </c>
       <c r="Q86">
-        <v>-26436.54103857647</v>
+        <v>-23922.31634050997</v>
       </c>
       <c r="R86">
         <v>5.249999999999999</v>
       </c>
       <c r="S86">
-        <v>0.3555028486151542</v>
+        <v>0.3547330960903526</v>
       </c>
       <c r="T86">
-        <v>6.033865777722428</v>
+        <v>6.021681059670341</v>
       </c>
       <c r="U86">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V86">
-        <v>0.03223625046643808</v>
+        <v>0.03457518666846504</v>
       </c>
       <c r="W86">
-        <v>0.2145886595502201</v>
+        <v>0.1995886595502201</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.2578900037315046</v>
+        <v>0.2766014933477203</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8394,13 +8394,13 @@
         <v>0.85</v>
       </c>
       <c r="B87">
-        <v>0.2388942959672349</v>
+        <v>0.2260211355632666</v>
       </c>
       <c r="C87">
-        <v>-127604.992874728</v>
+        <v>-123495.984158137</v>
       </c>
       <c r="D87">
-        <v>57929.36003742841</v>
+        <v>62038.36875401939</v>
       </c>
       <c r="E87">
         <v>185830.4612507959</v>
@@ -8427,37 +8427,37 @@
         <v>10954.1</v>
       </c>
       <c r="M87">
-        <v>42981.52620107483</v>
+        <v>40073.91940739247</v>
       </c>
       <c r="N87">
-        <v>-32027.42620107483</v>
+        <v>-29119.81940739248</v>
       </c>
       <c r="O87">
-        <v>-4003.428275134353</v>
+        <v>-3639.977425924059</v>
       </c>
       <c r="P87">
-        <v>-28023.99792594048</v>
+        <v>-25479.84198146842</v>
       </c>
       <c r="Q87">
-        <v>-26878.99792594048</v>
+        <v>-24334.84198146842</v>
       </c>
       <c r="R87">
         <v>5.666666666666666</v>
       </c>
       <c r="S87">
-        <v>0.3761497051894978</v>
+        <v>0.3753286358297094</v>
       </c>
       <c r="T87">
-        <v>6.436123496237258</v>
+        <v>6.423126463648363</v>
       </c>
       <c r="U87">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V87">
-        <v>0.03185700046095057</v>
+        <v>0.0341684197664831</v>
       </c>
       <c r="W87">
-        <v>0.2146727531633061</v>
+        <v>0.1996727531633061</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8465,7 +8465,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.2548560036876045</v>
+        <v>0.2733473581318648</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8476,13 +8476,13 @@
         <v>0.86</v>
       </c>
       <c r="B88">
-        <v>0.2406536621338602</v>
+        <v>0.227630501729892</v>
       </c>
       <c r="C88">
-        <v>-130408.5226307613</v>
+        <v>-126325.5563526329</v>
       </c>
       <c r="D88">
-        <v>57406.30619800868</v>
+        <v>61489.27247613714</v>
       </c>
       <c r="E88">
         <v>188110.9371674095</v>
@@ -8509,37 +8509,37 @@
         <v>10954.1</v>
       </c>
       <c r="M88">
-        <v>43487.19121520512</v>
+        <v>40545.37728277356</v>
       </c>
       <c r="N88">
-        <v>-32533.09121520512</v>
+        <v>-29591.27728277356</v>
       </c>
       <c r="O88">
-        <v>-4066.63640190064</v>
+        <v>-3698.909660346695</v>
       </c>
       <c r="P88">
-        <v>-28466.45481330448</v>
+        <v>-25892.36762242686</v>
       </c>
       <c r="Q88">
-        <v>-27321.45481330448</v>
+        <v>-24747.36762242686</v>
       </c>
       <c r="R88">
         <v>6.142857142857142</v>
       </c>
       <c r="S88">
-        <v>0.3997461127030333</v>
+        <v>0.3988663955318315</v>
       </c>
       <c r="T88">
-        <v>6.895846603111347</v>
+        <v>6.881921211051817</v>
       </c>
       <c r="U88">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V88">
-        <v>0.03148657022303254</v>
+        <v>0.03377111255989609</v>
       </c>
       <c r="W88">
-        <v>0.2147548911109716</v>
+        <v>0.1997548911109716</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8547,7 +8547,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.2518925617842603</v>
+        <v>0.2701689004791687</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8558,13 +8558,13 @@
         <v>0.87</v>
       </c>
       <c r="B89">
-        <v>0.2424130283004856</v>
+        <v>0.2292398678965173</v>
       </c>
       <c r="C89">
-        <v>-133202.6914279981</v>
+        <v>-129145.4938152466</v>
       </c>
       <c r="D89">
-        <v>56892.61331738558</v>
+        <v>60949.81093013709</v>
       </c>
       <c r="E89">
         <v>190391.4130840231</v>
@@ -8591,37 +8591,37 @@
         <v>10954.1</v>
       </c>
       <c r="M89">
-        <v>43992.85622933541</v>
+        <v>41016.83515815465</v>
       </c>
       <c r="N89">
-        <v>-33038.75622933541</v>
+        <v>-30062.73515815465</v>
       </c>
       <c r="O89">
-        <v>-4129.844528666927</v>
+        <v>-3757.841894769332</v>
       </c>
       <c r="P89">
-        <v>-28908.91170066849</v>
+        <v>-26304.89326338532</v>
       </c>
       <c r="Q89">
-        <v>-27763.91170066849</v>
+        <v>-25159.89326338532</v>
       </c>
       <c r="R89">
         <v>6.692307692307692</v>
       </c>
       <c r="S89">
-        <v>0.4269727367571128</v>
+        <v>0.4260253490342801</v>
       </c>
       <c r="T89">
-        <v>7.42629634181222</v>
+        <v>7.411299765748112</v>
       </c>
       <c r="U89">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V89">
-        <v>0.0311246556227678</v>
+        <v>0.03338293885231108</v>
       </c>
       <c r="W89">
-        <v>0.2148351408299551</v>
+        <v>0.199835140829955</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8629,7 +8629,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.2489972449821424</v>
+        <v>0.2670635108184886</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8640,13 +8640,13 @@
         <v>0.88</v>
       </c>
       <c r="B90">
-        <v>0.2441723944671109</v>
+        <v>0.2308492340631427</v>
       </c>
       <c r="C90">
-        <v>-135987.7483336671</v>
+        <v>-131956.0479246708</v>
       </c>
       <c r="D90">
-        <v>56388.03232833015</v>
+        <v>60419.73273732649</v>
       </c>
       <c r="E90">
         <v>192671.8890006368</v>
@@ -8673,37 +8673,37 @@
         <v>10954.1</v>
       </c>
       <c r="M90">
-        <v>44498.52124346571</v>
+        <v>41488.29303353575</v>
       </c>
       <c r="N90">
-        <v>-33544.42124346571</v>
+        <v>-30534.19303353575</v>
       </c>
       <c r="O90">
-        <v>-4193.052655433214</v>
+        <v>-3816.774129191968</v>
       </c>
       <c r="P90">
-        <v>-29351.3685880325</v>
+        <v>-26717.41890434378</v>
       </c>
       <c r="Q90">
-        <v>-28206.3685880325</v>
+        <v>-25572.41890434378</v>
       </c>
       <c r="R90">
         <v>7.333333333333334</v>
       </c>
       <c r="S90">
-        <v>0.4587371314868723</v>
+        <v>0.4577107947871368</v>
       </c>
       <c r="T90">
-        <v>8.045154370296574</v>
+        <v>8.028908079560455</v>
       </c>
       <c r="U90">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V90">
-        <v>0.03077096635432725</v>
+        <v>0.0330035872744439</v>
       </c>
       <c r="W90">
-        <v>0.2149135666916889</v>
+        <v>0.1999135666916889</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8711,7 +8711,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.2461677308346181</v>
+        <v>0.2640286981955512</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8722,13 +8722,13 @@
         <v>0.89</v>
       </c>
       <c r="B91">
-        <v>0.2459317606337363</v>
+        <v>0.232458600229768</v>
       </c>
       <c r="C91">
-        <v>-138763.9336567582</v>
+        <v>-134757.4613900729</v>
       </c>
       <c r="D91">
-        <v>55892.32292185268</v>
+        <v>59898.79518853794</v>
       </c>
       <c r="E91">
         <v>194952.3649172504</v>
@@ -8755,37 +8755,37 @@
         <v>10954.1</v>
       </c>
       <c r="M91">
-        <v>45004.186257596</v>
+        <v>41959.75090891683</v>
       </c>
       <c r="N91">
-        <v>-34050.086257596</v>
+        <v>-31005.65090891683</v>
       </c>
       <c r="O91">
-        <v>-4256.2607821995</v>
+        <v>-3875.706363614604</v>
       </c>
       <c r="P91">
-        <v>-29793.8254753965</v>
+        <v>-27129.94454530223</v>
       </c>
       <c r="Q91">
-        <v>-28648.8254753965</v>
+        <v>-25984.94454530223</v>
       </c>
       <c r="R91">
         <v>8.090909090909092</v>
       </c>
       <c r="S91">
-        <v>0.4962768707129516</v>
+        <v>0.4951572306768766</v>
       </c>
       <c r="T91">
-        <v>8.776532040323534</v>
+        <v>8.758808814065951</v>
       </c>
       <c r="U91">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V91">
-        <v>0.03042522515933481</v>
+        <v>0.03263276045113554</v>
       </c>
       <c r="W91">
-        <v>0.2149902301745074</v>
+        <v>0.1999902301745074</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.2434018012746785</v>
+        <v>0.2610620836090843</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8804,13 +8804,13 @@
         <v>0.9</v>
       </c>
       <c r="B92">
-        <v>0.2476911268003616</v>
+        <v>0.2340679663963933</v>
       </c>
       <c r="C92">
-        <v>-141531.4793296373</v>
+        <v>-137549.9686216426</v>
       </c>
       <c r="D92">
-        <v>55405.25316558725</v>
+        <v>59386.76387358187</v>
       </c>
       <c r="E92">
         <v>197232.840833864</v>
@@ -8837,37 +8837,37 @@
         <v>10954.1</v>
       </c>
       <c r="M92">
-        <v>45509.85127172629</v>
+        <v>42431.20878429792</v>
       </c>
       <c r="N92">
-        <v>-34555.75127172629</v>
+        <v>-31477.10878429793</v>
       </c>
       <c r="O92">
-        <v>-4319.468908965787</v>
+        <v>-3934.638598037241</v>
       </c>
       <c r="P92">
-        <v>-30236.28236276051</v>
+        <v>-27542.47018626069</v>
       </c>
       <c r="Q92">
-        <v>-29091.28236276051</v>
+        <v>-26397.47018626069</v>
       </c>
       <c r="R92">
         <v>9.000000000000002</v>
       </c>
       <c r="S92">
-        <v>0.5413245577842468</v>
+        <v>0.5400929537445642</v>
       </c>
       <c r="T92">
-        <v>9.654185244355888</v>
+        <v>9.634689695472547</v>
       </c>
       <c r="U92">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V92">
-        <v>0.03008716710200887</v>
+        <v>0.0322701742239007</v>
       </c>
       <c r="W92">
-        <v>0.2150651900243744</v>
+        <v>0.2000651900243744</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.240697336816071</v>
+        <v>0.2581613937912056</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8886,13 +8886,13 @@
         <v>0.91</v>
       </c>
       <c r="B93">
-        <v>0.2494504929669869</v>
+        <v>0.2356773325630187</v>
       </c>
       <c r="C93">
-        <v>-144290.6092698807</v>
+        <v>-140333.7960822947</v>
       </c>
       <c r="D93">
-        <v>54926.59914195743</v>
+        <v>58883.41232954335</v>
       </c>
       <c r="E93">
         <v>199513.3167504776</v>
@@ -8919,37 +8919,37 @@
         <v>10954.1</v>
       </c>
       <c r="M93">
-        <v>46015.51628585658</v>
+        <v>42902.66665967901</v>
       </c>
       <c r="N93">
-        <v>-35061.41628585658</v>
+        <v>-31948.56665967901</v>
       </c>
       <c r="O93">
-        <v>-4382.677035732073</v>
+        <v>-3993.570832459876</v>
       </c>
       <c r="P93">
-        <v>-30678.73925012451</v>
+        <v>-27954.99582721914</v>
       </c>
       <c r="Q93">
-        <v>-29533.73925012451</v>
+        <v>-26809.99582721914</v>
       </c>
       <c r="R93">
         <v>10.11111111111111</v>
       </c>
       <c r="S93">
-        <v>0.5963828419824964</v>
+        <v>0.5950143930495159</v>
       </c>
       <c r="T93">
-        <v>10.72687249372876</v>
+        <v>10.70521077274728</v>
       </c>
       <c r="U93">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V93">
-        <v>0.02975653889209669</v>
+        <v>0.03191555692473696</v>
       </c>
       <c r="W93">
-        <v>0.2151385024050135</v>
+        <v>0.2001385024050135</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8957,7 +8957,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.2380523111367735</v>
+        <v>0.2553244553978956</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8968,13 +8968,13 @@
         <v>0.92</v>
       </c>
       <c r="B94">
-        <v>0.2512098591336123</v>
+        <v>0.237286698729644</v>
       </c>
       <c r="C94">
-        <v>-147041.5397235148</v>
+        <v>-143109.1626216373</v>
       </c>
       <c r="D94">
-        <v>54456.14460493689</v>
+        <v>58388.52170681443</v>
       </c>
       <c r="E94">
         <v>201793.7926670912</v>
@@ -9001,37 +9001,37 @@
         <v>10954.1</v>
       </c>
       <c r="M94">
-        <v>46521.18129998688</v>
+        <v>43374.12453506009</v>
       </c>
       <c r="N94">
-        <v>-35567.08129998688</v>
+        <v>-32420.0245350601</v>
       </c>
       <c r="O94">
-        <v>-4445.88516249836</v>
+        <v>-4052.503066882512</v>
       </c>
       <c r="P94">
-        <v>-31121.19613748852</v>
+        <v>-28367.52146817758</v>
       </c>
       <c r="Q94">
-        <v>-29976.19613748852</v>
+        <v>-27222.52146817758</v>
       </c>
       <c r="R94">
         <v>11.50000000000001</v>
       </c>
       <c r="S94">
-        <v>0.6652056972303088</v>
+        <v>0.6636661921807055</v>
       </c>
       <c r="T94">
-        <v>12.06773155544487</v>
+        <v>12.04336211934069</v>
       </c>
       <c r="U94">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V94">
-        <v>0.0294330982519652</v>
+        <v>0.03156864869729416</v>
       </c>
       <c r="W94">
-        <v>0.2152102210382474</v>
+        <v>0.2002102210382474</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.2354647860157216</v>
+        <v>0.2525491895783534</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9050,13 +9050,13 @@
         <v>0.93</v>
       </c>
       <c r="B95">
-        <v>0.2529692253002376</v>
+        <v>0.2388960648962694</v>
       </c>
       <c r="C95">
-        <v>-149784.4795907655</v>
+        <v>-145876.2797932381</v>
       </c>
       <c r="D95">
-        <v>53993.68065429979</v>
+        <v>57901.88045182721</v>
       </c>
       <c r="E95">
         <v>204074.2685837048</v>
@@ -9083,37 +9083,37 @@
         <v>10954.1</v>
       </c>
       <c r="M95">
-        <v>47026.84631411717</v>
+        <v>43845.58241044118</v>
       </c>
       <c r="N95">
-        <v>-36072.74631411717</v>
+        <v>-32891.48241044118</v>
       </c>
       <c r="O95">
-        <v>-4509.093289264646</v>
+        <v>-4111.435301305148</v>
       </c>
       <c r="P95">
-        <v>-31563.65302485252</v>
+        <v>-28780.04710913603</v>
       </c>
       <c r="Q95">
-        <v>-30418.65302485252</v>
+        <v>-27635.04710913603</v>
       </c>
       <c r="R95">
         <v>13.2857142857143</v>
       </c>
       <c r="S95">
-        <v>0.7536922254060672</v>
+        <v>0.7519327910636635</v>
       </c>
       <c r="T95">
-        <v>13.79169320622271</v>
+        <v>13.76384242210364</v>
       </c>
       <c r="U95">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V95">
-        <v>0.02911661332452471</v>
+        <v>0.03122920086183939</v>
       </c>
       <c r="W95">
-        <v>0.2152803973352827</v>
+        <v>0.2002803973352827</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9121,7 +9121,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.2329329065961977</v>
+        <v>0.2498336068947151</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9132,13 +9132,13 @@
         <v>0.9400000000000001</v>
       </c>
       <c r="B96">
-        <v>0.254728591466863</v>
+        <v>0.2405054310628947</v>
       </c>
       <c r="C96">
-        <v>-152519.6307353496</v>
+        <v>-148635.3521561576</v>
       </c>
       <c r="D96">
-        <v>53539.00542632928</v>
+        <v>57423.28400552132</v>
       </c>
       <c r="E96">
         <v>206354.7445003184</v>
@@ -9165,37 +9165,37 @@
         <v>10954.1</v>
       </c>
       <c r="M96">
-        <v>47532.51132824746</v>
+        <v>44317.04028582227</v>
       </c>
       <c r="N96">
-        <v>-36578.41132824746</v>
+        <v>-33362.94028582227</v>
       </c>
       <c r="O96">
-        <v>-4572.301416030933</v>
+        <v>-4170.367535727784</v>
       </c>
       <c r="P96">
-        <v>-32006.10991221653</v>
+        <v>-29192.57275009449</v>
       </c>
       <c r="Q96">
-        <v>-30861.10991221653</v>
+        <v>-28047.57275009449</v>
       </c>
       <c r="R96">
         <v>15.66666666666668</v>
       </c>
       <c r="S96">
-        <v>0.8716742629737454</v>
+        <v>0.8696215895742744</v>
       </c>
       <c r="T96">
-        <v>16.09030874059316</v>
+        <v>16.05781615912093</v>
       </c>
       <c r="U96">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V96">
-        <v>0.02880686211894466</v>
+        <v>0.03089697532075599</v>
       </c>
       <c r="W96">
-        <v>0.2153490805196152</v>
+        <v>0.2003490805196152</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.2304548969515573</v>
+        <v>0.2471758025660479</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9214,13 +9214,13 @@
         <v>0.9500000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2564879576334883</v>
+        <v>0.24211479722952</v>
       </c>
       <c r="C97">
-        <v>-155247.1882782691</v>
+        <v>-151386.5775616493</v>
       </c>
       <c r="D97">
-        <v>53091.92380002335</v>
+        <v>56952.53451664321</v>
       </c>
       <c r="E97">
         <v>208635.220416932</v>
@@ -9247,37 +9247,37 @@
         <v>10954.1</v>
       </c>
       <c r="M97">
-        <v>48038.17634237775</v>
+        <v>44788.49816120336</v>
       </c>
       <c r="N97">
-        <v>-37084.07634237775</v>
+        <v>-33834.39816120336</v>
       </c>
       <c r="O97">
-        <v>-4635.509542797219</v>
+        <v>-4229.29977015042</v>
       </c>
       <c r="P97">
-        <v>-32448.56679958053</v>
+        <v>-29605.09839105294</v>
       </c>
       <c r="Q97">
-        <v>-31303.56679958053</v>
+        <v>-28460.09839105294</v>
       </c>
       <c r="R97">
         <v>19.00000000000003</v>
       </c>
       <c r="S97">
-        <v>1.036849115568495</v>
+        <v>1.03438590748913</v>
       </c>
       <c r="T97">
-        <v>19.3083704887118</v>
+        <v>19.26937939094512</v>
       </c>
       <c r="U97">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V97">
-        <v>0.02850363199137683</v>
+        <v>0.03057174400159014</v>
       </c>
       <c r="W97">
-        <v>0.2154163177421722</v>
+        <v>0.2004163177421722</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9285,7 +9285,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.2280290559310146</v>
+        <v>0.2445739520127211</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9296,13 +9296,13 @@
         <v>0.96</v>
       </c>
       <c r="B98">
-        <v>0.2582473238001136</v>
+        <v>0.2437241633961454</v>
       </c>
       <c r="C98">
-        <v>-157967.3408770079</v>
+        <v>-154130.1474258735</v>
       </c>
       <c r="D98">
-        <v>52652.24711789816</v>
+        <v>56489.44056903262</v>
       </c>
       <c r="E98">
         <v>210915.6963335456</v>
@@ -9329,37 +9329,37 @@
         <v>10954.1</v>
       </c>
       <c r="M98">
-        <v>48543.84135650804</v>
+        <v>45259.95603658444</v>
       </c>
       <c r="N98">
-        <v>-37589.74135650804</v>
+        <v>-34305.85603658445</v>
       </c>
       <c r="O98">
-        <v>-4698.717669563505</v>
+        <v>-4288.232004573056</v>
       </c>
       <c r="P98">
-        <v>-32891.02368694454</v>
+        <v>-30017.62403201139</v>
       </c>
       <c r="Q98">
-        <v>-31746.02368694454</v>
+        <v>-28872.62403201139</v>
       </c>
       <c r="R98">
         <v>23.99999999999998</v>
       </c>
       <c r="S98">
-        <v>1.284611394460616</v>
+        <v>1.281532384361409</v>
       </c>
       <c r="T98">
-        <v>24.1354631108897</v>
+        <v>24.08672423868135</v>
       </c>
       <c r="U98">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V98">
-        <v>0.02820671915813332</v>
+        <v>0.03025328833490691</v>
       </c>
       <c r="W98">
-        <v>0.2154821541892593</v>
+        <v>0.2004821541892593</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.2256537532650665</v>
+        <v>0.2420263066792553</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9378,13 +9378,13 @@
         <v>0.97</v>
       </c>
       <c r="B99">
-        <v>0.260006689966739</v>
+        <v>0.2453335295627707</v>
       </c>
       <c r="C99">
-        <v>-160680.270990969</v>
+        <v>-156866.246989413</v>
       </c>
       <c r="D99">
-        <v>52219.79292055069</v>
+        <v>56033.81692210667</v>
       </c>
       <c r="E99">
         <v>213196.1722501592</v>
@@ -9411,37 +9411,37 @@
         <v>10954.1</v>
       </c>
       <c r="M99">
-        <v>49049.50637063833</v>
+        <v>45731.41391196553</v>
       </c>
       <c r="N99">
-        <v>-38095.40637063833</v>
+        <v>-34777.31391196553</v>
       </c>
       <c r="O99">
-        <v>-4761.925796329791</v>
+        <v>-4347.164238995691</v>
       </c>
       <c r="P99">
-        <v>-33333.48057430854</v>
+        <v>-30430.14967296984</v>
       </c>
       <c r="Q99">
-        <v>-32188.48057430854</v>
+        <v>-29285.14967296984</v>
       </c>
       <c r="R99">
         <v>32.33333333333331</v>
       </c>
       <c r="S99">
-        <v>1.697548525947488</v>
+        <v>1.693443179148546</v>
       </c>
       <c r="T99">
-        <v>32.18061748118627</v>
+        <v>32.11563231824179</v>
       </c>
       <c r="U99">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V99">
-        <v>0.02791592823897731</v>
+        <v>0.02994139876444395</v>
       </c>
       <c r="W99">
-        <v>0.2155466331838292</v>
+        <v>0.2005466331838292</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.2233274259118184</v>
+        <v>0.2395311901155517</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9460,13 +9460,13 @@
         <v>0.98</v>
       </c>
       <c r="B100">
-        <v>0.2617660561333643</v>
+        <v>0.246942895729396</v>
       </c>
       <c r="C100">
-        <v>-163386.1551339377</v>
+        <v>-159595.0555643306</v>
       </c>
       <c r="D100">
-        <v>51794.3846941956</v>
+        <v>55585.4842638027</v>
       </c>
       <c r="E100">
         <v>215476.6481667728</v>
@@ -9493,37 +9493,37 @@
         <v>10954.1</v>
       </c>
       <c r="M100">
-        <v>49555.17138476863</v>
+        <v>46202.87178734662</v>
       </c>
       <c r="N100">
-        <v>-38601.07138476863</v>
+        <v>-35248.77178734662</v>
       </c>
       <c r="O100">
-        <v>-4825.133923096078</v>
+        <v>-4406.096473418328</v>
       </c>
       <c r="P100">
-        <v>-33775.93746167255</v>
+        <v>-30842.6753139283</v>
       </c>
       <c r="Q100">
-        <v>-32630.93746167255</v>
+        <v>-29697.6753139283</v>
       </c>
       <c r="R100">
         <v>48.99999999999996</v>
       </c>
       <c r="S100">
-        <v>2.523422788921231</v>
+        <v>2.517264768722819</v>
       </c>
       <c r="T100">
-        <v>48.27092622177939</v>
+        <v>48.17344847736269</v>
       </c>
       <c r="U100">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V100">
-        <v>0.02763107182837549</v>
+        <v>0.02963587428725575</v>
       </c>
       <c r="W100">
-        <v>0.2156097962805507</v>
+        <v>0.2006097962805506</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9531,7 +9531,7 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.221048574627004</v>
+        <v>0.237086994298046</v>
       </c>
       <c r="Z100">
         <v>0</v>
@@ -9542,13 +9542,13 @@
         <v>0.99</v>
       </c>
       <c r="B101">
-        <v>0.2635254222999897</v>
+        <v>0.2485522618960214</v>
       </c>
       <c r="C101">
-        <v>-166085.1641143044</v>
+        <v>-162316.7467694598</v>
       </c>
       <c r="D101">
-        <v>51375.85163044252</v>
+        <v>55144.26897528708</v>
       </c>
       <c r="E101">
         <v>217757.1240833864</v>
@@ -9575,37 +9575,37 @@
         <v>10954.1</v>
       </c>
       <c r="M101">
-        <v>50060.83639889891</v>
+        <v>46674.32966272771</v>
       </c>
       <c r="N101">
-        <v>-39106.73639889892</v>
+        <v>-35720.22966272771</v>
       </c>
       <c r="O101">
-        <v>-4888.342049862365</v>
+        <v>-4465.028707840964</v>
       </c>
       <c r="P101">
-        <v>-34218.39434903655</v>
+        <v>-31255.20095488675</v>
       </c>
       <c r="Q101">
-        <v>-33073.39434903655</v>
+        <v>-30110.20095488675</v>
       </c>
       <c r="R101">
         <v>98.99999999999991</v>
       </c>
       <c r="S101">
-        <v>5.001045577842462</v>
+        <v>4.988729537445638</v>
       </c>
       <c r="T101">
-        <v>96.54185244355878</v>
+        <v>96.34689695472538</v>
       </c>
       <c r="U101">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V101">
-        <v>0.02735197009273534</v>
+        <v>0.02933652202172791</v>
       </c>
       <c r="W101">
-        <v>0.2156716833551161</v>
+        <v>0.2006716833551161</v>
       </c>
       <c r="X101" t="inlineStr">
         <is>
@@ -9613,7 +9613,7 @@
         </is>
       </c>
       <c r="Y101">
-        <v>0.2188157607418827</v>
+        <v>0.2346921761738233</v>
       </c>
       <c r="Z101">
         <v>0</v>

--- a/research/traditional_assets/database/data/ireland/ireland_computer_services.xlsx
+++ b/research/traditional_assets/database/data/ireland/ireland_computer_services.xlsx
@@ -1284,7 +1284,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1421,22 +1421,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.09670781914840654</v>
+        <v>0.09667825477026819</v>
       </c>
       <c r="C2">
-        <v>227931.011307795</v>
+        <v>225778.1552153249</v>
       </c>
       <c r="D2">
-        <v>219624.911307795</v>
+        <v>219752.5311319384</v>
       </c>
       <c r="E2">
-        <v>-8009.991661360522</v>
+        <v>-5729.515744746916</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>2280.475916613605</v>
       </c>
       <c r="G2">
         <v>8306.1</v>
@@ -1457,28 +1457,28 @@
         <v>10954.1</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>128.2462499307404</v>
       </c>
       <c r="N2">
-        <v>10954.1</v>
+        <v>10825.85375006926</v>
       </c>
       <c r="O2">
-        <v>1369.2625</v>
+        <v>1353.231718758657</v>
       </c>
       <c r="P2">
-        <v>9584.837499999998</v>
+        <v>9472.622031310601</v>
       </c>
       <c r="Q2">
-        <v>10729.8375</v>
+        <v>10617.6220313106</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.09670781914840654</v>
+        <v>0.09715776199441517</v>
       </c>
       <c r="T2">
-        <v>0.9922881498763956</v>
+        <v>1.001058373423283</v>
       </c>
       <c r="U2">
         <v>0.0562366166625341</v>
@@ -1495,7 +1495,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>85.41458331854363</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1503,22 +1503,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.09667825477026819</v>
+        <v>0.09664869039212985</v>
       </c>
       <c r="C3">
-        <v>225778.1552153249</v>
+        <v>223625.4475239524</v>
       </c>
       <c r="D3">
-        <v>219752.5311319384</v>
+        <v>219880.2993571796</v>
       </c>
       <c r="E3">
-        <v>-5729.515744746916</v>
+        <v>-3449.039828133311</v>
       </c>
       <c r="F3">
-        <v>2280.475916613605</v>
+        <v>4560.951833227211</v>
       </c>
       <c r="G3">
         <v>8306.1</v>
@@ -1539,28 +1539,28 @@
         <v>10954.1</v>
       </c>
       <c r="M3">
-        <v>128.2462499307404</v>
+        <v>256.4924998614808</v>
       </c>
       <c r="N3">
-        <v>10825.85375006926</v>
+        <v>10697.60750013852</v>
       </c>
       <c r="O3">
-        <v>1353.231718758657</v>
+        <v>1337.200937517315</v>
       </c>
       <c r="P3">
-        <v>9472.622031310601</v>
+        <v>9360.406562621203</v>
       </c>
       <c r="Q3">
-        <v>10617.6220313106</v>
+        <v>10505.4065626212</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.09715776199441517</v>
+        <v>0.09761688734748522</v>
       </c>
       <c r="T3">
-        <v>1.001058373423283</v>
+        <v>1.010007581124188</v>
       </c>
       <c r="U3">
         <v>0.0562366166625341</v>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>85.41458331854363</v>
+        <v>42.70729165927182</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1585,22 +1585,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.09664869039212985</v>
+        <v>0.09661912601399153</v>
       </c>
       <c r="C4">
-        <v>223625.4475239524</v>
+        <v>221472.8884926779</v>
       </c>
       <c r="D4">
-        <v>219880.2993571796</v>
+        <v>220008.2162425187</v>
       </c>
       <c r="E4">
-        <v>-3449.039828133311</v>
+        <v>-1168.563911519706</v>
       </c>
       <c r="F4">
-        <v>4560.951833227211</v>
+        <v>6841.427749840816</v>
       </c>
       <c r="G4">
         <v>8306.1</v>
@@ -1621,28 +1621,28 @@
         <v>10954.1</v>
       </c>
       <c r="M4">
-        <v>256.4924998614808</v>
+        <v>384.7387497922212</v>
       </c>
       <c r="N4">
-        <v>10697.60750013852</v>
+        <v>10569.36125020778</v>
       </c>
       <c r="O4">
-        <v>1337.200937517315</v>
+        <v>1321.170156275972</v>
       </c>
       <c r="P4">
-        <v>9360.406562621203</v>
+        <v>9248.191093931806</v>
       </c>
       <c r="Q4">
-        <v>10505.4065626212</v>
+        <v>10393.19109393181</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.09761688734748522</v>
+        <v>0.09808547920268042</v>
       </c>
       <c r="T4">
-        <v>1.010007581124188</v>
+        <v>1.019141308571504</v>
       </c>
       <c r="U4">
         <v>0.0562366166625341</v>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>42.70729165927182</v>
+        <v>28.47152777284789</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1667,22 +1667,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.09661912601399153</v>
+        <v>0.09658956163585318</v>
       </c>
       <c r="C5">
-        <v>221472.8884926779</v>
+        <v>219320.4783811045</v>
       </c>
       <c r="D5">
-        <v>220008.2162425187</v>
+        <v>220136.282047559</v>
       </c>
       <c r="E5">
-        <v>-1168.563911519706</v>
+        <v>1111.9120050939</v>
       </c>
       <c r="F5">
-        <v>6841.427749840816</v>
+        <v>9121.903666454422</v>
       </c>
       <c r="G5">
         <v>8306.1</v>
@@ -1703,28 +1703,28 @@
         <v>10954.1</v>
       </c>
       <c r="M5">
-        <v>384.7387497922212</v>
+        <v>512.9849997229617</v>
       </c>
       <c r="N5">
-        <v>10569.36125020778</v>
+        <v>10441.11500027704</v>
       </c>
       <c r="O5">
-        <v>1321.170156275972</v>
+        <v>1305.13937503463</v>
       </c>
       <c r="P5">
-        <v>9248.191093931806</v>
+        <v>9135.975625242409</v>
       </c>
       <c r="Q5">
-        <v>10393.19109393181</v>
+        <v>10280.97562524241</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.09808547920268042</v>
+        <v>0.09856383338819218</v>
       </c>
       <c r="T5">
-        <v>1.019141308571504</v>
+        <v>1.028465322007306</v>
       </c>
       <c r="U5">
         <v>0.0562366166625341</v>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>28.47152777284789</v>
+        <v>21.35364582963591</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1749,22 +1749,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.09658956163585318</v>
+        <v>0.09655999725771486</v>
       </c>
       <c r="C6">
-        <v>219320.4783811045</v>
+        <v>217168.2174494402</v>
       </c>
       <c r="D6">
-        <v>220136.282047559</v>
+        <v>220264.4970325082</v>
       </c>
       <c r="E6">
-        <v>1111.9120050939</v>
+        <v>3392.387921707505</v>
       </c>
       <c r="F6">
-        <v>9121.903666454422</v>
+        <v>11402.37958306803</v>
       </c>
       <c r="G6">
         <v>8306.1</v>
@@ -1785,28 +1785,28 @@
         <v>10954.1</v>
       </c>
       <c r="M6">
-        <v>512.9849997229617</v>
+        <v>641.231249653702</v>
       </c>
       <c r="N6">
-        <v>10441.11500027704</v>
+        <v>10312.8687503463</v>
       </c>
       <c r="O6">
-        <v>1305.13937503463</v>
+        <v>1289.108593793287</v>
       </c>
       <c r="P6">
-        <v>9135.975625242409</v>
+        <v>9023.760156553009</v>
       </c>
       <c r="Q6">
-        <v>10280.97562524241</v>
+        <v>10168.76015655301</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.09856383338819218</v>
+        <v>0.09905225818813579</v>
       </c>
       <c r="T6">
-        <v>1.028465322007306</v>
+        <v>1.037985630462809</v>
       </c>
       <c r="U6">
         <v>0.0562366166625341</v>
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>21.35364582963591</v>
+        <v>17.08291666370873</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1831,22 +1831,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.09655999725771486</v>
+        <v>0.09653043287957651</v>
       </c>
       <c r="C7">
-        <v>217168.2174494402</v>
+        <v>215016.1059584994</v>
       </c>
       <c r="D7">
-        <v>220264.4970325082</v>
+        <v>220392.861458181</v>
       </c>
       <c r="E7">
-        <v>3392.387921707505</v>
+        <v>5672.863838321111</v>
       </c>
       <c r="F7">
-        <v>11402.37958306803</v>
+        <v>13682.85549968163</v>
       </c>
       <c r="G7">
         <v>8306.1</v>
@@ -1867,28 +1867,28 @@
         <v>10954.1</v>
       </c>
       <c r="M7">
-        <v>641.231249653702</v>
+        <v>769.4774995844425</v>
       </c>
       <c r="N7">
-        <v>10312.8687503463</v>
+        <v>10184.62250041556</v>
       </c>
       <c r="O7">
-        <v>1289.108593793287</v>
+        <v>1273.077812551945</v>
       </c>
       <c r="P7">
-        <v>9023.760156553009</v>
+        <v>8911.544687863612</v>
       </c>
       <c r="Q7">
-        <v>10168.76015655301</v>
+        <v>10056.54468786361</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.09905225818813579</v>
+        <v>0.09955107500509945</v>
       </c>
       <c r="T7">
-        <v>1.037985630462809</v>
+        <v>1.047708498672684</v>
       </c>
       <c r="U7">
         <v>0.0562366166625341</v>
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>17.08291666370873</v>
+        <v>14.23576388642394</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1913,22 +1913,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.09653043287957651</v>
+        <v>0.0965008685014382</v>
       </c>
       <c r="C8">
-        <v>215016.1059584994</v>
+        <v>212864.1441697049</v>
       </c>
       <c r="D8">
-        <v>220392.861458181</v>
+        <v>220521.3755860001</v>
       </c>
       <c r="E8">
-        <v>5672.863838321109</v>
+        <v>7953.339754934714</v>
       </c>
       <c r="F8">
-        <v>13682.85549968163</v>
+        <v>15963.33141629524</v>
       </c>
       <c r="G8">
         <v>8306.1</v>
@@ -1949,28 +1949,28 @@
         <v>10954.1</v>
       </c>
       <c r="M8">
-        <v>769.4774995844424</v>
+        <v>897.7237495151827</v>
       </c>
       <c r="N8">
-        <v>10184.62250041556</v>
+        <v>10056.37625048482</v>
       </c>
       <c r="O8">
-        <v>1273.077812551945</v>
+        <v>1257.047031310602</v>
       </c>
       <c r="P8">
-        <v>8911.544687863612</v>
+        <v>8799.329219174215</v>
       </c>
       <c r="Q8">
-        <v>10056.54468786361</v>
+        <v>9944.329219174215</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.09955107500509945</v>
+        <v>0.1000606190654387</v>
       </c>
       <c r="T8">
-        <v>1.047708498672684</v>
+        <v>1.057640460822556</v>
       </c>
       <c r="U8">
         <v>0.0562366166625341</v>
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>14.23576388642394</v>
+        <v>12.20208333122052</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1995,22 +1995,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.09650086850143819</v>
+        <v>0.09647130412329986</v>
       </c>
       <c r="C9">
-        <v>212864.1441697049</v>
+        <v>210712.3323450899</v>
       </c>
       <c r="D9">
-        <v>220521.3755860002</v>
+        <v>220650.0396779987</v>
       </c>
       <c r="E9">
-        <v>7953.339754934716</v>
+        <v>10233.81567154832</v>
       </c>
       <c r="F9">
-        <v>15963.33141629524</v>
+        <v>18243.80733290884</v>
       </c>
       <c r="G9">
         <v>8306.1</v>
@@ -2031,28 +2031,28 @@
         <v>10954.1</v>
       </c>
       <c r="M9">
-        <v>897.7237495151828</v>
+        <v>1025.969999445923</v>
       </c>
       <c r="N9">
-        <v>10056.37625048482</v>
+        <v>9928.130000554076</v>
       </c>
       <c r="O9">
-        <v>1257.047031310602</v>
+        <v>1241.01625006926</v>
       </c>
       <c r="P9">
-        <v>8799.329219174215</v>
+        <v>8687.113750484816</v>
       </c>
       <c r="Q9">
-        <v>9944.329219174215</v>
+        <v>9832.113750484816</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1000606190654387</v>
+        <v>0.1005812401705679</v>
       </c>
       <c r="T9">
-        <v>1.057640460822556</v>
+        <v>1.067788335193078</v>
       </c>
       <c r="U9">
         <v>0.0562366166625341</v>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>12.20208333122052</v>
+        <v>10.67682291481796</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2077,22 +2077,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.09647130412329986</v>
+        <v>0.09644173974516151</v>
       </c>
       <c r="C10">
-        <v>210712.3323450899</v>
+        <v>208560.6707472992</v>
       </c>
       <c r="D10">
-        <v>220650.0396779987</v>
+        <v>220778.8539968217</v>
       </c>
       <c r="E10">
-        <v>10233.81567154832</v>
+        <v>12514.29158816192</v>
       </c>
       <c r="F10">
-        <v>18243.80733290884</v>
+        <v>20524.28324952245</v>
       </c>
       <c r="G10">
         <v>8306.1</v>
@@ -2113,28 +2113,28 @@
         <v>10954.1</v>
       </c>
       <c r="M10">
-        <v>1025.969999445923</v>
+        <v>1154.216249376664</v>
       </c>
       <c r="N10">
-        <v>9928.130000554076</v>
+        <v>9799.883750623336</v>
       </c>
       <c r="O10">
-        <v>1241.01625006926</v>
+        <v>1224.985468827917</v>
       </c>
       <c r="P10">
-        <v>8687.113750484816</v>
+        <v>8574.898281795418</v>
       </c>
       <c r="Q10">
-        <v>9832.113750484816</v>
+        <v>9719.898281795418</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1005812401705679</v>
+        <v>0.1011133034977879</v>
       </c>
       <c r="T10">
-        <v>1.067788335193078</v>
+        <v>1.078159239769545</v>
       </c>
       <c r="U10">
         <v>0.0562366166625341</v>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>10.67682291481796</v>
+        <v>9.490509257615962</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.09644173974516151</v>
+        <v>0.09654342536702318</v>
       </c>
       <c r="C11">
-        <v>208560.6707472992</v>
+        <v>205837.7722921953</v>
       </c>
       <c r="D11">
-        <v>220778.8539968217</v>
+        <v>220336.4314583314</v>
       </c>
       <c r="E11">
-        <v>12514.29158816192</v>
+        <v>14794.76750477553</v>
       </c>
       <c r="F11">
-        <v>20524.28324952245</v>
+        <v>22804.75916613605</v>
       </c>
       <c r="G11">
         <v>8306.1</v>
@@ -2195,45 +2195,45 @@
         <v>10954.1</v>
       </c>
       <c r="M11">
-        <v>1154.216249376664</v>
+        <v>1316.669638056608</v>
       </c>
       <c r="N11">
-        <v>9799.883750623336</v>
+        <v>9637.43036194339</v>
       </c>
       <c r="O11">
-        <v>1224.985468827917</v>
+        <v>1204.678795242924</v>
       </c>
       <c r="P11">
-        <v>8574.898281795418</v>
+        <v>8432.751566700466</v>
       </c>
       <c r="Q11">
-        <v>9719.898281795418</v>
+        <v>9577.751566700466</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1011133034977879</v>
+        <v>0.1016571904545016</v>
       </c>
       <c r="T11">
-        <v>1.078159239769545</v>
+        <v>1.088760608892156</v>
       </c>
       <c r="U11">
-        <v>0.0562366166625341</v>
+        <v>0.05773661666253409</v>
       </c>
       <c r="V11">
         <v>0.125</v>
       </c>
       <c r="W11">
-        <v>0.04920703957971734</v>
+        <v>0.05051953957971733</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y11">
-        <v>9.490509257615962</v>
+        <v>8.319550845091371</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2241,22 +2241,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.09654342536702318</v>
+        <v>0.09652698598888484</v>
       </c>
       <c r="C12">
-        <v>205837.7722921953</v>
+        <v>203628.7020355826</v>
       </c>
       <c r="D12">
-        <v>220336.4314583314</v>
+        <v>220407.8371183323</v>
       </c>
       <c r="E12">
-        <v>14794.76750477553</v>
+        <v>17075.24342138914</v>
       </c>
       <c r="F12">
-        <v>22804.75916613605</v>
+        <v>25085.23508274966</v>
       </c>
       <c r="G12">
         <v>8306.1</v>
@@ -2277,28 +2277,28 @@
         <v>10954.1</v>
       </c>
       <c r="M12">
-        <v>1316.669638056608</v>
+        <v>1448.336601862269</v>
       </c>
       <c r="N12">
-        <v>9637.43036194339</v>
+        <v>9505.763398137729</v>
       </c>
       <c r="O12">
-        <v>1204.678795242924</v>
+        <v>1188.220424767216</v>
       </c>
       <c r="P12">
-        <v>8432.751566700466</v>
+        <v>8317.542973370513</v>
       </c>
       <c r="Q12">
-        <v>9577.751566700466</v>
+        <v>9462.542973370513</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1016571904545016</v>
+        <v>0.1022132995900179</v>
       </c>
       <c r="T12">
-        <v>1.088760608892156</v>
+        <v>1.099600211028759</v>
       </c>
       <c r="U12">
         <v>0.05773661666253409</v>
@@ -2315,7 +2315,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>8.319550845091367</v>
+        <v>7.563228040992152</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2323,22 +2323,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.09652698598888484</v>
+        <v>0.09651054661074651</v>
       </c>
       <c r="C13">
-        <v>203628.7020355826</v>
+        <v>201419.678075637</v>
       </c>
       <c r="D13">
-        <v>220407.8371183323</v>
+        <v>220479.2890750003</v>
       </c>
       <c r="E13">
-        <v>17075.24342138914</v>
+        <v>19355.71933800274</v>
       </c>
       <c r="F13">
-        <v>25085.23508274966</v>
+        <v>27365.71099936326</v>
       </c>
       <c r="G13">
         <v>8306.1</v>
@@ -2359,28 +2359,28 @@
         <v>10954.1</v>
       </c>
       <c r="M13">
-        <v>1448.336601862269</v>
+        <v>1580.003565667929</v>
       </c>
       <c r="N13">
-        <v>9505.763398137729</v>
+        <v>9374.096434332068</v>
       </c>
       <c r="O13">
-        <v>1188.220424767216</v>
+        <v>1171.762054291509</v>
       </c>
       <c r="P13">
-        <v>8317.542973370513</v>
+        <v>8202.33438004056</v>
       </c>
       <c r="Q13">
-        <v>9462.542973370513</v>
+        <v>9347.33438004056</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1022132995900179</v>
+        <v>0.1027820475695232</v>
       </c>
       <c r="T13">
-        <v>1.099600211028759</v>
+        <v>1.110686167759375</v>
       </c>
       <c r="U13">
         <v>0.05773661666253409</v>
@@ -2397,7 +2397,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>7.563228040992152</v>
+        <v>6.93295903757614</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2405,22 +2405,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.09651054661074651</v>
+        <v>0.09668748223260819</v>
       </c>
       <c r="C14">
-        <v>201419.678075637</v>
+        <v>198372.5963375409</v>
       </c>
       <c r="D14">
-        <v>220479.2890750003</v>
+        <v>219712.6832535178</v>
       </c>
       <c r="E14">
-        <v>19355.71933800274</v>
+        <v>21636.19525461634</v>
       </c>
       <c r="F14">
-        <v>27365.71099936326</v>
+        <v>29646.18691597687</v>
       </c>
       <c r="G14">
         <v>8306.1</v>
@@ -2441,45 +2441,45 @@
         <v>10954.1</v>
       </c>
       <c r="M14">
-        <v>1580.003565667929</v>
+        <v>1762.069047230751</v>
       </c>
       <c r="N14">
-        <v>9374.096434332068</v>
+        <v>9192.030952769248</v>
       </c>
       <c r="O14">
-        <v>1171.762054291509</v>
+        <v>1149.003869096156</v>
       </c>
       <c r="P14">
-        <v>8202.33438004056</v>
+        <v>8043.027083673092</v>
       </c>
       <c r="Q14">
-        <v>9347.33438004056</v>
+        <v>9188.027083673092</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1027820475695232</v>
+        <v>0.1033638702152241</v>
       </c>
       <c r="T14">
-        <v>1.110686167759375</v>
+        <v>1.122026974070005</v>
       </c>
       <c r="U14">
-        <v>0.05773661666253409</v>
+        <v>0.05943661666253409</v>
       </c>
       <c r="V14">
         <v>0.125</v>
       </c>
       <c r="W14">
-        <v>0.05051953957971733</v>
+        <v>0.05200703957971733</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y14">
-        <v>6.93295903757614</v>
+        <v>6.21661223617505</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2487,22 +2487,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.09668748223260819</v>
+        <v>0.09668591785446984</v>
       </c>
       <c r="C15">
-        <v>198372.5963375409</v>
+        <v>196098.8750149857</v>
       </c>
       <c r="D15">
-        <v>219712.6832535178</v>
+        <v>219719.4378475762</v>
       </c>
       <c r="E15">
-        <v>21636.19525461634</v>
+        <v>23916.67117122995</v>
       </c>
       <c r="F15">
-        <v>29646.18691597687</v>
+        <v>31926.66283259047</v>
       </c>
       <c r="G15">
         <v>8306.1</v>
@@ -2523,28 +2523,28 @@
         <v>10954.1</v>
       </c>
       <c r="M15">
-        <v>1762.069047230751</v>
+        <v>1897.612820094655</v>
       </c>
       <c r="N15">
-        <v>9192.030952769248</v>
+        <v>9056.487179905344</v>
       </c>
       <c r="O15">
-        <v>1149.003869096156</v>
+        <v>1132.060897488168</v>
       </c>
       <c r="P15">
-        <v>8043.027083673092</v>
+        <v>7924.426282417176</v>
       </c>
       <c r="Q15">
-        <v>9188.027083673092</v>
+        <v>9069.426282417175</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1033638702152241</v>
+        <v>0.1039592236201272</v>
       </c>
       <c r="T15">
-        <v>1.122026974070005</v>
+        <v>1.133631520062278</v>
       </c>
       <c r="U15">
         <v>0.05943661666253409</v>
@@ -2561,7 +2561,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>6.21661223617505</v>
+        <v>5.772568505019689</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2569,22 +2569,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.09668591785446984</v>
+        <v>0.09678935347633151</v>
       </c>
       <c r="C16">
-        <v>196098.8750149857</v>
+        <v>193372.6821959327</v>
       </c>
       <c r="D16">
-        <v>219719.4378475762</v>
+        <v>219273.7209451368</v>
       </c>
       <c r="E16">
-        <v>23916.67117122995</v>
+        <v>26197.14708784356</v>
       </c>
       <c r="F16">
-        <v>31926.66283259047</v>
+        <v>34207.13874920408</v>
       </c>
       <c r="G16">
         <v>8306.1</v>
@@ -2605,45 +2605,45 @@
         <v>10954.1</v>
       </c>
       <c r="M16">
-        <v>1897.612820094655</v>
+        <v>2060.522303957922</v>
       </c>
       <c r="N16">
-        <v>9056.487179905344</v>
+        <v>8893.577696042077</v>
       </c>
       <c r="O16">
-        <v>1132.060897488168</v>
+        <v>1111.69721200526</v>
       </c>
       <c r="P16">
-        <v>7924.426282417176</v>
+        <v>7781.880484036818</v>
       </c>
       <c r="Q16">
-        <v>9069.426282417175</v>
+        <v>8926.880484036818</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1039592236201272</v>
+        <v>0.1045685853404399</v>
       </c>
       <c r="T16">
-        <v>1.133631520062278</v>
+        <v>1.145509114195545</v>
       </c>
       <c r="U16">
-        <v>0.05943661666253409</v>
+        <v>0.0602366166625341</v>
       </c>
       <c r="V16">
         <v>0.125</v>
       </c>
       <c r="W16">
-        <v>0.05200703957971733</v>
+        <v>0.05270703957971733</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y16">
-        <v>5.772568505019689</v>
+        <v>5.316176378658453</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2651,22 +2651,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.09678935347633151</v>
+        <v>0.09679478909819317</v>
       </c>
       <c r="C17">
-        <v>193372.6821959327</v>
+        <v>191068.833518056</v>
       </c>
       <c r="D17">
-        <v>219273.7209451368</v>
+        <v>219250.3481838736</v>
       </c>
       <c r="E17">
-        <v>26197.14708784355</v>
+        <v>28477.62300445716</v>
       </c>
       <c r="F17">
-        <v>34207.13874920407</v>
+        <v>36487.61466581769</v>
       </c>
       <c r="G17">
         <v>8306.1</v>
@@ -2687,28 +2687,28 @@
         <v>10954.1</v>
       </c>
       <c r="M17">
-        <v>2060.522303957922</v>
+        <v>2197.890457555117</v>
       </c>
       <c r="N17">
-        <v>8893.577696042077</v>
+        <v>8756.209542444882</v>
       </c>
       <c r="O17">
-        <v>1111.69721200526</v>
+        <v>1094.52619280561</v>
       </c>
       <c r="P17">
-        <v>7781.880484036818</v>
+        <v>7661.683349639272</v>
       </c>
       <c r="Q17">
-        <v>8926.880484036818</v>
+        <v>8806.683349639272</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1045685853404399</v>
+        <v>0.1051924556731409</v>
       </c>
       <c r="T17">
-        <v>1.145509114195545</v>
+        <v>1.157669508189128</v>
       </c>
       <c r="U17">
         <v>0.0602366166625341</v>
@@ -2725,7 +2725,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>5.316176378658453</v>
+        <v>4.983915354992298</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2733,22 +2733,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.09679478909819317</v>
+        <v>0.09680022472005483</v>
       </c>
       <c r="C18">
-        <v>191068.833518056</v>
+        <v>188764.9898223334</v>
       </c>
       <c r="D18">
-        <v>219250.3481838736</v>
+        <v>219226.9804047647</v>
       </c>
       <c r="E18">
-        <v>28477.62300445716</v>
+        <v>30758.09892107077</v>
       </c>
       <c r="F18">
-        <v>36487.61466581769</v>
+        <v>38768.09058243129</v>
       </c>
       <c r="G18">
         <v>8306.1</v>
@@ -2769,28 +2769,28 @@
         <v>10954.1</v>
       </c>
       <c r="M18">
-        <v>2197.890457555117</v>
+        <v>2335.258611152312</v>
       </c>
       <c r="N18">
-        <v>8756.209542444882</v>
+        <v>8618.841388847686</v>
       </c>
       <c r="O18">
-        <v>1094.52619280561</v>
+        <v>1077.355173605961</v>
       </c>
       <c r="P18">
-        <v>7661.683349639272</v>
+        <v>7541.486215241725</v>
       </c>
       <c r="Q18">
-        <v>8806.683349639272</v>
+        <v>8686.486215241726</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1051924556731409</v>
+        <v>0.1058313590259071</v>
       </c>
       <c r="T18">
-        <v>1.157669508189128</v>
+        <v>1.170122923724725</v>
       </c>
       <c r="U18">
         <v>0.0602366166625341</v>
@@ -2807,7 +2807,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>4.983915354992298</v>
+        <v>4.690743863522163</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2815,22 +2815,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.09680022472005483</v>
+        <v>0.09680566034191651</v>
       </c>
       <c r="C19">
-        <v>188764.9898223334</v>
+        <v>186461.1511071721</v>
       </c>
       <c r="D19">
-        <v>219226.9804047647</v>
+        <v>219203.617606217</v>
       </c>
       <c r="E19">
-        <v>30758.09892107077</v>
+        <v>33038.57483768438</v>
       </c>
       <c r="F19">
-        <v>38768.09058243129</v>
+        <v>41048.5664990449</v>
       </c>
       <c r="G19">
         <v>8306.1</v>
@@ -2851,28 +2851,28 @@
         <v>10954.1</v>
       </c>
       <c r="M19">
-        <v>2335.258611152312</v>
+        <v>2472.626764749507</v>
       </c>
       <c r="N19">
-        <v>8618.841388847686</v>
+        <v>8481.473235250491</v>
       </c>
       <c r="O19">
-        <v>1077.355173605961</v>
+        <v>1060.184154406311</v>
       </c>
       <c r="P19">
-        <v>7541.486215241725</v>
+        <v>7421.289080844179</v>
       </c>
       <c r="Q19">
-        <v>8686.486215241726</v>
+        <v>8566.289080844179</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1058313590259071</v>
+        <v>0.1064858453872773</v>
       </c>
       <c r="T19">
-        <v>1.170122923724725</v>
+        <v>1.182880081102655</v>
       </c>
       <c r="U19">
         <v>0.0602366166625341</v>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>4.690743863522163</v>
+        <v>4.430146982215376</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2897,22 +2897,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.09680566034191651</v>
+        <v>0.09697734596377817</v>
       </c>
       <c r="C20">
-        <v>186461.1511071721</v>
+        <v>183445.3086197776</v>
       </c>
       <c r="D20">
-        <v>219203.617606217</v>
+        <v>218468.2510354361</v>
       </c>
       <c r="E20">
-        <v>33038.57483768437</v>
+        <v>35319.05075429798</v>
       </c>
       <c r="F20">
-        <v>41048.56649904489</v>
+        <v>43329.0424156585</v>
       </c>
       <c r="G20">
         <v>8306.1</v>
@@ -2933,45 +2933,45 @@
         <v>10954.1</v>
       </c>
       <c r="M20">
-        <v>2472.626764749506</v>
+        <v>2653.32396076236</v>
       </c>
       <c r="N20">
-        <v>8481.473235250493</v>
+        <v>8300.776039237639</v>
       </c>
       <c r="O20">
-        <v>1060.184154406312</v>
+        <v>1037.597004904705</v>
       </c>
       <c r="P20">
-        <v>7421.289080844181</v>
+        <v>7263.179034332934</v>
       </c>
       <c r="Q20">
-        <v>8566.289080844181</v>
+        <v>8408.179034332934</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1064858453872773</v>
+        <v>0.1071564919057184</v>
       </c>
       <c r="T20">
-        <v>1.182880081102655</v>
+        <v>1.195952230020779</v>
       </c>
       <c r="U20">
-        <v>0.0602366166625341</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V20">
         <v>0.125</v>
       </c>
       <c r="W20">
-        <v>0.05270703957971733</v>
+        <v>0.05358203957971733</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y20">
-        <v>4.430146982215378</v>
+        <v>4.128444231458506</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2979,22 +2979,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.09697734596377817</v>
+        <v>0.09699153158563983</v>
       </c>
       <c r="C21">
-        <v>183445.3086197776</v>
+        <v>181104.2932369287</v>
       </c>
       <c r="D21">
-        <v>218468.2510354361</v>
+        <v>218407.7115692008</v>
       </c>
       <c r="E21">
-        <v>35319.05075429798</v>
+        <v>37599.52667091158</v>
       </c>
       <c r="F21">
-        <v>43329.0424156585</v>
+        <v>45609.51833227211</v>
       </c>
       <c r="G21">
         <v>8306.1</v>
@@ -3015,28 +3015,28 @@
         <v>10954.1</v>
       </c>
       <c r="M21">
-        <v>2653.32396076236</v>
+        <v>2792.972590276168</v>
       </c>
       <c r="N21">
-        <v>8300.776039237639</v>
+        <v>8161.12740972383</v>
       </c>
       <c r="O21">
-        <v>1037.597004904705</v>
+        <v>1020.140926215479</v>
       </c>
       <c r="P21">
-        <v>7263.179034332934</v>
+        <v>7140.986483508352</v>
       </c>
       <c r="Q21">
-        <v>8408.179034332934</v>
+        <v>8285.986483508352</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1071564919057184</v>
+        <v>0.1078439045871205</v>
       </c>
       <c r="T21">
-        <v>1.195952230020779</v>
+        <v>1.209351182661857</v>
       </c>
       <c r="U21">
         <v>0.0612366166625341</v>
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>4.128444231458506</v>
+        <v>3.92202201988558</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3061,22 +3061,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.09699153158563983</v>
+        <v>0.09700571720750149</v>
       </c>
       <c r="C22">
-        <v>181104.2932369287</v>
+        <v>178763.3113968176</v>
       </c>
       <c r="D22">
-        <v>218407.7115692008</v>
+        <v>218347.2056457033</v>
       </c>
       <c r="E22">
-        <v>37599.52667091158</v>
+        <v>39880.00258752519</v>
       </c>
       <c r="F22">
-        <v>45609.51833227211</v>
+        <v>47889.99424888571</v>
       </c>
       <c r="G22">
         <v>8306.1</v>
@@ -3097,28 +3097,28 @@
         <v>10954.1</v>
       </c>
       <c r="M22">
-        <v>2792.972590276168</v>
+        <v>2932.621219789977</v>
       </c>
       <c r="N22">
-        <v>8161.12740972383</v>
+        <v>8021.478780210022</v>
       </c>
       <c r="O22">
-        <v>1020.140926215479</v>
+        <v>1002.684847526253</v>
       </c>
       <c r="P22">
-        <v>7140.986483508352</v>
+        <v>7018.79393268377</v>
       </c>
       <c r="Q22">
-        <v>8285.986483508352</v>
+        <v>8163.79393268377</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1078439045871205</v>
+        <v>0.1085487201212163</v>
       </c>
       <c r="T22">
-        <v>1.209351182661857</v>
+        <v>1.223089349293848</v>
       </c>
       <c r="U22">
         <v>0.0612366166625341</v>
@@ -3135,7 +3135,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>3.92202201988558</v>
+        <v>3.735259066557695</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3143,22 +3143,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.09700571720750149</v>
+        <v>0.09701990282936318</v>
       </c>
       <c r="C23">
-        <v>178763.3113968176</v>
+        <v>176422.3630715747</v>
       </c>
       <c r="D23">
-        <v>218347.2056457033</v>
+        <v>218286.733237074</v>
       </c>
       <c r="E23">
-        <v>39880.00258752518</v>
+        <v>42160.47850413879</v>
       </c>
       <c r="F23">
-        <v>47889.99424888571</v>
+        <v>50170.47016549932</v>
       </c>
       <c r="G23">
         <v>8306.1</v>
@@ -3179,28 +3179,28 @@
         <v>10954.1</v>
       </c>
       <c r="M23">
-        <v>2932.621219789976</v>
+        <v>3072.269849303786</v>
       </c>
       <c r="N23">
-        <v>8021.478780210022</v>
+        <v>7881.830150696213</v>
       </c>
       <c r="O23">
-        <v>1002.684847526253</v>
+        <v>985.2287688370266</v>
       </c>
       <c r="P23">
-        <v>7018.79393268377</v>
+        <v>6896.601381859185</v>
       </c>
       <c r="Q23">
-        <v>8163.79393268377</v>
+        <v>8041.601381859185</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1085487201212163</v>
+        <v>0.109271607848494</v>
       </c>
       <c r="T23">
-        <v>1.223089349293848</v>
+        <v>1.237179776608711</v>
       </c>
       <c r="U23">
         <v>0.0612366166625341</v>
@@ -3217,7 +3217,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>3.735259066557696</v>
+        <v>3.565474563532345</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.09701990282936318</v>
+        <v>0.09703408845122483</v>
       </c>
       <c r="C24">
-        <v>176422.3630715747</v>
+        <v>174081.4482333618</v>
       </c>
       <c r="D24">
-        <v>218286.733237074</v>
+        <v>218226.2943154747</v>
       </c>
       <c r="E24">
-        <v>42160.47850413879</v>
+        <v>44440.9544207524</v>
       </c>
       <c r="F24">
-        <v>50170.47016549932</v>
+        <v>52450.94608211293</v>
       </c>
       <c r="G24">
         <v>8306.1</v>
@@ -3261,28 +3261,28 @@
         <v>10954.1</v>
       </c>
       <c r="M24">
-        <v>3072.269849303786</v>
+        <v>3211.918478817594</v>
       </c>
       <c r="N24">
-        <v>7881.830150696213</v>
+        <v>7742.181521182405</v>
       </c>
       <c r="O24">
-        <v>985.2287688370266</v>
+        <v>967.7726901478006</v>
       </c>
       <c r="P24">
-        <v>6896.601381859185</v>
+        <v>6774.408831034604</v>
       </c>
       <c r="Q24">
-        <v>8041.601381859185</v>
+        <v>7919.408831034604</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.109271607848494</v>
+        <v>0.1100132718803764</v>
       </c>
       <c r="T24">
-        <v>1.237179776608711</v>
+        <v>1.251636189048635</v>
       </c>
       <c r="U24">
         <v>0.0612366166625341</v>
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>3.565474563532345</v>
+        <v>3.410453930335287</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3307,22 +3307,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.09703408845122483</v>
+        <v>0.0970482740730865</v>
       </c>
       <c r="C25">
-        <v>174081.4482333618</v>
+        <v>171740.5668543708</v>
       </c>
       <c r="D25">
-        <v>218226.2943154747</v>
+        <v>218165.8888530973</v>
       </c>
       <c r="E25">
-        <v>44440.9544207524</v>
+        <v>46721.43033736601</v>
       </c>
       <c r="F25">
-        <v>52450.94608211293</v>
+        <v>54731.42199872653</v>
       </c>
       <c r="G25">
         <v>8306.1</v>
@@ -3343,28 +3343,28 @@
         <v>10954.1</v>
       </c>
       <c r="M25">
-        <v>3211.918478817594</v>
+        <v>3351.567108331402</v>
       </c>
       <c r="N25">
-        <v>7742.181521182405</v>
+        <v>7602.532891668596</v>
       </c>
       <c r="O25">
-        <v>967.7726901478006</v>
+        <v>950.3166114585745</v>
       </c>
       <c r="P25">
-        <v>6774.408831034604</v>
+        <v>6652.216280210021</v>
       </c>
       <c r="Q25">
-        <v>7919.408831034604</v>
+        <v>7797.216280210021</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1100132718803764</v>
+        <v>0.110774453386782</v>
       </c>
       <c r="T25">
-        <v>1.251636189048635</v>
+        <v>1.266473033394873</v>
       </c>
       <c r="U25">
         <v>0.0612366166625341</v>
@@ -3381,7 +3381,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>3.410453930335287</v>
+        <v>3.268351683237983</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3389,22 +3389,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.0970482740730865</v>
+        <v>0.09706245969494816</v>
       </c>
       <c r="C26">
-        <v>171740.5668543708</v>
+        <v>169399.7189068246</v>
       </c>
       <c r="D26">
-        <v>218165.8888530973</v>
+        <v>218105.5168221647</v>
       </c>
       <c r="E26">
-        <v>46721.430337366</v>
+        <v>49001.90625397961</v>
       </c>
       <c r="F26">
-        <v>54731.42199872652</v>
+        <v>57011.89791534013</v>
       </c>
       <c r="G26">
         <v>8306.1</v>
@@ -3425,28 +3425,28 @@
         <v>10954.1</v>
       </c>
       <c r="M26">
-        <v>3351.567108331402</v>
+        <v>3491.21573784521</v>
       </c>
       <c r="N26">
-        <v>7602.532891668597</v>
+        <v>7462.884262154788</v>
       </c>
       <c r="O26">
-        <v>950.3166114585746</v>
+        <v>932.8605327693485</v>
       </c>
       <c r="P26">
-        <v>6652.216280210022</v>
+        <v>6530.02372938544</v>
       </c>
       <c r="Q26">
-        <v>7797.216280210022</v>
+        <v>7675.02372938544</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.110774453386782</v>
+        <v>0.1115559330666918</v>
       </c>
       <c r="T26">
-        <v>1.266473033394873</v>
+        <v>1.281705526923677</v>
       </c>
       <c r="U26">
         <v>0.0612366166625341</v>
@@ -3463,7 +3463,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>3.268351683237984</v>
+        <v>3.137617615908464</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3471,22 +3471,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.09706245969494816</v>
+        <v>0.09707664531680983</v>
       </c>
       <c r="C27">
-        <v>169399.7189068246</v>
+        <v>167058.9043629769</v>
       </c>
       <c r="D27">
-        <v>218105.5168221647</v>
+        <v>218045.1781949306</v>
       </c>
       <c r="E27">
-        <v>49001.90625397961</v>
+        <v>51282.38217059321</v>
       </c>
       <c r="F27">
-        <v>57011.89791534013</v>
+        <v>59292.37383195374</v>
       </c>
       <c r="G27">
         <v>8306.1</v>
@@ -3507,28 +3507,28 @@
         <v>10954.1</v>
       </c>
       <c r="M27">
-        <v>3491.21573784521</v>
+        <v>3630.864367359019</v>
       </c>
       <c r="N27">
-        <v>7462.884262154788</v>
+        <v>7323.235632640979</v>
       </c>
       <c r="O27">
-        <v>932.8605327693485</v>
+        <v>915.4044540801224</v>
       </c>
       <c r="P27">
-        <v>6530.02372938544</v>
+        <v>6407.831178560857</v>
       </c>
       <c r="Q27">
-        <v>7675.02372938544</v>
+        <v>7552.831178560857</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1115559330666918</v>
+        <v>0.1123585338190315</v>
       </c>
       <c r="T27">
-        <v>1.281705526923677</v>
+        <v>1.297349709466774</v>
       </c>
       <c r="U27">
         <v>0.0612366166625341</v>
@@ -3545,7 +3545,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>3.137617615908464</v>
+        <v>3.0169400152966</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3553,22 +3553,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.09707664531680983</v>
+        <v>0.09768145593867149</v>
       </c>
       <c r="C28">
-        <v>167058.9043629769</v>
+        <v>162236.5560676486</v>
       </c>
       <c r="D28">
-        <v>218045.1781949306</v>
+        <v>215503.305816216</v>
       </c>
       <c r="E28">
-        <v>51282.38217059321</v>
+        <v>53562.85808720682</v>
       </c>
       <c r="F28">
-        <v>59292.37383195374</v>
+        <v>61572.84974856734</v>
       </c>
       <c r="G28">
         <v>8306.1</v>
@@ -3589,45 +3589,45 @@
         <v>10954.1</v>
       </c>
       <c r="M28">
-        <v>3630.864367359019</v>
+        <v>3924.445121244245</v>
       </c>
       <c r="N28">
-        <v>7323.235632640979</v>
+        <v>7029.654878755753</v>
       </c>
       <c r="O28">
-        <v>915.4044540801224</v>
+        <v>878.7068598444691</v>
       </c>
       <c r="P28">
-        <v>6407.831178560857</v>
+        <v>6150.948018911284</v>
       </c>
       <c r="Q28">
-        <v>7552.831178560857</v>
+        <v>7295.948018911284</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1123585338190315</v>
+        <v>0.1131831236330792</v>
       </c>
       <c r="T28">
-        <v>1.297349709466774</v>
+        <v>1.313422499750777</v>
       </c>
       <c r="U28">
-        <v>0.0612366166625341</v>
+        <v>0.06373661666253409</v>
       </c>
       <c r="V28">
         <v>0.125</v>
       </c>
       <c r="W28">
-        <v>0.05358203957971733</v>
+        <v>0.05576953957971733</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y28">
-        <v>3.0169400152966</v>
+        <v>2.791248102999845</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3635,22 +3635,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.09768145593867149</v>
+        <v>0.09771751656053317</v>
       </c>
       <c r="C29">
-        <v>162236.5560676486</v>
+        <v>159806.3968892804</v>
       </c>
       <c r="D29">
-        <v>215503.305816216</v>
+        <v>215353.6225544614</v>
       </c>
       <c r="E29">
-        <v>53562.85808720682</v>
+        <v>55843.33400382043</v>
       </c>
       <c r="F29">
-        <v>61572.84974856734</v>
+        <v>63853.32566518095</v>
       </c>
       <c r="G29">
         <v>8306.1</v>
@@ -3671,28 +3671,28 @@
         <v>10954.1</v>
       </c>
       <c r="M29">
-        <v>3924.445121244245</v>
+        <v>4069.794940549588</v>
       </c>
       <c r="N29">
-        <v>7029.654878755753</v>
+        <v>6884.305059450411</v>
       </c>
       <c r="O29">
-        <v>878.7068598444691</v>
+        <v>860.5381324313014</v>
       </c>
       <c r="P29">
-        <v>6150.948018911284</v>
+        <v>6023.76692701911</v>
       </c>
       <c r="Q29">
-        <v>7295.948018911284</v>
+        <v>7168.76692701911</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1131831236330792</v>
+        <v>0.1140306187197393</v>
       </c>
       <c r="T29">
-        <v>1.313422499750777</v>
+        <v>1.329941756431558</v>
       </c>
       <c r="U29">
         <v>0.06373661666253409</v>
@@ -3709,7 +3709,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>2.791248102999845</v>
+        <v>2.691560670749851</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3717,22 +3717,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.09771751656053317</v>
+        <v>0.09775357718239483</v>
       </c>
       <c r="C30">
-        <v>159806.3968892804</v>
+        <v>157376.4454991645</v>
       </c>
       <c r="D30">
-        <v>215353.6225544614</v>
+        <v>215204.1470809591</v>
       </c>
       <c r="E30">
-        <v>55843.33400382043</v>
+        <v>58123.80992043403</v>
       </c>
       <c r="F30">
-        <v>63853.32566518095</v>
+        <v>66133.80158179456</v>
       </c>
       <c r="G30">
         <v>8306.1</v>
@@ -3753,28 +3753,28 @@
         <v>10954.1</v>
       </c>
       <c r="M30">
-        <v>4069.794940549588</v>
+        <v>4215.14475985493</v>
       </c>
       <c r="N30">
-        <v>6884.305059450411</v>
+        <v>6738.955240145068</v>
       </c>
       <c r="O30">
-        <v>860.5381324313014</v>
+        <v>842.3694050181335</v>
       </c>
       <c r="P30">
-        <v>6023.76692701911</v>
+        <v>5896.585835126934</v>
       </c>
       <c r="Q30">
-        <v>7168.76692701911</v>
+        <v>7041.585835126934</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1140306187197393</v>
+        <v>0.1149019869074321</v>
       </c>
       <c r="T30">
-        <v>1.329941756431558</v>
+        <v>1.346926344286446</v>
       </c>
       <c r="U30">
         <v>0.06373661666253409</v>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>2.691560670749851</v>
+        <v>2.598748233827442</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3799,22 +3799,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.09775357718239482</v>
+        <v>0.09778963780425648</v>
       </c>
       <c r="C31">
-        <v>157376.4454991646</v>
+        <v>154946.7014649279</v>
       </c>
       <c r="D31">
-        <v>215204.1470809591</v>
+        <v>215054.878963336</v>
       </c>
       <c r="E31">
-        <v>58123.80992043402</v>
+        <v>60404.28583704762</v>
       </c>
       <c r="F31">
-        <v>66133.80158179454</v>
+        <v>68414.27749840815</v>
       </c>
       <c r="G31">
         <v>8306.1</v>
@@ -3835,28 +3835,28 @@
         <v>10954.1</v>
       </c>
       <c r="M31">
-        <v>4215.144759854929</v>
+        <v>4360.494579160272</v>
       </c>
       <c r="N31">
-        <v>6738.955240145069</v>
+        <v>6593.605420839726</v>
       </c>
       <c r="O31">
-        <v>842.3694050181336</v>
+        <v>824.2006776049658</v>
       </c>
       <c r="P31">
-        <v>5896.585835126935</v>
+        <v>5769.404743234761</v>
       </c>
       <c r="Q31">
-        <v>7041.585835126935</v>
+        <v>6914.404743234761</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1149019869074321</v>
+        <v>0.115798251329059</v>
       </c>
       <c r="T31">
-        <v>1.346926344286445</v>
+        <v>1.364396206080044</v>
       </c>
       <c r="U31">
         <v>0.06373661666253409</v>
@@ -3873,7 +3873,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>2.598748233827443</v>
+        <v>2.512123292699861</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3881,22 +3881,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.09778963780425648</v>
+        <v>0.09877507342611816</v>
       </c>
       <c r="C32">
-        <v>154946.7014649279</v>
+        <v>148665.8018645004</v>
       </c>
       <c r="D32">
-        <v>215054.878963336</v>
+        <v>211054.4552795221</v>
       </c>
       <c r="E32">
-        <v>60404.28583704762</v>
+        <v>62684.76175366123</v>
       </c>
       <c r="F32">
-        <v>68414.27749840815</v>
+        <v>70694.75341502175</v>
       </c>
       <c r="G32">
         <v>8306.1</v>
@@ -3917,45 +3917,45 @@
         <v>10954.1</v>
       </c>
       <c r="M32">
-        <v>4360.494579160272</v>
+        <v>4753.276035418191</v>
       </c>
       <c r="N32">
-        <v>6593.605420839726</v>
+        <v>6200.823964581808</v>
       </c>
       <c r="O32">
-        <v>824.2006776049658</v>
+        <v>775.1029955727259</v>
       </c>
       <c r="P32">
-        <v>5769.404743234761</v>
+        <v>5425.720969009081</v>
       </c>
       <c r="Q32">
-        <v>6914.404743234761</v>
+        <v>6570.720969009081</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.115798251329059</v>
+        <v>0.1167204944295736</v>
       </c>
       <c r="T32">
-        <v>1.364396206080044</v>
+        <v>1.382372440679254</v>
       </c>
       <c r="U32">
-        <v>0.06373661666253409</v>
+        <v>0.0672366166625341</v>
       </c>
       <c r="V32">
         <v>0.125</v>
       </c>
       <c r="W32">
-        <v>0.05576953957971733</v>
+        <v>0.05883203957971733</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y32">
-        <v>2.512123292699861</v>
+        <v>2.304536895896108</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3963,22 +3963,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.09877507342611816</v>
+        <v>0.09962575904797981</v>
       </c>
       <c r="C33">
-        <v>148665.8018645004</v>
+        <v>143049.7298743397</v>
       </c>
       <c r="D33">
-        <v>211054.4552795221</v>
+        <v>207718.859205975</v>
       </c>
       <c r="E33">
-        <v>62684.76175366123</v>
+        <v>64965.23767027485</v>
       </c>
       <c r="F33">
-        <v>70694.75341502175</v>
+        <v>72975.22933163538</v>
       </c>
       <c r="G33">
         <v>8306.1</v>
@@ -3999,45 +3999,45 @@
         <v>10954.1</v>
       </c>
       <c r="M33">
-        <v>4753.276035418191</v>
+        <v>5110.938162560261</v>
       </c>
       <c r="N33">
-        <v>6200.823964581808</v>
+        <v>5843.161837439738</v>
       </c>
       <c r="O33">
-        <v>775.1029955727259</v>
+        <v>730.3952296799672</v>
       </c>
       <c r="P33">
-        <v>5425.720969009081</v>
+        <v>5112.766607759771</v>
       </c>
       <c r="Q33">
-        <v>6570.720969009081</v>
+        <v>6257.766607759771</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1167204944295736</v>
+        <v>0.1176698623271622</v>
       </c>
       <c r="T33">
-        <v>1.382372440679254</v>
+        <v>1.400877388060794</v>
       </c>
       <c r="U33">
-        <v>0.0672366166625341</v>
+        <v>0.07003661666253409</v>
       </c>
       <c r="V33">
         <v>0.125</v>
       </c>
       <c r="W33">
-        <v>0.05883203957971733</v>
+        <v>0.06128203957971733</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y33">
-        <v>2.304536895896108</v>
+        <v>2.143266001581337</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4045,22 +4045,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.09962575904797981</v>
+        <v>0.09971694466984148</v>
       </c>
       <c r="C34">
-        <v>143049.7298743397</v>
+        <v>140417.9548723443</v>
       </c>
       <c r="D34">
-        <v>207718.859205975</v>
+        <v>207367.5601205933</v>
       </c>
       <c r="E34">
-        <v>64965.23767027485</v>
+        <v>67245.71358688847</v>
       </c>
       <c r="F34">
-        <v>72975.22933163538</v>
+        <v>75255.70524824898</v>
       </c>
       <c r="G34">
         <v>8306.1</v>
@@ -4081,28 +4081,28 @@
         <v>10954.1</v>
       </c>
       <c r="M34">
-        <v>5110.938162560261</v>
+        <v>5270.654980140269</v>
       </c>
       <c r="N34">
-        <v>5843.161837439738</v>
+        <v>5683.44501985973</v>
       </c>
       <c r="O34">
-        <v>730.3952296799672</v>
+        <v>710.4306274824662</v>
       </c>
       <c r="P34">
-        <v>5112.766607759771</v>
+        <v>4973.014392377263</v>
       </c>
       <c r="Q34">
-        <v>6257.766607759771</v>
+        <v>6118.014392377263</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1176698623271622</v>
+        <v>0.1186475695649773</v>
       </c>
       <c r="T34">
-        <v>1.400877388060794</v>
+        <v>1.419934721931335</v>
       </c>
       <c r="U34">
         <v>0.07003661666253409</v>
@@ -4119,7 +4119,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>2.143266001581337</v>
+        <v>2.078318546987964</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4127,22 +4127,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.09971694466984148</v>
+        <v>0.09980813029170314</v>
       </c>
       <c r="C35">
-        <v>140417.9548723443</v>
+        <v>137787.3661149158</v>
       </c>
       <c r="D35">
-        <v>207367.5601205933</v>
+        <v>207017.4472797784</v>
       </c>
       <c r="E35">
-        <v>67245.71358688847</v>
+        <v>69526.18950350207</v>
       </c>
       <c r="F35">
-        <v>75255.70524824898</v>
+        <v>77536.18116486259</v>
       </c>
       <c r="G35">
         <v>8306.1</v>
@@ -4163,28 +4163,28 @@
         <v>10954.1</v>
       </c>
       <c r="M35">
-        <v>5270.654980140269</v>
+        <v>5430.371797720277</v>
       </c>
       <c r="N35">
-        <v>5683.44501985973</v>
+        <v>5523.728202279722</v>
       </c>
       <c r="O35">
-        <v>710.4306274824662</v>
+        <v>690.4660252849652</v>
       </c>
       <c r="P35">
-        <v>4973.014392377263</v>
+        <v>4833.262176994756</v>
       </c>
       <c r="Q35">
-        <v>6118.014392377263</v>
+        <v>5978.262176994756</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1186475695649773</v>
+        <v>0.1196549042948474</v>
       </c>
       <c r="T35">
-        <v>1.419934721931335</v>
+        <v>1.43956955076765</v>
       </c>
       <c r="U35">
         <v>0.07003661666253409</v>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>2.078318546987964</v>
+        <v>2.017191530900083</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4209,22 +4209,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.09980813029170314</v>
+        <v>0.1022880659135648</v>
       </c>
       <c r="C36">
-        <v>137787.3661149158</v>
+        <v>126418.422863599</v>
       </c>
       <c r="D36">
-        <v>207017.4472797784</v>
+        <v>197928.9799450752</v>
       </c>
       <c r="E36">
-        <v>69526.18950350207</v>
+        <v>71806.66542011568</v>
       </c>
       <c r="F36">
-        <v>77536.18116486259</v>
+        <v>79816.65708147619</v>
       </c>
       <c r="G36">
         <v>8306.1</v>
@@ -4245,45 +4245,45 @@
         <v>10954.1</v>
       </c>
       <c r="M36">
-        <v>5430.371797720277</v>
+        <v>6212.658540535801</v>
       </c>
       <c r="N36">
-        <v>5523.728202279722</v>
+        <v>4741.441459464198</v>
       </c>
       <c r="O36">
-        <v>690.4660252849652</v>
+        <v>592.6801824330247</v>
       </c>
       <c r="P36">
-        <v>4833.262176994756</v>
+        <v>4148.761277031173</v>
       </c>
       <c r="Q36">
-        <v>5978.262176994756</v>
+        <v>5293.761277031173</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1196549042948474</v>
+        <v>0.1206932339394827</v>
       </c>
       <c r="T36">
-        <v>1.43956955076765</v>
+        <v>1.459808528183544</v>
       </c>
       <c r="U36">
-        <v>0.07003661666253409</v>
+        <v>0.07783661666253411</v>
       </c>
       <c r="V36">
         <v>0.125</v>
       </c>
       <c r="W36">
-        <v>0.06128203957971733</v>
+        <v>0.06810703957971734</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y36">
-        <v>2.017191530900083</v>
+        <v>1.763190416554791</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1022880659135648</v>
+        <v>0.1036760015354265</v>
       </c>
       <c r="C37">
-        <v>126418.422863599</v>
+        <v>119391.3736769512</v>
       </c>
       <c r="D37">
-        <v>197928.9799450752</v>
+        <v>193182.406675041</v>
       </c>
       <c r="E37">
-        <v>71806.66542011568</v>
+        <v>74087.14133672928</v>
       </c>
       <c r="F37">
-        <v>79816.65708147619</v>
+        <v>82097.1329980898</v>
       </c>
       <c r="G37">
         <v>8306.1</v>
@@ -4327,45 +4327,45 @@
         <v>10954.1</v>
       </c>
       <c r="M37">
-        <v>6212.658540535801</v>
+        <v>6710.341888957944</v>
       </c>
       <c r="N37">
-        <v>4741.441459464198</v>
+        <v>4243.758111042054</v>
       </c>
       <c r="O37">
-        <v>592.6801824330247</v>
+        <v>530.4697638802568</v>
       </c>
       <c r="P37">
-        <v>4148.761277031173</v>
+        <v>3713.288347161797</v>
       </c>
       <c r="Q37">
-        <v>5293.761277031173</v>
+        <v>4858.288347161797</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1206932339394827</v>
+        <v>0.1217640113855129</v>
       </c>
       <c r="T37">
-        <v>1.459808528183544</v>
+        <v>1.480679973643684</v>
       </c>
       <c r="U37">
-        <v>0.07783661666253411</v>
+        <v>0.0817366166625341</v>
       </c>
       <c r="V37">
         <v>0.125</v>
       </c>
       <c r="W37">
-        <v>0.06810703957971734</v>
+        <v>0.07151953957971734</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y37">
-        <v>1.763190416554791</v>
+        <v>1.632420550438015</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4373,22 +4373,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1036760015354265</v>
+        <v>0.1038695621572882</v>
       </c>
       <c r="C38">
-        <v>119391.3736769512</v>
+        <v>116466.9716589582</v>
       </c>
       <c r="D38">
-        <v>193182.406675041</v>
+        <v>192538.4805736615</v>
       </c>
       <c r="E38">
-        <v>74087.14133672927</v>
+        <v>76367.61725334288</v>
       </c>
       <c r="F38">
-        <v>82097.13299808979</v>
+        <v>84377.60891470339</v>
       </c>
       <c r="G38">
         <v>8306.1</v>
@@ -4409,28 +4409,28 @@
         <v>10954.1</v>
       </c>
       <c r="M38">
-        <v>6710.341888957943</v>
+        <v>6896.740274762331</v>
       </c>
       <c r="N38">
-        <v>4243.758111042055</v>
+        <v>4057.359725237668</v>
       </c>
       <c r="O38">
-        <v>530.4697638802569</v>
+        <v>507.1699656547084</v>
       </c>
       <c r="P38">
-        <v>3713.288347161798</v>
+        <v>3550.189759582959</v>
       </c>
       <c r="Q38">
-        <v>4858.288347161799</v>
+        <v>4695.18975958296</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1217640113855129</v>
+        <v>0.1228687817663377</v>
       </c>
       <c r="T38">
-        <v>1.480679973643684</v>
+        <v>1.502214004673988</v>
       </c>
       <c r="U38">
         <v>0.0817366166625341</v>
@@ -4447,7 +4447,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>1.632420550438015</v>
+        <v>1.588301076101853</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4455,22 +4455,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1038695621572882</v>
+        <v>0.1040631227791498</v>
       </c>
       <c r="C39">
-        <v>116466.9716589582</v>
+        <v>113546.8481186941</v>
       </c>
       <c r="D39">
-        <v>192538.4805736615</v>
+        <v>191898.8329500111</v>
       </c>
       <c r="E39">
-        <v>76367.61725334288</v>
+        <v>78648.09316995648</v>
       </c>
       <c r="F39">
-        <v>84377.60891470339</v>
+        <v>86658.084831317</v>
       </c>
       <c r="G39">
         <v>8306.1</v>
@@ -4491,28 +4491,28 @@
         <v>10954.1</v>
       </c>
       <c r="M39">
-        <v>6896.740274762331</v>
+        <v>7083.138660566718</v>
       </c>
       <c r="N39">
-        <v>4057.359725237668</v>
+        <v>3870.96133943328</v>
       </c>
       <c r="O39">
-        <v>507.1699656547084</v>
+        <v>483.87016742916</v>
       </c>
       <c r="P39">
-        <v>3550.189759582959</v>
+        <v>3387.09117200412</v>
       </c>
       <c r="Q39">
-        <v>4695.18975958296</v>
+        <v>4532.09117200412</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1228687817663377</v>
+        <v>0.1240091899013826</v>
       </c>
       <c r="T39">
-        <v>1.502214004673988</v>
+        <v>1.524442681866559</v>
       </c>
       <c r="U39">
         <v>0.0817366166625341</v>
@@ -4529,7 +4529,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>1.588301076101853</v>
+        <v>1.54650367936233</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4537,22 +4537,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1040631227791498</v>
+        <v>0.1042566834010115</v>
       </c>
       <c r="C40">
-        <v>113546.8481186941</v>
+        <v>110630.9605557247</v>
       </c>
       <c r="D40">
-        <v>191898.8329500111</v>
+        <v>191263.4213036553</v>
       </c>
       <c r="E40">
-        <v>78648.09316995648</v>
+        <v>80928.56908657009</v>
       </c>
       <c r="F40">
-        <v>86658.084831317</v>
+        <v>88938.56074793061</v>
       </c>
       <c r="G40">
         <v>8306.1</v>
@@ -4573,28 +4573,28 @@
         <v>10954.1</v>
       </c>
       <c r="M40">
-        <v>7083.138660566718</v>
+        <v>7269.537046371105</v>
       </c>
       <c r="N40">
-        <v>3870.96133943328</v>
+        <v>3684.562953628893</v>
       </c>
       <c r="O40">
-        <v>483.87016742916</v>
+        <v>460.5703692036117</v>
       </c>
       <c r="P40">
-        <v>3387.09117200412</v>
+        <v>3223.992584425282</v>
       </c>
       <c r="Q40">
-        <v>4532.09117200412</v>
+        <v>4368.992584425281</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1240091899013826</v>
+        <v>0.1251869884670848</v>
       </c>
       <c r="T40">
-        <v>1.524442681866559</v>
+        <v>1.547400168147412</v>
       </c>
       <c r="U40">
         <v>0.0817366166625341</v>
@@ -4611,7 +4611,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>1.54650367936233</v>
+        <v>1.50684973886586</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4619,22 +4619,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1042566834010115</v>
+        <v>0.1094202440228731</v>
       </c>
       <c r="C41">
-        <v>110630.9605557247</v>
+        <v>92827.11961883512</v>
       </c>
       <c r="D41">
-        <v>191263.4213036553</v>
+        <v>175740.0562833793</v>
       </c>
       <c r="E41">
-        <v>80928.56908657009</v>
+        <v>83209.0450031837</v>
       </c>
       <c r="F41">
-        <v>88938.56074793061</v>
+        <v>91219.03666454421</v>
       </c>
       <c r="G41">
         <v>8306.1</v>
@@ -4655,45 +4655,45 @@
         <v>10954.1</v>
       </c>
       <c r="M41">
-        <v>7269.537046371105</v>
+        <v>8751.245752812021</v>
       </c>
       <c r="N41">
-        <v>3684.562953628893</v>
+        <v>2202.854247187977</v>
       </c>
       <c r="O41">
-        <v>460.5703692036117</v>
+        <v>275.3567808984972</v>
       </c>
       <c r="P41">
-        <v>3223.992584425282</v>
+        <v>1927.49746628948</v>
       </c>
       <c r="Q41">
-        <v>4368.992584425281</v>
+        <v>3072.49746628948</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1251869884670848</v>
+        <v>0.126404046984977</v>
       </c>
       <c r="T41">
-        <v>1.547400168147412</v>
+        <v>1.57112290397096</v>
       </c>
       <c r="U41">
-        <v>0.0817366166625341</v>
+        <v>0.0959366166625341</v>
       </c>
       <c r="V41">
         <v>0.125</v>
       </c>
       <c r="W41">
-        <v>0.07151953957971734</v>
+        <v>0.08394453957971734</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y41">
-        <v>1.50684973886586</v>
+        <v>1.251718933442149</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4701,22 +4701,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1094202440228731</v>
+        <v>0.1205311292903624</v>
       </c>
       <c r="C42">
-        <v>92827.11961883512</v>
+        <v>64417.93909399948</v>
       </c>
       <c r="D42">
-        <v>175740.0562833793</v>
+        <v>149611.3516751573</v>
       </c>
       <c r="E42">
-        <v>83209.0450031837</v>
+        <v>85489.5209197973</v>
       </c>
       <c r="F42">
-        <v>91219.03666454421</v>
+        <v>93499.51258115782</v>
       </c>
       <c r="G42">
         <v>8306.1</v>
@@ -4737,45 +4737,45 @@
         <v>10954.1</v>
       </c>
       <c r="M42">
-        <v>8751.245752812021</v>
+        <v>11644.11295645343</v>
       </c>
       <c r="N42">
-        <v>2202.854247187977</v>
+        <v>-690.0129564534363</v>
       </c>
       <c r="O42">
-        <v>275.3567808984972</v>
+        <v>-86.25161955667954</v>
       </c>
       <c r="P42">
-        <v>1927.49746628948</v>
+        <v>-603.7613368967568</v>
       </c>
       <c r="Q42">
-        <v>3072.49746628948</v>
+        <v>541.2386631032432</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.126404046984977</v>
+        <v>0.1279244075136732</v>
       </c>
       <c r="T42">
-        <v>1.57112290397096</v>
+        <v>1.600757560520812</v>
       </c>
       <c r="U42">
-        <v>0.0959366166625341</v>
+        <v>0.1245366166625341</v>
       </c>
       <c r="V42">
-        <v>0.125</v>
+        <v>0.1175926843994693</v>
       </c>
       <c r="W42">
-        <v>0.08394453957971734</v>
+        <v>0.109892021603159</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y42">
-        <v>1.251718933442149</v>
+        <v>0.9407414751957541</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4783,22 +4783,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1205311292903624</v>
+        <v>0.1213184954569877</v>
       </c>
       <c r="C43">
-        <v>64417.93909399948</v>
+        <v>60577.59475390551</v>
       </c>
       <c r="D43">
-        <v>149611.3516751573</v>
+        <v>148051.4832516769</v>
       </c>
       <c r="E43">
-        <v>85489.5209197973</v>
+        <v>87769.99683641091</v>
       </c>
       <c r="F43">
-        <v>93499.51258115782</v>
+        <v>95779.98849777142</v>
       </c>
       <c r="G43">
         <v>8306.1</v>
@@ -4819,37 +4819,37 @@
         <v>10954.1</v>
       </c>
       <c r="M43">
-        <v>11644.11295645343</v>
+        <v>11928.11571148888</v>
       </c>
       <c r="N43">
-        <v>-690.0129564534363</v>
+        <v>-974.0157114888862</v>
       </c>
       <c r="O43">
-        <v>-86.25161955667954</v>
+        <v>-121.7519639361108</v>
       </c>
       <c r="P43">
-        <v>-603.7613368967568</v>
+        <v>-852.2637475527754</v>
       </c>
       <c r="Q43">
-        <v>541.2386631032432</v>
+        <v>292.7362524472246</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1279244075136732</v>
+        <v>0.1293403455742537</v>
       </c>
       <c r="T43">
-        <v>1.600757560520812</v>
+        <v>1.628356828805653</v>
       </c>
       <c r="U43">
         <v>0.1245366166625341</v>
       </c>
       <c r="V43">
-        <v>0.1175926843994693</v>
+        <v>0.1147928585804343</v>
       </c>
       <c r="W43">
-        <v>0.109892021603159</v>
+        <v>0.1102407024379061</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4857,7 +4857,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.9407414751957541</v>
+        <v>0.9183428686434743</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4865,22 +4865,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1213184954569877</v>
+        <v>0.1221058616236131</v>
       </c>
       <c r="C44">
-        <v>60577.59475390552</v>
+        <v>56769.4415874619</v>
       </c>
       <c r="D44">
-        <v>148051.4832516769</v>
+        <v>146523.8060018469</v>
       </c>
       <c r="E44">
-        <v>87769.99683641089</v>
+        <v>90050.4727530245</v>
       </c>
       <c r="F44">
-        <v>95779.98849777141</v>
+        <v>98060.46441438502</v>
       </c>
       <c r="G44">
         <v>8306.1</v>
@@ -4901,37 +4901,37 @@
         <v>10954.1</v>
       </c>
       <c r="M44">
-        <v>11928.11571148888</v>
+        <v>12212.11846652433</v>
       </c>
       <c r="N44">
-        <v>-974.0157114888843</v>
+        <v>-1258.018466524334</v>
       </c>
       <c r="O44">
-        <v>-121.7519639361105</v>
+        <v>-157.2523083155418</v>
       </c>
       <c r="P44">
-        <v>-852.2637475527738</v>
+        <v>-1100.766158208792</v>
       </c>
       <c r="Q44">
-        <v>292.7362524472262</v>
+        <v>44.23384179120762</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1293403455742537</v>
+        <v>0.1308059656720477</v>
       </c>
       <c r="T44">
-        <v>1.628356828805653</v>
+        <v>1.65692449246891</v>
       </c>
       <c r="U44">
         <v>0.1245366166625341</v>
       </c>
       <c r="V44">
-        <v>0.1147928585804343</v>
+        <v>0.1121232572180986</v>
       </c>
       <c r="W44">
-        <v>0.1102407024379061</v>
+        <v>0.110573165559409</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4939,7 +4939,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.9183428686434745</v>
+        <v>0.8969860577447889</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4947,22 +4947,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1221058616236131</v>
+        <v>0.1228932277902384</v>
       </c>
       <c r="C45">
-        <v>56769.4415874619</v>
+        <v>52992.49327297528</v>
       </c>
       <c r="D45">
-        <v>146523.8060018469</v>
+        <v>145027.3336039739</v>
       </c>
       <c r="E45">
-        <v>90050.4727530245</v>
+        <v>92330.94866963812</v>
       </c>
       <c r="F45">
-        <v>98060.46441438502</v>
+        <v>100340.9403309986</v>
       </c>
       <c r="G45">
         <v>8306.1</v>
@@ -4983,37 +4983,37 @@
         <v>10954.1</v>
       </c>
       <c r="M45">
-        <v>12212.11846652433</v>
+        <v>12496.12122155978</v>
       </c>
       <c r="N45">
-        <v>-1258.018466524334</v>
+        <v>-1542.021221559786</v>
       </c>
       <c r="O45">
-        <v>-157.2523083155418</v>
+        <v>-192.7526526949732</v>
       </c>
       <c r="P45">
-        <v>-1100.766158208792</v>
+        <v>-1349.268568864813</v>
       </c>
       <c r="Q45">
-        <v>44.23384179120762</v>
+        <v>-204.2685688648126</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1308059656720477</v>
+        <v>0.1323239293447628</v>
       </c>
       <c r="T45">
-        <v>1.65692449246891</v>
+        <v>1.686512429834426</v>
       </c>
       <c r="U45">
         <v>0.1245366166625341</v>
       </c>
       <c r="V45">
-        <v>0.1121232572180986</v>
+        <v>0.1095750013722327</v>
       </c>
       <c r="W45">
-        <v>0.110573165559409</v>
+        <v>0.1108905167208437</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5021,7 +5021,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.8969860577447889</v>
+        <v>0.8766000109778618</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5029,22 +5029,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1228932277902384</v>
+        <v>0.1236805939568637</v>
       </c>
       <c r="C46">
-        <v>52992.49327297528</v>
+        <v>49245.8033752651</v>
       </c>
       <c r="D46">
-        <v>145027.3336039739</v>
+        <v>143561.1196228773</v>
       </c>
       <c r="E46">
-        <v>92330.94866963812</v>
+        <v>94611.42458625173</v>
       </c>
       <c r="F46">
-        <v>100340.9403309986</v>
+        <v>102621.4162476122</v>
       </c>
       <c r="G46">
         <v>8306.1</v>
@@ -5065,37 +5065,37 @@
         <v>10954.1</v>
       </c>
       <c r="M46">
-        <v>12496.12122155978</v>
+        <v>12780.12397659523</v>
       </c>
       <c r="N46">
-        <v>-1542.021221559786</v>
+        <v>-1826.023976595236</v>
       </c>
       <c r="O46">
-        <v>-192.7526526949732</v>
+        <v>-228.2529970744044</v>
       </c>
       <c r="P46">
-        <v>-1349.268568864813</v>
+        <v>-1597.770979520831</v>
       </c>
       <c r="Q46">
-        <v>-204.2685688648126</v>
+        <v>-452.7709795208311</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1323239293447628</v>
+        <v>0.1338970916964858</v>
       </c>
       <c r="T46">
-        <v>1.686512429834426</v>
+        <v>1.717176292195052</v>
       </c>
       <c r="U46">
         <v>0.1245366166625341</v>
       </c>
       <c r="V46">
-        <v>0.1095750013722327</v>
+        <v>0.1071400013417387</v>
       </c>
       <c r="W46">
-        <v>0.1108905167208437</v>
+        <v>0.1111937633862146</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5103,7 +5103,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.8766000109778618</v>
+        <v>0.8571200107339093</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5111,22 +5111,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1236805939568637</v>
+        <v>0.1244679601234891</v>
       </c>
       <c r="C47">
-        <v>49245.8033752651</v>
+        <v>45528.46334959783</v>
       </c>
       <c r="D47">
-        <v>143561.1196228773</v>
+        <v>142124.2555138237</v>
       </c>
       <c r="E47">
-        <v>94611.42458625173</v>
+        <v>96891.90050286533</v>
       </c>
       <c r="F47">
-        <v>102621.4162476122</v>
+        <v>104901.8921642259</v>
       </c>
       <c r="G47">
         <v>8306.1</v>
@@ -5147,37 +5147,37 @@
         <v>10954.1</v>
       </c>
       <c r="M47">
-        <v>12780.12397659523</v>
+        <v>13064.12673163068</v>
       </c>
       <c r="N47">
-        <v>-1826.023976595236</v>
+        <v>-2110.026731630685</v>
       </c>
       <c r="O47">
-        <v>-228.2529970744044</v>
+        <v>-263.7533414538357</v>
       </c>
       <c r="P47">
-        <v>-1597.770979520831</v>
+        <v>-1846.27339017685</v>
       </c>
       <c r="Q47">
-        <v>-452.7709795208311</v>
+        <v>-701.2733901768497</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1338970916964858</v>
+        <v>0.1355285193204947</v>
       </c>
       <c r="T47">
-        <v>1.717176292195052</v>
+        <v>1.748975853161627</v>
       </c>
       <c r="U47">
         <v>0.1245366166625341</v>
       </c>
       <c r="V47">
-        <v>0.1071400013417387</v>
+        <v>0.1048108708777878</v>
       </c>
       <c r="W47">
-        <v>0.1111937633862146</v>
+        <v>0.1114838254139607</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5185,7 +5185,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.8571200107339093</v>
+        <v>0.8384869670223025</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5193,22 +5193,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1244679601234891</v>
+        <v>0.1252553262901144</v>
       </c>
       <c r="C48">
-        <v>45528.46334959783</v>
+        <v>41839.60066430108</v>
       </c>
       <c r="D48">
-        <v>142124.2555138237</v>
+        <v>140715.8687451405</v>
       </c>
       <c r="E48">
-        <v>96891.90050286533</v>
+        <v>99172.37641947894</v>
       </c>
       <c r="F48">
-        <v>104901.8921642259</v>
+        <v>107182.3680808395</v>
       </c>
       <c r="G48">
         <v>8306.1</v>
@@ -5229,37 +5229,37 @@
         <v>10954.1</v>
       </c>
       <c r="M48">
-        <v>13064.12673163068</v>
+        <v>13348.12948666613</v>
       </c>
       <c r="N48">
-        <v>-2110.026731630685</v>
+        <v>-2394.029486666135</v>
       </c>
       <c r="O48">
-        <v>-263.7533414538357</v>
+        <v>-299.2536858332669</v>
       </c>
       <c r="P48">
-        <v>-1846.27339017685</v>
+        <v>-2094.775800832868</v>
       </c>
       <c r="Q48">
-        <v>-701.2733901768497</v>
+        <v>-949.7758008328683</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1355285193204947</v>
+        <v>0.1372215102510701</v>
       </c>
       <c r="T48">
-        <v>1.748975853161627</v>
+        <v>1.781975397560904</v>
       </c>
       <c r="U48">
         <v>0.1245366166625341</v>
       </c>
       <c r="V48">
-        <v>0.1048108708777878</v>
+        <v>0.1025808523484732</v>
       </c>
       <c r="W48">
-        <v>0.1114838254139607</v>
+        <v>0.1117615443766963</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5267,7 +5267,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.8384869670223025</v>
+        <v>0.8206468187877854</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5275,22 +5275,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1252553262901144</v>
+        <v>0.1260426924567398</v>
       </c>
       <c r="C49">
-        <v>41839.60066430108</v>
+        <v>38178.37703390721</v>
       </c>
       <c r="D49">
-        <v>140715.8687451405</v>
+        <v>139335.1210313603</v>
       </c>
       <c r="E49">
-        <v>99172.37641947894</v>
+        <v>101452.8523360925</v>
       </c>
       <c r="F49">
-        <v>107182.3680808395</v>
+        <v>109462.8439974531</v>
       </c>
       <c r="G49">
         <v>8306.1</v>
@@ -5311,37 +5311,37 @@
         <v>10954.1</v>
       </c>
       <c r="M49">
-        <v>13348.12948666613</v>
+        <v>13632.13224170158</v>
       </c>
       <c r="N49">
-        <v>-2394.029486666135</v>
+        <v>-2678.032241701585</v>
       </c>
       <c r="O49">
-        <v>-299.2536858332669</v>
+        <v>-334.7540302126981</v>
       </c>
       <c r="P49">
-        <v>-2094.775800832868</v>
+        <v>-2343.278211488887</v>
       </c>
       <c r="Q49">
-        <v>-949.7758008328683</v>
+        <v>-1198.278211488887</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1372215102510701</v>
+        <v>0.1389796162174369</v>
       </c>
       <c r="T49">
-        <v>1.781975397560904</v>
+        <v>1.816244155206306</v>
       </c>
       <c r="U49">
         <v>0.1245366166625341</v>
       </c>
       <c r="V49">
-        <v>0.1025808523484732</v>
+        <v>0.10044375125788</v>
       </c>
       <c r="W49">
-        <v>0.1117615443766963</v>
+        <v>0.1120276917159846</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5349,7 +5349,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.8206468187877854</v>
+        <v>0.8035500100630399</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1260426924567398</v>
+        <v>0.1680839535647544</v>
       </c>
       <c r="C50">
-        <v>38178.37703390722</v>
+        <v>-12005.55664664165</v>
       </c>
       <c r="D50">
-        <v>139335.1210313603</v>
+        <v>91431.663267425</v>
       </c>
       <c r="E50">
-        <v>101452.8523360925</v>
+        <v>103733.3282527061</v>
       </c>
       <c r="F50">
-        <v>109462.843997453</v>
+        <v>111743.3199140667</v>
       </c>
       <c r="G50">
         <v>8306.1</v>
@@ -5393,45 +5393,45 @@
         <v>10954.1</v>
       </c>
       <c r="M50">
-        <v>13632.13224170158</v>
+        <v>23101.43589367331</v>
       </c>
       <c r="N50">
-        <v>-2678.032241701583</v>
+        <v>-12147.33589367331</v>
       </c>
       <c r="O50">
-        <v>-334.7540302126979</v>
+        <v>-1518.416986709164</v>
       </c>
       <c r="P50">
-        <v>-2343.278211488885</v>
+        <v>-10628.91890696415</v>
       </c>
       <c r="Q50">
-        <v>-1198.278211488885</v>
+        <v>-9483.918906964149</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1389796162174368</v>
+        <v>0.1427201870087381</v>
       </c>
       <c r="T50">
-        <v>1.816244155206305</v>
+        <v>1.889154842249519</v>
       </c>
       <c r="U50">
-        <v>0.1245366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V50">
-        <v>0.10044375125788</v>
+        <v>0.05927174857451149</v>
       </c>
       <c r="W50">
-        <v>0.1120276917159846</v>
+        <v>0.1944829758985672</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y50">
-        <v>0.8035500100630401</v>
+        <v>0.4741739885960919</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5439,22 +5439,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1680839535647544</v>
+        <v>0.1696933197313797</v>
       </c>
       <c r="C51">
-        <v>-12005.55664664165</v>
+        <v>-15473.72392336986</v>
       </c>
       <c r="D51">
-        <v>91431.663267425</v>
+        <v>90243.97190731039</v>
       </c>
       <c r="E51">
-        <v>103733.3282527061</v>
+        <v>106013.8041693197</v>
       </c>
       <c r="F51">
-        <v>111743.3199140667</v>
+        <v>114023.7958306803</v>
       </c>
       <c r="G51">
         <v>8306.1</v>
@@ -5475,37 +5475,37 @@
         <v>10954.1</v>
       </c>
       <c r="M51">
-        <v>23101.43589367331</v>
+        <v>23572.8937690544</v>
       </c>
       <c r="N51">
-        <v>-12147.33589367331</v>
+        <v>-12618.7937690544</v>
       </c>
       <c r="O51">
-        <v>-1518.416986709164</v>
+        <v>-1577.3492211318</v>
       </c>
       <c r="P51">
-        <v>-10628.91890696415</v>
+        <v>-11041.4445479226</v>
       </c>
       <c r="Q51">
-        <v>-9483.918906964149</v>
+        <v>-9896.444547922598</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1427201870087381</v>
+        <v>0.1446585907489128</v>
       </c>
       <c r="T51">
-        <v>1.889154842249519</v>
+        <v>1.926937939094509</v>
       </c>
       <c r="U51">
         <v>0.2067366166625341</v>
       </c>
       <c r="V51">
-        <v>0.05927174857451149</v>
+        <v>0.05808631360302127</v>
       </c>
       <c r="W51">
-        <v>0.1944829758985672</v>
+        <v>0.1947280487138466</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5513,7 +5513,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.4741739885960919</v>
+        <v>0.4646905088241702</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5521,22 +5521,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1696933197313797</v>
+        <v>0.171302685898005</v>
       </c>
       <c r="C52">
-        <v>-15473.72392336986</v>
+        <v>-18911.43081149863</v>
       </c>
       <c r="D52">
-        <v>90243.97190731039</v>
+        <v>89086.74093579523</v>
       </c>
       <c r="E52">
-        <v>106013.8041693197</v>
+        <v>108294.2800859334</v>
       </c>
       <c r="F52">
-        <v>114023.7958306803</v>
+        <v>116304.2717472939</v>
       </c>
       <c r="G52">
         <v>8306.1</v>
@@ -5557,37 +5557,37 @@
         <v>10954.1</v>
       </c>
       <c r="M52">
-        <v>23572.8937690544</v>
+        <v>24044.35164443549</v>
       </c>
       <c r="N52">
-        <v>-12618.7937690544</v>
+        <v>-13090.25164443549</v>
       </c>
       <c r="O52">
-        <v>-1577.3492211318</v>
+        <v>-1636.281455554436</v>
       </c>
       <c r="P52">
-        <v>-11041.4445479226</v>
+        <v>-11453.97018888105</v>
       </c>
       <c r="Q52">
-        <v>-9896.444547922598</v>
+        <v>-10308.97018888105</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1446585907489128</v>
+        <v>0.1466761130090947</v>
       </c>
       <c r="T52">
-        <v>1.926937939094509</v>
+        <v>1.966263203157662</v>
       </c>
       <c r="U52">
         <v>0.2067366166625341</v>
       </c>
       <c r="V52">
-        <v>0.05808631360302127</v>
+        <v>0.05694736627747183</v>
       </c>
       <c r="W52">
-        <v>0.1947280487138466</v>
+        <v>0.1949635108304875</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.4646905088241702</v>
+        <v>0.4555789302197747</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5603,22 +5603,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.171302685898005</v>
+        <v>0.1729120520646304</v>
       </c>
       <c r="C53">
-        <v>-18911.43081149863</v>
+        <v>-22319.83428830998</v>
       </c>
       <c r="D53">
-        <v>89086.74093579523</v>
+        <v>87958.81337559748</v>
       </c>
       <c r="E53">
-        <v>108294.2800859334</v>
+        <v>110574.756002547</v>
       </c>
       <c r="F53">
-        <v>116304.2717472939</v>
+        <v>118584.7476639075</v>
       </c>
       <c r="G53">
         <v>8306.1</v>
@@ -5639,37 +5639,37 @@
         <v>10954.1</v>
       </c>
       <c r="M53">
-        <v>24044.35164443549</v>
+        <v>24515.80951981658</v>
       </c>
       <c r="N53">
-        <v>-13090.25164443549</v>
+        <v>-13561.70951981658</v>
       </c>
       <c r="O53">
-        <v>-1636.281455554436</v>
+        <v>-1695.213689977072</v>
       </c>
       <c r="P53">
-        <v>-11453.97018888105</v>
+        <v>-11866.4958298395</v>
       </c>
       <c r="Q53">
-        <v>-10308.97018888105</v>
+        <v>-10721.4958298395</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1466761130090947</v>
+        <v>0.1487776986967842</v>
       </c>
       <c r="T53">
-        <v>1.966263203157662</v>
+        <v>2.007227019890114</v>
       </c>
       <c r="U53">
         <v>0.2067366166625341</v>
       </c>
       <c r="V53">
-        <v>0.05694736627747183</v>
+        <v>0.05585222461828968</v>
       </c>
       <c r="W53">
-        <v>0.1949635108304875</v>
+        <v>0.195189916711873</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5677,7 +5677,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.4555789302197747</v>
+        <v>0.4468177969463174</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5685,22 +5685,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1729120520646304</v>
+        <v>0.1745214182312557</v>
       </c>
       <c r="C54">
-        <v>-22319.83428830998</v>
+        <v>-25700.03346969436</v>
       </c>
       <c r="D54">
-        <v>87958.81337559748</v>
+        <v>86859.09011082671</v>
       </c>
       <c r="E54">
-        <v>110574.756002547</v>
+        <v>112855.2319191606</v>
       </c>
       <c r="F54">
-        <v>118584.7476639075</v>
+        <v>120865.2235805211</v>
       </c>
       <c r="G54">
         <v>8306.1</v>
@@ -5721,37 +5721,37 @@
         <v>10954.1</v>
       </c>
       <c r="M54">
-        <v>24515.80951981658</v>
+        <v>24987.26739519766</v>
       </c>
       <c r="N54">
-        <v>-13561.70951981658</v>
+        <v>-14033.16739519767</v>
       </c>
       <c r="O54">
-        <v>-1695.213689977072</v>
+        <v>-1754.145924399708</v>
       </c>
       <c r="P54">
-        <v>-11866.4958298395</v>
+        <v>-12279.02147079796</v>
       </c>
       <c r="Q54">
-        <v>-10721.4958298395</v>
+        <v>-11134.02147079796</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1487776986967842</v>
+        <v>0.1509687135626732</v>
       </c>
       <c r="T54">
-        <v>2.007227019890114</v>
+        <v>2.049933977760116</v>
       </c>
       <c r="U54">
         <v>0.2067366166625341</v>
       </c>
       <c r="V54">
-        <v>0.05585222461828968</v>
+        <v>0.05479840905945402</v>
       </c>
       <c r="W54">
-        <v>0.195189916711873</v>
+        <v>0.195407778975093</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5759,7 +5759,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.4468177969463174</v>
+        <v>0.4383872724756321</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5767,22 +5767,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1745214182312557</v>
+        <v>0.176130784397881</v>
       </c>
       <c r="C55">
-        <v>-25700.03346969436</v>
+        <v>-29053.07318260548</v>
       </c>
       <c r="D55">
-        <v>86859.09011082671</v>
+        <v>85786.5263145292</v>
       </c>
       <c r="E55">
-        <v>112855.2319191606</v>
+        <v>115135.7078357742</v>
       </c>
       <c r="F55">
-        <v>120865.2235805211</v>
+        <v>123145.6994971347</v>
       </c>
       <c r="G55">
         <v>8306.1</v>
@@ -5803,37 +5803,37 @@
         <v>10954.1</v>
       </c>
       <c r="M55">
-        <v>24987.26739519766</v>
+        <v>25458.72527057875</v>
       </c>
       <c r="N55">
-        <v>-14033.16739519767</v>
+        <v>-14504.62527057875</v>
       </c>
       <c r="O55">
-        <v>-1754.145924399708</v>
+        <v>-1813.078158822344</v>
       </c>
       <c r="P55">
-        <v>-12279.02147079796</v>
+        <v>-12691.54711175641</v>
       </c>
       <c r="Q55">
-        <v>-11134.02147079796</v>
+        <v>-11546.54711175641</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1509687135626732</v>
+        <v>0.1532549899444705</v>
       </c>
       <c r="T55">
-        <v>2.049933977760116</v>
+        <v>2.094497759885336</v>
       </c>
       <c r="U55">
         <v>0.2067366166625341</v>
       </c>
       <c r="V55">
-        <v>0.05479840905945402</v>
+        <v>0.05378362370650117</v>
       </c>
       <c r="W55">
-        <v>0.195407778975093</v>
+        <v>0.1956175722656012</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5841,7 +5841,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.4383872724756321</v>
+        <v>0.4302689896520094</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5849,22 +5849,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.176130784397881</v>
+        <v>0.1777401505645064</v>
       </c>
       <c r="C56">
-        <v>-29053.07318260548</v>
+        <v>-32379.94727606078</v>
       </c>
       <c r="D56">
-        <v>85786.5263145292</v>
+        <v>84740.12813768751</v>
       </c>
       <c r="E56">
-        <v>115135.7078357742</v>
+        <v>117416.1837523878</v>
       </c>
       <c r="F56">
-        <v>123145.6994971347</v>
+        <v>125426.1754137483</v>
       </c>
       <c r="G56">
         <v>8306.1</v>
@@ -5885,37 +5885,37 @@
         <v>10954.1</v>
       </c>
       <c r="M56">
-        <v>25458.72527057875</v>
+        <v>25930.18314595984</v>
       </c>
       <c r="N56">
-        <v>-14504.62527057875</v>
+        <v>-14976.08314595984</v>
       </c>
       <c r="O56">
-        <v>-1813.078158822344</v>
+        <v>-1872.01039324498</v>
       </c>
       <c r="P56">
-        <v>-12691.54711175641</v>
+        <v>-13104.07275271486</v>
       </c>
       <c r="Q56">
-        <v>-11546.54711175641</v>
+        <v>-11959.07275271486</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1532549899444705</v>
+        <v>0.1556428786099032</v>
       </c>
       <c r="T56">
-        <v>2.094497759885336</v>
+        <v>2.141042154549455</v>
       </c>
       <c r="U56">
         <v>0.2067366166625341</v>
       </c>
       <c r="V56">
-        <v>0.05378362370650117</v>
+        <v>0.05280573963911024</v>
       </c>
       <c r="W56">
-        <v>0.1956175722656012</v>
+        <v>0.1958197367091818</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5923,7 +5923,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.4302689896520094</v>
+        <v>0.4224459171128819</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5931,22 +5931,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1777401505645064</v>
+        <v>0.1793495167311318</v>
       </c>
       <c r="C57">
-        <v>-32379.94727606078</v>
+        <v>-35681.6016927423</v>
       </c>
       <c r="D57">
-        <v>84740.12813768751</v>
+        <v>83718.94963761959</v>
       </c>
       <c r="E57">
-        <v>117416.1837523878</v>
+        <v>119696.6596690014</v>
       </c>
       <c r="F57">
-        <v>125426.1754137483</v>
+        <v>127706.6513303619</v>
       </c>
       <c r="G57">
         <v>8306.1</v>
@@ -5967,37 +5967,37 @@
         <v>10954.1</v>
       </c>
       <c r="M57">
-        <v>25930.18314595984</v>
+        <v>26401.64102134093</v>
       </c>
       <c r="N57">
-        <v>-14976.08314595984</v>
+        <v>-15447.54102134093</v>
       </c>
       <c r="O57">
-        <v>-1872.01039324498</v>
+        <v>-1930.942627667616</v>
       </c>
       <c r="P57">
-        <v>-13104.07275271486</v>
+        <v>-13516.59839367331</v>
       </c>
       <c r="Q57">
-        <v>-11959.07275271486</v>
+        <v>-12371.59839367331</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1556428786099032</v>
+        <v>0.1581393076692191</v>
       </c>
       <c r="T57">
-        <v>2.141042154549455</v>
+        <v>2.189702203516488</v>
       </c>
       <c r="U57">
         <v>0.2067366166625341</v>
       </c>
       <c r="V57">
-        <v>0.05280573963911024</v>
+        <v>0.05186278000269755</v>
       </c>
       <c r="W57">
-        <v>0.1958197367091818</v>
+        <v>0.1960146809940631</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -6005,7 +6005,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.4224459171128819</v>
+        <v>0.4149022400215805</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6013,22 +6013,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1793495167311318</v>
+        <v>0.1809588828977571</v>
       </c>
       <c r="C58">
-        <v>-35681.6016927423</v>
+        <v>-38958.93732115241</v>
       </c>
       <c r="D58">
-        <v>83718.94963761959</v>
+        <v>82722.08992582309</v>
       </c>
       <c r="E58">
-        <v>119696.6596690014</v>
+        <v>121977.135585615</v>
       </c>
       <c r="F58">
-        <v>127706.6513303619</v>
+        <v>129987.1272469755</v>
       </c>
       <c r="G58">
         <v>8306.1</v>
@@ -6049,37 +6049,37 @@
         <v>10954.1</v>
       </c>
       <c r="M58">
-        <v>26401.64102134093</v>
+        <v>26873.09889672201</v>
       </c>
       <c r="N58">
-        <v>-15447.54102134093</v>
+        <v>-15918.99889672202</v>
       </c>
       <c r="O58">
-        <v>-1930.942627667616</v>
+        <v>-1989.874862090252</v>
       </c>
       <c r="P58">
-        <v>-13516.59839367331</v>
+        <v>-13929.12403463176</v>
       </c>
       <c r="Q58">
-        <v>-12371.59839367331</v>
+        <v>-12784.12403463176</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1581393076692191</v>
+        <v>0.1607518497080382</v>
       </c>
       <c r="T58">
-        <v>2.189702203516488</v>
+        <v>2.240625510575011</v>
       </c>
       <c r="U58">
         <v>0.2067366166625341</v>
       </c>
       <c r="V58">
-        <v>0.05186278000269755</v>
+        <v>0.0509529066693169</v>
       </c>
       <c r="W58">
-        <v>0.1960146809940631</v>
+        <v>0.1962027851285977</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6087,7 +6087,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.4149022400215805</v>
+        <v>0.4076232533545352</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6095,22 +6095,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1809588828977571</v>
+        <v>0.1825682490643824</v>
       </c>
       <c r="C59">
-        <v>-38958.93732115241</v>
+        <v>-42212.81264639988</v>
       </c>
       <c r="D59">
-        <v>82722.08992582309</v>
+        <v>81748.69051718923</v>
       </c>
       <c r="E59">
-        <v>121977.135585615</v>
+        <v>124257.6115022286</v>
       </c>
       <c r="F59">
-        <v>129987.1272469755</v>
+        <v>132267.6031635891</v>
       </c>
       <c r="G59">
         <v>8306.1</v>
@@ -6131,37 +6131,37 @@
         <v>10954.1</v>
       </c>
       <c r="M59">
-        <v>26873.09889672201</v>
+        <v>27344.5567721031</v>
       </c>
       <c r="N59">
-        <v>-15918.99889672202</v>
+        <v>-16390.45677210311</v>
       </c>
       <c r="O59">
-        <v>-1989.874862090252</v>
+        <v>-2048.807096512888</v>
       </c>
       <c r="P59">
-        <v>-13929.12403463176</v>
+        <v>-14341.64967559022</v>
       </c>
       <c r="Q59">
-        <v>-12784.12403463176</v>
+        <v>-13196.64967559022</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1607518497080382</v>
+        <v>0.1634887985106105</v>
       </c>
       <c r="T59">
-        <v>2.240625510575011</v>
+        <v>2.293973737017273</v>
       </c>
       <c r="U59">
         <v>0.2067366166625341</v>
       </c>
       <c r="V59">
-        <v>0.0509529066693169</v>
+        <v>0.0500744082784666</v>
       </c>
       <c r="W59">
-        <v>0.1962027851285977</v>
+        <v>0.1963844029136655</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6169,7 +6169,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.4076232533545352</v>
+        <v>0.4005952662277329</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6177,22 +6177,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1825682490643824</v>
+        <v>0.1841776152310077</v>
       </c>
       <c r="C60">
-        <v>-42212.81264639985</v>
+        <v>-45444.04621600997</v>
       </c>
       <c r="D60">
-        <v>81748.69051718923</v>
+        <v>80797.93286419273</v>
       </c>
       <c r="E60">
-        <v>124257.6115022286</v>
+        <v>126538.0874188422</v>
       </c>
       <c r="F60">
-        <v>132267.6031635891</v>
+        <v>134548.0790802027</v>
       </c>
       <c r="G60">
         <v>8306.1</v>
@@ -6213,37 +6213,37 @@
         <v>10954.1</v>
       </c>
       <c r="M60">
-        <v>27344.5567721031</v>
+        <v>27816.01464748419</v>
       </c>
       <c r="N60">
-        <v>-16390.4567721031</v>
+        <v>-16861.91464748419</v>
       </c>
       <c r="O60">
-        <v>-2048.807096512887</v>
+        <v>-2107.739330935524</v>
       </c>
       <c r="P60">
-        <v>-14341.64967559021</v>
+        <v>-14754.17531654867</v>
       </c>
       <c r="Q60">
-        <v>-13196.64967559021</v>
+        <v>-13609.17531654867</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1634887985106105</v>
+        <v>0.1663592570108693</v>
       </c>
       <c r="T60">
-        <v>2.293973737017272</v>
+        <v>2.349924315968913</v>
       </c>
       <c r="U60">
         <v>0.2067366166625341</v>
       </c>
       <c r="V60">
-        <v>0.05007440827846662</v>
+        <v>0.04922568949408582</v>
       </c>
       <c r="W60">
-        <v>0.1963844029136655</v>
+        <v>0.1965598641636463</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6251,7 +6251,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.400595266227733</v>
+        <v>0.3938055159526865</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6259,22 +6259,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1841776152310077</v>
+        <v>0.1857869813976331</v>
       </c>
       <c r="C61">
-        <v>-45444.04621600997</v>
+        <v>-48653.41893564514</v>
       </c>
       <c r="D61">
-        <v>80797.93286419273</v>
+        <v>79869.03606117115</v>
       </c>
       <c r="E61">
-        <v>126538.0874188422</v>
+        <v>128818.5633354558</v>
       </c>
       <c r="F61">
-        <v>134548.0790802027</v>
+        <v>136828.5549968163</v>
       </c>
       <c r="G61">
         <v>8306.1</v>
@@ -6295,37 +6295,37 @@
         <v>10954.1</v>
       </c>
       <c r="M61">
-        <v>27816.01464748419</v>
+        <v>28287.47252286528</v>
       </c>
       <c r="N61">
-        <v>-16861.91464748419</v>
+        <v>-17333.37252286528</v>
       </c>
       <c r="O61">
-        <v>-2107.739330935524</v>
+        <v>-2166.67156535816</v>
       </c>
       <c r="P61">
-        <v>-14754.17531654867</v>
+        <v>-15166.70095750712</v>
       </c>
       <c r="Q61">
-        <v>-13609.17531654867</v>
+        <v>-14021.70095750712</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1663592570108693</v>
+        <v>0.169373238436141</v>
       </c>
       <c r="T61">
-        <v>2.349924315968913</v>
+        <v>2.408672423868136</v>
       </c>
       <c r="U61">
         <v>0.2067366166625341</v>
       </c>
       <c r="V61">
-        <v>0.04922568949408582</v>
+        <v>0.04840526133585106</v>
       </c>
       <c r="W61">
-        <v>0.1965598641636463</v>
+        <v>0.1967294767052945</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6333,7 +6333,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.3938055159526865</v>
+        <v>0.3872420906868085</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6341,22 +6341,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1857869813976331</v>
+        <v>0.1873963475642584</v>
       </c>
       <c r="C62">
-        <v>-48653.41893564514</v>
+        <v>-51841.67620826791</v>
       </c>
       <c r="D62">
-        <v>79869.03606117115</v>
+        <v>78961.25470516201</v>
       </c>
       <c r="E62">
-        <v>128818.5633354558</v>
+        <v>131099.0392520694</v>
       </c>
       <c r="F62">
-        <v>136828.5549968163</v>
+        <v>139109.0309134299</v>
       </c>
       <c r="G62">
         <v>8306.1</v>
@@ -6377,37 +6377,37 @@
         <v>10954.1</v>
       </c>
       <c r="M62">
-        <v>28287.47252286528</v>
+        <v>28758.93039824636</v>
       </c>
       <c r="N62">
-        <v>-17333.37252286528</v>
+        <v>-17804.83039824637</v>
       </c>
       <c r="O62">
-        <v>-2166.67156535816</v>
+        <v>-2225.603799780796</v>
       </c>
       <c r="P62">
-        <v>-15166.70095750712</v>
+        <v>-15579.22659846557</v>
       </c>
       <c r="Q62">
-        <v>-14021.70095750712</v>
+        <v>-14434.22659846557</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.169373238436141</v>
+        <v>0.1725417830114267</v>
       </c>
       <c r="T62">
-        <v>2.408672423868136</v>
+        <v>2.47043325524937</v>
       </c>
       <c r="U62">
         <v>0.2067366166625341</v>
       </c>
       <c r="V62">
-        <v>0.04840526133585106</v>
+        <v>0.04761173246149285</v>
       </c>
       <c r="W62">
-        <v>0.1967294767052945</v>
+        <v>0.1968935281800033</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6415,7 +6415,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.3872420906868085</v>
+        <v>0.3808938596919428</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1873963475642584</v>
+        <v>0.1890057137308838</v>
       </c>
       <c r="C63">
-        <v>-51841.67620826791</v>
+        <v>-55009.52992906312</v>
       </c>
       <c r="D63">
-        <v>78961.25470516201</v>
+        <v>78073.87690098038</v>
       </c>
       <c r="E63">
-        <v>131099.0392520694</v>
+        <v>133379.515168683</v>
       </c>
       <c r="F63">
-        <v>139109.0309134299</v>
+        <v>141389.5068300435</v>
       </c>
       <c r="G63">
         <v>8306.1</v>
@@ -6459,37 +6459,37 @@
         <v>10954.1</v>
       </c>
       <c r="M63">
-        <v>28758.93039824636</v>
+        <v>29230.38827362745</v>
       </c>
       <c r="N63">
-        <v>-17804.83039824637</v>
+        <v>-18276.28827362745</v>
       </c>
       <c r="O63">
-        <v>-2225.603799780796</v>
+        <v>-2284.536034203431</v>
       </c>
       <c r="P63">
-        <v>-15579.22659846557</v>
+        <v>-15991.75223942402</v>
       </c>
       <c r="Q63">
-        <v>-14434.22659846557</v>
+        <v>-14846.75223942402</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1725417830114267</v>
+        <v>0.1758770930906748</v>
       </c>
       <c r="T63">
-        <v>2.47043325524937</v>
+        <v>2.535444656703302</v>
       </c>
       <c r="U63">
         <v>0.2067366166625341</v>
       </c>
       <c r="V63">
-        <v>0.04761173246149285</v>
+        <v>0.04684380129275909</v>
       </c>
       <c r="W63">
-        <v>0.1968935281800033</v>
+        <v>0.197052287671657</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6497,7 +6497,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.3808938596919428</v>
+        <v>0.3747504103420728</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6505,22 +6505,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1890057137308838</v>
+        <v>0.1906150798975091</v>
       </c>
       <c r="C64">
-        <v>-55009.52992906312</v>
+        <v>-58157.66034733941</v>
       </c>
       <c r="D64">
-        <v>78073.87690098038</v>
+        <v>77206.22239931772</v>
       </c>
       <c r="E64">
-        <v>133379.515168683</v>
+        <v>135659.9910852966</v>
       </c>
       <c r="F64">
-        <v>141389.5068300435</v>
+        <v>143669.9827466571</v>
       </c>
       <c r="G64">
         <v>8306.1</v>
@@ -6541,37 +6541,37 @@
         <v>10954.1</v>
       </c>
       <c r="M64">
-        <v>29230.38827362745</v>
+        <v>29701.84614900854</v>
       </c>
       <c r="N64">
-        <v>-18276.28827362745</v>
+        <v>-18747.74614900854</v>
       </c>
       <c r="O64">
-        <v>-2284.536034203431</v>
+        <v>-2343.468268626068</v>
       </c>
       <c r="P64">
-        <v>-15991.75223942402</v>
+        <v>-16404.27788038248</v>
       </c>
       <c r="Q64">
-        <v>-14846.75223942402</v>
+        <v>-15259.27788038248</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1758770930906748</v>
+        <v>0.1793926902012336</v>
       </c>
       <c r="T64">
-        <v>2.535444656703302</v>
+        <v>2.603970187965553</v>
       </c>
       <c r="U64">
         <v>0.2067366166625341</v>
       </c>
       <c r="V64">
-        <v>0.04684380129275909</v>
+        <v>0.04610024889128672</v>
       </c>
       <c r="W64">
-        <v>0.197052287671657</v>
+        <v>0.1972060071794488</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6579,7 +6579,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.3747504103420728</v>
+        <v>0.3688019911302938</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6587,22 +6587,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1906150798975091</v>
+        <v>0.1922244460641345</v>
       </c>
       <c r="C65">
-        <v>-58157.66034733941</v>
+        <v>-61286.71780564444</v>
       </c>
       <c r="D65">
-        <v>77206.22239931772</v>
+        <v>76357.64085762631</v>
       </c>
       <c r="E65">
-        <v>135659.9910852966</v>
+        <v>137940.4670019102</v>
       </c>
       <c r="F65">
-        <v>143669.9827466571</v>
+        <v>145950.4586632708</v>
       </c>
       <c r="G65">
         <v>8306.1</v>
@@ -6623,37 +6623,37 @@
         <v>10954.1</v>
       </c>
       <c r="M65">
-        <v>29701.84614900854</v>
+        <v>30173.30402438963</v>
       </c>
       <c r="N65">
-        <v>-18747.74614900854</v>
+        <v>-19219.20402438963</v>
       </c>
       <c r="O65">
-        <v>-2343.468268626068</v>
+        <v>-2402.400503048704</v>
       </c>
       <c r="P65">
-        <v>-16404.27788038248</v>
+        <v>-16816.80352134093</v>
       </c>
       <c r="Q65">
-        <v>-15259.27788038248</v>
+        <v>-15671.80352134093</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1793926902012336</v>
+        <v>0.183103598262379</v>
       </c>
       <c r="T65">
-        <v>2.603970187965553</v>
+        <v>2.676302693186818</v>
       </c>
       <c r="U65">
         <v>0.2067366166625341</v>
       </c>
       <c r="V65">
-        <v>0.04610024889128672</v>
+        <v>0.04537993250236037</v>
       </c>
       <c r="W65">
-        <v>0.1972060071794488</v>
+        <v>0.1973549229526219</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6661,7 +6661,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.3688019911302938</v>
+        <v>0.3630394600188829</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6669,22 +6669,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1922244460641345</v>
+        <v>0.1938338122307598</v>
       </c>
       <c r="C66">
-        <v>-61286.71780564444</v>
+        <v>-64397.3243654386</v>
       </c>
       <c r="D66">
-        <v>76357.64085762631</v>
+        <v>75527.51021444573</v>
       </c>
       <c r="E66">
-        <v>137940.4670019102</v>
+        <v>140220.9429185238</v>
       </c>
       <c r="F66">
-        <v>145950.4586632708</v>
+        <v>148230.9345798843</v>
       </c>
       <c r="G66">
         <v>8306.1</v>
@@ -6705,37 +6705,37 @@
         <v>10954.1</v>
       </c>
       <c r="M66">
-        <v>30173.30402438963</v>
+        <v>30644.76189977072</v>
       </c>
       <c r="N66">
-        <v>-19219.20402438963</v>
+        <v>-19690.66189977072</v>
       </c>
       <c r="O66">
-        <v>-2402.400503048704</v>
+        <v>-2461.33273747134</v>
       </c>
       <c r="P66">
-        <v>-16816.80352134093</v>
+        <v>-17229.32916229938</v>
       </c>
       <c r="Q66">
-        <v>-15671.80352134093</v>
+        <v>-16084.32916229938</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.183103598262379</v>
+        <v>0.1870265582127326</v>
       </c>
       <c r="T66">
-        <v>2.676302693186818</v>
+        <v>2.752768484420728</v>
       </c>
       <c r="U66">
         <v>0.2067366166625341</v>
       </c>
       <c r="V66">
-        <v>0.04537993250236037</v>
+        <v>0.04468177969463175</v>
       </c>
       <c r="W66">
-        <v>0.1973549229526219</v>
+        <v>0.1974992567020052</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6743,7 +6743,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.3630394600188829</v>
+        <v>0.357454237557054</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6751,22 +6751,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1938338122307598</v>
+        <v>0.1954431783973852</v>
       </c>
       <c r="C67">
-        <v>-64397.3243654386</v>
+        <v>-67490.07532786684</v>
       </c>
       <c r="D67">
-        <v>75527.51021444573</v>
+        <v>74715.23516863112</v>
       </c>
       <c r="E67">
-        <v>140220.9429185238</v>
+        <v>142501.4188351374</v>
       </c>
       <c r="F67">
-        <v>148230.9345798843</v>
+        <v>150511.410496498</v>
       </c>
       <c r="G67">
         <v>8306.1</v>
@@ -6787,37 +6787,37 @@
         <v>10954.1</v>
       </c>
       <c r="M67">
-        <v>30644.76189977072</v>
+        <v>31116.21977515181</v>
       </c>
       <c r="N67">
-        <v>-19690.66189977072</v>
+        <v>-20162.11977515181</v>
       </c>
       <c r="O67">
-        <v>-2461.33273747134</v>
+        <v>-2520.264971893977</v>
       </c>
       <c r="P67">
-        <v>-17229.32916229938</v>
+        <v>-17641.85480325784</v>
       </c>
       <c r="Q67">
-        <v>-16084.32916229938</v>
+        <v>-16496.85480325784</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1870265582127326</v>
+        <v>0.1911802805131071</v>
       </c>
       <c r="T67">
-        <v>2.752768484420728</v>
+        <v>2.833732263374279</v>
       </c>
       <c r="U67">
         <v>0.2067366166625341</v>
       </c>
       <c r="V67">
-        <v>0.04468177969463175</v>
+        <v>0.04400478303259187</v>
       </c>
       <c r="W67">
-        <v>0.1974992567020052</v>
+        <v>0.1976392167014072</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6825,7 +6825,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.357454237557054</v>
+        <v>0.3520382642607349</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6833,22 +6833,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1954431783973852</v>
+        <v>0.1970525445640105</v>
       </c>
       <c r="C68">
-        <v>-67490.07532786684</v>
+        <v>-70565.54065744176</v>
       </c>
       <c r="D68">
-        <v>74715.23516863112</v>
+        <v>73920.24575566979</v>
       </c>
       <c r="E68">
-        <v>142501.4188351374</v>
+        <v>144781.894751751</v>
       </c>
       <c r="F68">
-        <v>150511.410496498</v>
+        <v>152791.8864131116</v>
       </c>
       <c r="G68">
         <v>8306.1</v>
@@ -6869,37 +6869,37 @@
         <v>10954.1</v>
       </c>
       <c r="M68">
-        <v>31116.21977515181</v>
+        <v>31587.6776505329</v>
       </c>
       <c r="N68">
-        <v>-20162.11977515181</v>
+        <v>-20633.5776505329</v>
       </c>
       <c r="O68">
-        <v>-2520.264971893977</v>
+        <v>-2579.197206316612</v>
       </c>
       <c r="P68">
-        <v>-17641.85480325784</v>
+        <v>-18054.38044421629</v>
       </c>
       <c r="Q68">
-        <v>-16496.85480325784</v>
+        <v>-16909.38044421629</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1911802805131071</v>
+        <v>0.1955857435589588</v>
       </c>
       <c r="T68">
-        <v>2.833732263374279</v>
+        <v>2.919602938021983</v>
       </c>
       <c r="U68">
         <v>0.2067366166625341</v>
       </c>
       <c r="V68">
-        <v>0.04400478303259187</v>
+        <v>0.04334799522613527</v>
       </c>
       <c r="W68">
-        <v>0.1976392167014072</v>
+        <v>0.1977749987903792</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.3520382642607349</v>
+        <v>0.3467839618090822</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6915,22 +6915,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1970525445640105</v>
+        <v>0.1986619107306359</v>
       </c>
       <c r="C69">
-        <v>-70565.54065744176</v>
+        <v>-73624.2663157941</v>
       </c>
       <c r="D69">
-        <v>73920.24575566979</v>
+        <v>73141.99601393107</v>
       </c>
       <c r="E69">
-        <v>144781.894751751</v>
+        <v>147062.3706683647</v>
       </c>
       <c r="F69">
-        <v>152791.8864131116</v>
+        <v>155072.3623297252</v>
       </c>
       <c r="G69">
         <v>8306.1</v>
@@ -6951,37 +6951,37 @@
         <v>10954.1</v>
       </c>
       <c r="M69">
-        <v>31587.6776505329</v>
+        <v>32059.13552591399</v>
       </c>
       <c r="N69">
-        <v>-20633.5776505329</v>
+        <v>-21105.03552591399</v>
       </c>
       <c r="O69">
-        <v>-2579.197206316612</v>
+        <v>-2638.129440739248</v>
       </c>
       <c r="P69">
-        <v>-18054.38044421629</v>
+        <v>-18466.90608517474</v>
       </c>
       <c r="Q69">
-        <v>-16909.38044421629</v>
+        <v>-17321.90608517474</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1955857435589588</v>
+        <v>0.2002665480451764</v>
       </c>
       <c r="T69">
-        <v>2.919602938021983</v>
+        <v>3.010840529835171</v>
       </c>
       <c r="U69">
         <v>0.2067366166625341</v>
       </c>
       <c r="V69">
-        <v>0.04334799522613527</v>
+        <v>0.04271052470810387</v>
       </c>
       <c r="W69">
-        <v>0.1977749987903792</v>
+        <v>0.1979067872884991</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6989,7 +6989,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.3467839618090822</v>
+        <v>0.3416841976648309</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6997,22 +6997,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1986619107306359</v>
+        <v>0.2002712768972612</v>
       </c>
       <c r="C70">
-        <v>-73624.2663157941</v>
+        <v>-76666.77551204815</v>
       </c>
       <c r="D70">
-        <v>73141.99601393107</v>
+        <v>72379.96273429062</v>
       </c>
       <c r="E70">
-        <v>147062.3706683647</v>
+        <v>149342.8465849783</v>
       </c>
       <c r="F70">
-        <v>155072.3623297252</v>
+        <v>157352.8382463388</v>
       </c>
       <c r="G70">
         <v>8306.1</v>
@@ -7033,37 +7033,37 @@
         <v>10954.1</v>
       </c>
       <c r="M70">
-        <v>32059.13552591399</v>
+        <v>32530.59340129507</v>
       </c>
       <c r="N70">
-        <v>-21105.03552591399</v>
+        <v>-21576.49340129507</v>
       </c>
       <c r="O70">
-        <v>-2638.129440739248</v>
+        <v>-2697.061675161884</v>
       </c>
       <c r="P70">
-        <v>-18466.90608517474</v>
+        <v>-18879.43172613319</v>
       </c>
       <c r="Q70">
-        <v>-17321.90608517474</v>
+        <v>-17734.43172613319</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2002665480451764</v>
+        <v>0.2052493399176014</v>
       </c>
       <c r="T70">
-        <v>3.010840529835171</v>
+        <v>3.10796441789437</v>
       </c>
       <c r="U70">
         <v>0.2067366166625341</v>
       </c>
       <c r="V70">
-        <v>0.04271052470810387</v>
+        <v>0.04209153159639222</v>
       </c>
       <c r="W70">
-        <v>0.1979067872884991</v>
+        <v>0.1980347558301518</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7071,7 +7071,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.3416841976648309</v>
+        <v>0.3367322527711378</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7079,22 +7079,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2002712768972612</v>
+        <v>0.2018806430638865</v>
       </c>
       <c r="C71">
-        <v>-76666.77551204815</v>
+        <v>-79693.56987584096</v>
       </c>
       <c r="D71">
-        <v>72379.96273429062</v>
+        <v>71633.64428711143</v>
       </c>
       <c r="E71">
-        <v>149342.8465849783</v>
+        <v>151623.3225015919</v>
       </c>
       <c r="F71">
-        <v>157352.8382463388</v>
+        <v>159633.3141629524</v>
       </c>
       <c r="G71">
         <v>8306.1</v>
@@ -7115,37 +7115,37 @@
         <v>10954.1</v>
       </c>
       <c r="M71">
-        <v>32530.59340129507</v>
+        <v>33002.05127667616</v>
       </c>
       <c r="N71">
-        <v>-21576.49340129507</v>
+        <v>-22047.95127667616</v>
       </c>
       <c r="O71">
-        <v>-2697.061675161884</v>
+        <v>-2755.99390958452</v>
       </c>
       <c r="P71">
-        <v>-18879.43172613319</v>
+        <v>-19291.95736709164</v>
       </c>
       <c r="Q71">
-        <v>-17734.43172613319</v>
+        <v>-18146.95736709164</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2052493399176014</v>
+        <v>0.2105643179148547</v>
       </c>
       <c r="T71">
-        <v>3.10796441789437</v>
+        <v>3.211563231824182</v>
       </c>
       <c r="U71">
         <v>0.2067366166625341</v>
       </c>
       <c r="V71">
-        <v>0.04209153159639222</v>
+        <v>0.04149022400215804</v>
       </c>
       <c r="W71">
-        <v>0.1980347558301518</v>
+        <v>0.1981590681277573</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7153,7 +7153,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.3367322527711378</v>
+        <v>0.3319217920172643</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7161,22 +7161,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2018806430638865</v>
+        <v>0.2034900092305119</v>
       </c>
       <c r="C72">
-        <v>-79693.56987584096</v>
+        <v>-82705.13055851113</v>
       </c>
       <c r="D72">
-        <v>71633.64428711143</v>
+        <v>70902.55952105485</v>
       </c>
       <c r="E72">
-        <v>151623.3225015919</v>
+        <v>153903.7984182055</v>
       </c>
       <c r="F72">
-        <v>159633.3141629524</v>
+        <v>161913.790079566</v>
       </c>
       <c r="G72">
         <v>8306.1</v>
@@ -7197,37 +7197,37 @@
         <v>10954.1</v>
       </c>
       <c r="M72">
-        <v>33002.05127667616</v>
+        <v>33473.50915205725</v>
       </c>
       <c r="N72">
-        <v>-22047.95127667616</v>
+        <v>-22519.40915205725</v>
       </c>
       <c r="O72">
-        <v>-2755.99390958452</v>
+        <v>-2814.926144007156</v>
       </c>
       <c r="P72">
-        <v>-19291.95736709164</v>
+        <v>-19704.48300805009</v>
       </c>
       <c r="Q72">
-        <v>-18146.95736709164</v>
+        <v>-18559.48300805009</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2105643179148547</v>
+        <v>0.2162458461188153</v>
       </c>
       <c r="T72">
-        <v>3.211563231824182</v>
+        <v>3.322306791542258</v>
       </c>
       <c r="U72">
         <v>0.2067366166625341</v>
       </c>
       <c r="V72">
-        <v>0.04149022400215804</v>
+        <v>0.04090585465001498</v>
       </c>
       <c r="W72">
-        <v>0.1981590681277573</v>
+        <v>0.1982798786705006</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7235,7 +7235,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.3319217920172643</v>
+        <v>0.3272468372001198</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7243,22 +7243,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2034900092305119</v>
+        <v>0.2050993753971372</v>
       </c>
       <c r="C73">
-        <v>-82705.1305585111</v>
+        <v>-85701.91926753745</v>
       </c>
       <c r="D73">
-        <v>70902.55952105485</v>
+        <v>70186.24672864212</v>
       </c>
       <c r="E73">
-        <v>153903.7984182054</v>
+        <v>156184.2743348191</v>
       </c>
       <c r="F73">
-        <v>161913.790079566</v>
+        <v>164194.2659961796</v>
       </c>
       <c r="G73">
         <v>8306.1</v>
@@ -7279,37 +7279,37 @@
         <v>10954.1</v>
       </c>
       <c r="M73">
-        <v>33473.50915205724</v>
+        <v>33944.96702743833</v>
       </c>
       <c r="N73">
-        <v>-22519.40915205724</v>
+        <v>-22990.86702743833</v>
       </c>
       <c r="O73">
-        <v>-2814.926144007155</v>
+        <v>-2873.858378429792</v>
       </c>
       <c r="P73">
-        <v>-19704.48300805008</v>
+        <v>-20117.00864900854</v>
       </c>
       <c r="Q73">
-        <v>-18559.48300805008</v>
+        <v>-18972.00864900854</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2162458461188152</v>
+        <v>0.2223331977659158</v>
       </c>
       <c r="T73">
-        <v>3.322306791542257</v>
+        <v>3.440960605525909</v>
       </c>
       <c r="U73">
         <v>0.2067366166625341</v>
       </c>
       <c r="V73">
-        <v>0.04090585465001498</v>
+        <v>0.04033771777987588</v>
       </c>
       <c r="W73">
-        <v>0.1982798786705006</v>
+        <v>0.1983973333648344</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7317,7 +7317,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.3272468372001199</v>
+        <v>0.3227017422390071</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7325,22 +7325,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2050993753971372</v>
+        <v>0.2067087415637625</v>
       </c>
       <c r="C74">
-        <v>-85701.91926753745</v>
+        <v>-88684.37923890007</v>
       </c>
       <c r="D74">
-        <v>70186.24672864212</v>
+        <v>69484.26267389308</v>
       </c>
       <c r="E74">
-        <v>156184.2743348191</v>
+        <v>158464.7502514326</v>
       </c>
       <c r="F74">
-        <v>164194.2659961796</v>
+        <v>166474.7419127932</v>
       </c>
       <c r="G74">
         <v>8306.1</v>
@@ -7361,37 +7361,37 @@
         <v>10954.1</v>
       </c>
       <c r="M74">
-        <v>33944.96702743833</v>
+        <v>34416.42490281942</v>
       </c>
       <c r="N74">
-        <v>-22990.86702743833</v>
+        <v>-23462.32490281942</v>
       </c>
       <c r="O74">
-        <v>-2873.858378429792</v>
+        <v>-2932.790612852427</v>
       </c>
       <c r="P74">
-        <v>-20117.00864900854</v>
+        <v>-20529.53428996699</v>
       </c>
       <c r="Q74">
-        <v>-18972.00864900854</v>
+        <v>-19384.53428996699</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2223331977659158</v>
+        <v>0.2288714643498385</v>
       </c>
       <c r="T74">
-        <v>3.440960605525909</v>
+        <v>3.568403590915757</v>
       </c>
       <c r="U74">
         <v>0.2067366166625341</v>
       </c>
       <c r="V74">
-        <v>0.04033771777987588</v>
+        <v>0.03978514630343923</v>
       </c>
       <c r="W74">
-        <v>0.1983973333648344</v>
+        <v>0.1985115701223371</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7399,7 +7399,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.3227017422390071</v>
+        <v>0.3182811704275138</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7407,22 +7407,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2067087415637625</v>
+        <v>0.2083181077303879</v>
       </c>
       <c r="C75">
-        <v>-88684.37923890007</v>
+        <v>-91652.93615166823</v>
       </c>
       <c r="D75">
-        <v>69484.26267389308</v>
+        <v>68796.18167773855</v>
       </c>
       <c r="E75">
-        <v>158464.7502514326</v>
+        <v>160745.2261680463</v>
       </c>
       <c r="F75">
-        <v>166474.7419127932</v>
+        <v>168755.2178294068</v>
       </c>
       <c r="G75">
         <v>8306.1</v>
@@ -7443,37 +7443,37 @@
         <v>10954.1</v>
       </c>
       <c r="M75">
-        <v>34416.42490281942</v>
+        <v>34887.88277820051</v>
       </c>
       <c r="N75">
-        <v>-23462.32490281942</v>
+        <v>-23933.78277820051</v>
       </c>
       <c r="O75">
-        <v>-2932.790612852427</v>
+        <v>-2991.722847275064</v>
       </c>
       <c r="P75">
-        <v>-20529.53428996699</v>
+        <v>-20942.05993092545</v>
       </c>
       <c r="Q75">
-        <v>-19384.53428996699</v>
+        <v>-19797.05993092545</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2288714643498385</v>
+        <v>0.2359126745171401</v>
       </c>
       <c r="T75">
-        <v>3.568403590915757</v>
+        <v>3.705649882874056</v>
       </c>
       <c r="U75">
         <v>0.2067366166625341</v>
       </c>
       <c r="V75">
-        <v>0.03978514630343923</v>
+        <v>0.03924750919123059</v>
       </c>
       <c r="W75">
-        <v>0.1985115701223371</v>
+        <v>0.1986227193999074</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7481,7 +7481,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.3182811704275138</v>
+        <v>0.3139800735298447</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7489,22 +7489,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2083181077303879</v>
+        <v>0.2099274738970132</v>
       </c>
       <c r="C76">
-        <v>-91652.93615166823</v>
+        <v>-94607.99898877894</v>
       </c>
       <c r="D76">
-        <v>68796.18167773855</v>
+        <v>68121.59475724143</v>
       </c>
       <c r="E76">
-        <v>160745.2261680463</v>
+        <v>163025.7020846599</v>
       </c>
       <c r="F76">
-        <v>168755.2178294068</v>
+        <v>171035.6937460204</v>
       </c>
       <c r="G76">
         <v>8306.1</v>
@@ -7525,37 +7525,37 @@
         <v>10954.1</v>
       </c>
       <c r="M76">
-        <v>34887.88277820051</v>
+        <v>35359.3406535816</v>
       </c>
       <c r="N76">
-        <v>-23933.78277820051</v>
+        <v>-24405.2406535816</v>
       </c>
       <c r="O76">
-        <v>-2991.722847275064</v>
+        <v>-3050.6550816977</v>
       </c>
       <c r="P76">
-        <v>-20942.05993092545</v>
+        <v>-21354.5855718839</v>
       </c>
       <c r="Q76">
-        <v>-19797.05993092545</v>
+        <v>-20209.5855718839</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2359126745171401</v>
+        <v>0.2435171814978257</v>
       </c>
       <c r="T76">
-        <v>3.705649882874056</v>
+        <v>3.853875878189018</v>
       </c>
       <c r="U76">
         <v>0.2067366166625341</v>
       </c>
       <c r="V76">
-        <v>0.03924750919123059</v>
+        <v>0.03872420906868085</v>
       </c>
       <c r="W76">
-        <v>0.1986227193999074</v>
+        <v>0.1987309046967424</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.3139800735298447</v>
+        <v>0.3097936725494468</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7571,22 +7571,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2099274738970132</v>
+        <v>0.2115368400636385</v>
       </c>
       <c r="C77">
-        <v>-94607.99898877894</v>
+        <v>-97549.96084766569</v>
       </c>
       <c r="D77">
-        <v>68121.59475724143</v>
+        <v>67460.10881496831</v>
       </c>
       <c r="E77">
-        <v>163025.7020846599</v>
+        <v>165306.1780012735</v>
       </c>
       <c r="F77">
-        <v>171035.6937460204</v>
+        <v>173316.169662634</v>
       </c>
       <c r="G77">
         <v>8306.1</v>
@@ -7607,37 +7607,37 @@
         <v>10954.1</v>
       </c>
       <c r="M77">
-        <v>35359.3406535816</v>
+        <v>35830.79852896269</v>
       </c>
       <c r="N77">
-        <v>-24405.2406535816</v>
+        <v>-24876.69852896269</v>
       </c>
       <c r="O77">
-        <v>-3050.6550816977</v>
+        <v>-3109.587316120336</v>
       </c>
       <c r="P77">
-        <v>-21354.5855718839</v>
+        <v>-21767.11121284236</v>
       </c>
       <c r="Q77">
-        <v>-20209.5855718839</v>
+        <v>-20622.11121284236</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2435171814978257</v>
+        <v>0.2517553973935684</v>
       </c>
       <c r="T77">
-        <v>3.853875878189018</v>
+        <v>4.014454039780228</v>
       </c>
       <c r="U77">
         <v>0.2067366166625341</v>
       </c>
       <c r="V77">
-        <v>0.03872420906868085</v>
+        <v>0.03821468000198767</v>
       </c>
       <c r="W77">
-        <v>0.1987309046967424</v>
+        <v>0.1988362430120817</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.3097936725494468</v>
+        <v>0.3057174400159014</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7653,22 +7653,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2115368400636385</v>
+        <v>0.2131462062302639</v>
       </c>
       <c r="C78">
-        <v>-97549.96084766569</v>
+        <v>-100479.1997041113</v>
       </c>
       <c r="D78">
-        <v>67460.10881496831</v>
+        <v>66811.34587513632</v>
       </c>
       <c r="E78">
-        <v>165306.1780012735</v>
+        <v>167586.6539178871</v>
       </c>
       <c r="F78">
-        <v>173316.169662634</v>
+        <v>175596.6455792476</v>
       </c>
       <c r="G78">
         <v>8306.1</v>
@@ -7689,37 +7689,37 @@
         <v>10954.1</v>
       </c>
       <c r="M78">
-        <v>35830.79852896269</v>
+        <v>36302.25640434377</v>
       </c>
       <c r="N78">
-        <v>-24876.69852896269</v>
+        <v>-25348.15640434378</v>
       </c>
       <c r="O78">
-        <v>-3109.587316120336</v>
+        <v>-3168.519550542972</v>
       </c>
       <c r="P78">
-        <v>-21767.11121284236</v>
+        <v>-22179.6368538008</v>
       </c>
       <c r="Q78">
-        <v>-20622.11121284236</v>
+        <v>-21034.6368538008</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2517553973935684</v>
+        <v>0.260709979888941</v>
       </c>
       <c r="T78">
-        <v>4.014454039780228</v>
+        <v>4.188995519770672</v>
       </c>
       <c r="U78">
         <v>0.2067366166625341</v>
       </c>
       <c r="V78">
-        <v>0.03821468000198767</v>
+        <v>0.03771838545650732</v>
       </c>
       <c r="W78">
-        <v>0.1988362430120817</v>
+        <v>0.1989388452672824</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7727,7 +7727,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.3057174400159014</v>
+        <v>0.3017470836520585</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7735,22 +7735,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2131462062302639</v>
+        <v>0.2147555723968892</v>
       </c>
       <c r="C79">
-        <v>-100479.1997041113</v>
+        <v>-103396.0791324455</v>
       </c>
       <c r="D79">
-        <v>66811.34587513632</v>
+        <v>66174.94236341568</v>
       </c>
       <c r="E79">
-        <v>167586.6539178871</v>
+        <v>169867.1298345007</v>
       </c>
       <c r="F79">
-        <v>175596.6455792476</v>
+        <v>177877.1214958612</v>
       </c>
       <c r="G79">
         <v>8306.1</v>
@@ -7771,37 +7771,37 @@
         <v>10954.1</v>
       </c>
       <c r="M79">
-        <v>36302.25640434377</v>
+        <v>36773.71427972486</v>
       </c>
       <c r="N79">
-        <v>-25348.15640434378</v>
+        <v>-25819.61427972486</v>
       </c>
       <c r="O79">
-        <v>-3168.519550542972</v>
+        <v>-3227.451784965608</v>
       </c>
       <c r="P79">
-        <v>-22179.6368538008</v>
+        <v>-22592.16249475925</v>
       </c>
       <c r="Q79">
-        <v>-21034.6368538008</v>
+        <v>-21447.16249475925</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.260709979888941</v>
+        <v>0.2704786153384383</v>
       </c>
       <c r="T79">
-        <v>4.188995519770672</v>
+        <v>4.379404407032975</v>
       </c>
       <c r="U79">
         <v>0.2067366166625341</v>
       </c>
       <c r="V79">
-        <v>0.03771838545650732</v>
+        <v>0.03723481641219312</v>
       </c>
       <c r="W79">
-        <v>0.1989388452672824</v>
+        <v>0.1990388166954267</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7809,7 +7809,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.3017470836520585</v>
+        <v>0.2978785312975449</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7817,22 +7817,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2147555723968892</v>
+        <v>0.2163649385635146</v>
       </c>
       <c r="C80">
-        <v>-103396.0791324455</v>
+        <v>-106300.94898497</v>
       </c>
       <c r="D80">
-        <v>66174.94236341568</v>
+        <v>65550.54842750485</v>
       </c>
       <c r="E80">
-        <v>169867.1298345007</v>
+        <v>172147.6057511143</v>
       </c>
       <c r="F80">
-        <v>177877.1214958612</v>
+        <v>180157.5974124748</v>
       </c>
       <c r="G80">
         <v>8306.1</v>
@@ -7853,37 +7853,37 @@
         <v>10954.1</v>
       </c>
       <c r="M80">
-        <v>36773.71427972486</v>
+        <v>37245.17215510595</v>
       </c>
       <c r="N80">
-        <v>-25819.61427972486</v>
+        <v>-26291.07215510595</v>
       </c>
       <c r="O80">
-        <v>-3227.451784965608</v>
+        <v>-3286.384019388244</v>
       </c>
       <c r="P80">
-        <v>-22592.16249475925</v>
+        <v>-23004.68813571771</v>
       </c>
       <c r="Q80">
-        <v>-21447.16249475925</v>
+        <v>-21859.68813571771</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2704786153384383</v>
+        <v>0.2811775970212211</v>
       </c>
       <c r="T80">
-        <v>4.379404407032975</v>
+        <v>4.587947474034547</v>
       </c>
       <c r="U80">
         <v>0.2067366166625341</v>
       </c>
       <c r="V80">
-        <v>0.03723481641219312</v>
+        <v>0.03676348962216536</v>
       </c>
       <c r="W80">
-        <v>0.1990388166954267</v>
+        <v>0.1991362572013395</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7891,7 +7891,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.2978785312975449</v>
+        <v>0.2941079169773229</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7899,22 +7899,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2163649385635146</v>
+        <v>0.2179743047301399</v>
       </c>
       <c r="C81">
-        <v>-106300.94898497</v>
+        <v>-109194.146033278</v>
       </c>
       <c r="D81">
-        <v>65550.54842750485</v>
+        <v>64937.82729581038</v>
       </c>
       <c r="E81">
-        <v>172147.6057511143</v>
+        <v>174428.0816677279</v>
       </c>
       <c r="F81">
-        <v>180157.5974124748</v>
+        <v>182438.0733290884</v>
       </c>
       <c r="G81">
         <v>8306.1</v>
@@ -7935,37 +7935,37 @@
         <v>10954.1</v>
       </c>
       <c r="M81">
-        <v>37245.17215510595</v>
+        <v>37716.63003048704</v>
       </c>
       <c r="N81">
-        <v>-26291.07215510595</v>
+        <v>-26762.53003048704</v>
       </c>
       <c r="O81">
-        <v>-3286.384019388244</v>
+        <v>-3345.31625381088</v>
       </c>
       <c r="P81">
-        <v>-23004.68813571771</v>
+        <v>-23417.21377667616</v>
       </c>
       <c r="Q81">
-        <v>-21859.68813571771</v>
+        <v>-22272.21377667616</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2811775970212211</v>
+        <v>0.2929464768722821</v>
       </c>
       <c r="T81">
-        <v>4.587947474034547</v>
+        <v>4.817344847736273</v>
       </c>
       <c r="U81">
         <v>0.2067366166625341</v>
       </c>
       <c r="V81">
-        <v>0.03676348962216536</v>
+        <v>0.03630394600188829</v>
       </c>
       <c r="W81">
-        <v>0.1991362572013395</v>
+        <v>0.1992312616946044</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7973,7 +7973,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.2941079169773229</v>
+        <v>0.2904315680151064</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7981,22 +7981,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2179743047301399</v>
+        <v>0.2195836708967653</v>
       </c>
       <c r="C82">
-        <v>-109194.146033278</v>
+        <v>-112075.9945739406</v>
       </c>
       <c r="D82">
-        <v>64937.82729581038</v>
+        <v>64336.45467176148</v>
       </c>
       <c r="E82">
-        <v>174428.0816677279</v>
+        <v>176708.5575843415</v>
       </c>
       <c r="F82">
-        <v>182438.0733290884</v>
+        <v>184718.549245702</v>
       </c>
       <c r="G82">
         <v>8306.1</v>
@@ -8017,37 +8017,37 @@
         <v>10954.1</v>
       </c>
       <c r="M82">
-        <v>37716.63003048704</v>
+        <v>38188.08790586813</v>
       </c>
       <c r="N82">
-        <v>-26762.53003048704</v>
+        <v>-27233.98790586813</v>
       </c>
       <c r="O82">
-        <v>-3345.31625381088</v>
+        <v>-3404.248488233517</v>
       </c>
       <c r="P82">
-        <v>-23417.21377667616</v>
+        <v>-23829.73941763462</v>
       </c>
       <c r="Q82">
-        <v>-22272.21377667616</v>
+        <v>-22684.73941763462</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2929464768722821</v>
+        <v>0.3059541861813497</v>
       </c>
       <c r="T82">
-        <v>4.817344847736273</v>
+        <v>5.070889313406605</v>
       </c>
       <c r="U82">
         <v>0.2067366166625341</v>
       </c>
       <c r="V82">
-        <v>0.03630394600188829</v>
+        <v>0.03585574913766745</v>
       </c>
       <c r="W82">
-        <v>0.1992312616946044</v>
+        <v>0.1993239203979122</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8055,7 +8055,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.2904315680151064</v>
+        <v>0.2868459931013395</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8063,22 +8063,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2195836708967653</v>
+        <v>0.2211930370633906</v>
       </c>
       <c r="C83">
-        <v>-112075.9945739406</v>
+        <v>-114946.8070008453</v>
       </c>
       <c r="D83">
-        <v>64336.45467176148</v>
+        <v>63746.11816147037</v>
       </c>
       <c r="E83">
-        <v>176708.5575843415</v>
+        <v>178989.0335009551</v>
       </c>
       <c r="F83">
-        <v>184718.549245702</v>
+        <v>186999.0251623156</v>
       </c>
       <c r="G83">
         <v>8306.1</v>
@@ -8099,37 +8099,37 @@
         <v>10954.1</v>
       </c>
       <c r="M83">
-        <v>38188.08790586813</v>
+        <v>38659.54578124922</v>
       </c>
       <c r="N83">
-        <v>-27233.98790586813</v>
+        <v>-27705.44578124922</v>
       </c>
       <c r="O83">
-        <v>-3404.248488233517</v>
+        <v>-3463.180722656152</v>
       </c>
       <c r="P83">
-        <v>-23829.73941763462</v>
+        <v>-24242.26505859307</v>
       </c>
       <c r="Q83">
-        <v>-22684.73941763462</v>
+        <v>-23097.26505859307</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3059541861813497</v>
+        <v>0.320407196524758</v>
       </c>
       <c r="T83">
-        <v>5.070889313406605</v>
+        <v>5.352605386373638</v>
       </c>
       <c r="U83">
         <v>0.2067366166625341</v>
       </c>
       <c r="V83">
-        <v>0.03585574913766745</v>
+        <v>0.03541848390428126</v>
       </c>
       <c r="W83">
-        <v>0.1993239203979122</v>
+        <v>0.1994143191328466</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8137,7 +8137,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.2868459931013395</v>
+        <v>0.2833478712342501</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8145,22 +8145,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2211930370633906</v>
+        <v>0.2228024032300159</v>
       </c>
       <c r="C84">
-        <v>-114946.8070008453</v>
+        <v>-117806.8843463132</v>
       </c>
       <c r="D84">
-        <v>63746.11816147037</v>
+        <v>63166.51673261606</v>
       </c>
       <c r="E84">
-        <v>178989.0335009551</v>
+        <v>181269.5094175687</v>
       </c>
       <c r="F84">
-        <v>186999.0251623156</v>
+        <v>189279.5010789293</v>
       </c>
       <c r="G84">
         <v>8306.1</v>
@@ -8181,37 +8181,37 @@
         <v>10954.1</v>
       </c>
       <c r="M84">
-        <v>38659.54578124922</v>
+        <v>39131.00365663031</v>
       </c>
       <c r="N84">
-        <v>-27705.44578124922</v>
+        <v>-28176.90365663031</v>
       </c>
       <c r="O84">
-        <v>-3463.180722656152</v>
+        <v>-3522.112957078789</v>
       </c>
       <c r="P84">
-        <v>-24242.26505859307</v>
+        <v>-24654.79069955152</v>
       </c>
       <c r="Q84">
-        <v>-23097.26505859307</v>
+        <v>-23509.79069955152</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.320407196524758</v>
+        <v>0.3365605610262143</v>
       </c>
       <c r="T84">
-        <v>5.352605386373638</v>
+        <v>5.667464526748558</v>
       </c>
       <c r="U84">
         <v>0.2067366166625341</v>
       </c>
       <c r="V84">
-        <v>0.03541848390428126</v>
+        <v>0.03499175518254292</v>
       </c>
       <c r="W84">
-        <v>0.1994143191328466</v>
+        <v>0.1995025395850115</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8219,7 +8219,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.2833478712342501</v>
+        <v>0.2799340414603434</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8227,22 +8227,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2228024032300159</v>
+        <v>0.2244117693966413</v>
       </c>
       <c r="C85">
-        <v>-117806.8843463132</v>
+        <v>-120656.5167929609</v>
       </c>
       <c r="D85">
-        <v>63166.51673261606</v>
+        <v>62597.36020258195</v>
       </c>
       <c r="E85">
-        <v>181269.5094175687</v>
+        <v>183549.9853341823</v>
       </c>
       <c r="F85">
-        <v>189279.5010789293</v>
+        <v>191559.9769955428</v>
       </c>
       <c r="G85">
         <v>8306.1</v>
@@ -8263,37 +8263,37 @@
         <v>10954.1</v>
       </c>
       <c r="M85">
-        <v>39131.00365663031</v>
+        <v>39602.4615320114</v>
       </c>
       <c r="N85">
-        <v>-28176.90365663031</v>
+        <v>-28648.3615320114</v>
       </c>
       <c r="O85">
-        <v>-3522.112957078789</v>
+        <v>-3581.045191501425</v>
       </c>
       <c r="P85">
-        <v>-24654.79069955152</v>
+        <v>-25067.31634050997</v>
       </c>
       <c r="Q85">
-        <v>-23509.79069955152</v>
+        <v>-23922.31634050997</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3365605610262143</v>
+        <v>0.3547330960903528</v>
       </c>
       <c r="T85">
-        <v>5.667464526748558</v>
+        <v>6.021681059670343</v>
       </c>
       <c r="U85">
         <v>0.2067366166625341</v>
       </c>
       <c r="V85">
-        <v>0.03499175518254292</v>
+        <v>0.03457518666846503</v>
       </c>
       <c r="W85">
-        <v>0.1995025395850115</v>
+        <v>0.1995886595502201</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8301,7 +8301,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.2799340414603434</v>
+        <v>0.2766014933477203</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8309,22 +8309,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2244117693966413</v>
+        <v>0.2260211355632666</v>
       </c>
       <c r="C86">
-        <v>-120656.5167929609</v>
+        <v>-123495.984158137</v>
       </c>
       <c r="D86">
-        <v>62597.36020258195</v>
+        <v>62038.36875401939</v>
       </c>
       <c r="E86">
-        <v>183549.9853341823</v>
+        <v>185830.4612507959</v>
       </c>
       <c r="F86">
-        <v>191559.9769955428</v>
+        <v>193840.4529121564</v>
       </c>
       <c r="G86">
         <v>8306.1</v>
@@ -8345,37 +8345,37 @@
         <v>10954.1</v>
       </c>
       <c r="M86">
-        <v>39602.46153201139</v>
+        <v>40073.91940739247</v>
       </c>
       <c r="N86">
-        <v>-28648.36153201139</v>
+        <v>-29119.81940739248</v>
       </c>
       <c r="O86">
-        <v>-3581.045191501424</v>
+        <v>-3639.977425924059</v>
       </c>
       <c r="P86">
-        <v>-25067.31634050997</v>
+        <v>-25479.84198146842</v>
       </c>
       <c r="Q86">
-        <v>-23922.31634050997</v>
+        <v>-24334.84198146842</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3547330960903526</v>
+        <v>0.3753286358297094</v>
       </c>
       <c r="T86">
-        <v>6.021681059670341</v>
+        <v>6.423126463648363</v>
       </c>
       <c r="U86">
         <v>0.2067366166625341</v>
       </c>
       <c r="V86">
-        <v>0.03457518666846504</v>
+        <v>0.0341684197664831</v>
       </c>
       <c r="W86">
-        <v>0.1995886595502201</v>
+        <v>0.1996727531633061</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.2766014933477203</v>
+        <v>0.2733473581318648</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8391,22 +8391,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2260211355632666</v>
+        <v>0.227630501729892</v>
       </c>
       <c r="C87">
-        <v>-123495.984158137</v>
+        <v>-126325.5563526329</v>
       </c>
       <c r="D87">
-        <v>62038.36875401939</v>
+        <v>61489.27247613714</v>
       </c>
       <c r="E87">
-        <v>185830.4612507959</v>
+        <v>188110.9371674095</v>
       </c>
       <c r="F87">
-        <v>193840.4529121564</v>
+        <v>196120.92882877</v>
       </c>
       <c r="G87">
         <v>8306.1</v>
@@ -8427,37 +8427,37 @@
         <v>10954.1</v>
       </c>
       <c r="M87">
-        <v>40073.91940739247</v>
+        <v>40545.37728277356</v>
       </c>
       <c r="N87">
-        <v>-29119.81940739248</v>
+        <v>-29591.27728277356</v>
       </c>
       <c r="O87">
-        <v>-3639.977425924059</v>
+        <v>-3698.909660346695</v>
       </c>
       <c r="P87">
-        <v>-25479.84198146842</v>
+        <v>-25892.36762242686</v>
       </c>
       <c r="Q87">
-        <v>-24334.84198146842</v>
+        <v>-24747.36762242686</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3753286358297094</v>
+        <v>0.3988663955318315</v>
       </c>
       <c r="T87">
-        <v>6.423126463648363</v>
+        <v>6.881921211051817</v>
       </c>
       <c r="U87">
         <v>0.2067366166625341</v>
       </c>
       <c r="V87">
-        <v>0.0341684197664831</v>
+        <v>0.03377111255989609</v>
       </c>
       <c r="W87">
-        <v>0.1996727531633061</v>
+        <v>0.1997548911109716</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8465,7 +8465,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.2733473581318648</v>
+        <v>0.2701689004791687</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8473,22 +8473,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.227630501729892</v>
+        <v>0.2292398678965173</v>
       </c>
       <c r="C88">
-        <v>-126325.5563526329</v>
+        <v>-129145.4938152466</v>
       </c>
       <c r="D88">
-        <v>61489.27247613714</v>
+        <v>60949.81093013709</v>
       </c>
       <c r="E88">
-        <v>188110.9371674095</v>
+        <v>190391.4130840231</v>
       </c>
       <c r="F88">
-        <v>196120.92882877</v>
+        <v>198401.4047453837</v>
       </c>
       <c r="G88">
         <v>8306.1</v>
@@ -8509,37 +8509,37 @@
         <v>10954.1</v>
       </c>
       <c r="M88">
-        <v>40545.37728277356</v>
+        <v>41016.83515815465</v>
       </c>
       <c r="N88">
-        <v>-29591.27728277356</v>
+        <v>-30062.73515815465</v>
       </c>
       <c r="O88">
-        <v>-3698.909660346695</v>
+        <v>-3757.841894769332</v>
       </c>
       <c r="P88">
-        <v>-25892.36762242686</v>
+        <v>-26304.89326338532</v>
       </c>
       <c r="Q88">
-        <v>-24747.36762242686</v>
+        <v>-25159.89326338532</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3988663955318315</v>
+        <v>0.4260253490342801</v>
       </c>
       <c r="T88">
-        <v>6.881921211051817</v>
+        <v>7.411299765748112</v>
       </c>
       <c r="U88">
         <v>0.2067366166625341</v>
       </c>
       <c r="V88">
-        <v>0.03377111255989609</v>
+        <v>0.03338293885231108</v>
       </c>
       <c r="W88">
-        <v>0.1997548911109716</v>
+        <v>0.199835140829955</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8547,7 +8547,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.2701689004791687</v>
+        <v>0.2670635108184886</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8555,22 +8555,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2292398678965173</v>
+        <v>0.2308492340631427</v>
       </c>
       <c r="C89">
-        <v>-129145.4938152466</v>
+        <v>-131956.0479246708</v>
       </c>
       <c r="D89">
-        <v>60949.81093013709</v>
+        <v>60419.73273732649</v>
       </c>
       <c r="E89">
-        <v>190391.4130840231</v>
+        <v>192671.8890006368</v>
       </c>
       <c r="F89">
-        <v>198401.4047453837</v>
+        <v>200681.8806619973</v>
       </c>
       <c r="G89">
         <v>8306.1</v>
@@ -8591,37 +8591,37 @@
         <v>10954.1</v>
       </c>
       <c r="M89">
-        <v>41016.83515815465</v>
+        <v>41488.29303353575</v>
       </c>
       <c r="N89">
-        <v>-30062.73515815465</v>
+        <v>-30534.19303353575</v>
       </c>
       <c r="O89">
-        <v>-3757.841894769332</v>
+        <v>-3816.774129191968</v>
       </c>
       <c r="P89">
-        <v>-26304.89326338532</v>
+        <v>-26717.41890434378</v>
       </c>
       <c r="Q89">
-        <v>-25159.89326338532</v>
+        <v>-25572.41890434378</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.4260253490342801</v>
+        <v>0.4577107947871368</v>
       </c>
       <c r="T89">
-        <v>7.411299765748112</v>
+        <v>8.028908079560455</v>
       </c>
       <c r="U89">
         <v>0.2067366166625341</v>
       </c>
       <c r="V89">
-        <v>0.03338293885231108</v>
+        <v>0.0330035872744439</v>
       </c>
       <c r="W89">
-        <v>0.199835140829955</v>
+        <v>0.1999135666916889</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8629,7 +8629,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.2670635108184886</v>
+        <v>0.2640286981955512</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8637,22 +8637,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2308492340631427</v>
+        <v>0.232458600229768</v>
       </c>
       <c r="C90">
-        <v>-131956.0479246708</v>
+        <v>-134757.4613900729</v>
       </c>
       <c r="D90">
-        <v>60419.73273732649</v>
+        <v>59898.79518853794</v>
       </c>
       <c r="E90">
-        <v>192671.8890006368</v>
+        <v>194952.3649172504</v>
       </c>
       <c r="F90">
-        <v>200681.8806619973</v>
+        <v>202962.3565786109</v>
       </c>
       <c r="G90">
         <v>8306.1</v>
@@ -8673,37 +8673,37 @@
         <v>10954.1</v>
       </c>
       <c r="M90">
-        <v>41488.29303353575</v>
+        <v>41959.75090891683</v>
       </c>
       <c r="N90">
-        <v>-30534.19303353575</v>
+        <v>-31005.65090891683</v>
       </c>
       <c r="O90">
-        <v>-3816.774129191968</v>
+        <v>-3875.706363614604</v>
       </c>
       <c r="P90">
-        <v>-26717.41890434378</v>
+        <v>-27129.94454530223</v>
       </c>
       <c r="Q90">
-        <v>-25572.41890434378</v>
+        <v>-25984.94454530223</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.4577107947871368</v>
+        <v>0.4951572306768766</v>
       </c>
       <c r="T90">
-        <v>8.028908079560455</v>
+        <v>8.758808814065951</v>
       </c>
       <c r="U90">
         <v>0.2067366166625341</v>
       </c>
       <c r="V90">
-        <v>0.0330035872744439</v>
+        <v>0.03263276045113554</v>
       </c>
       <c r="W90">
-        <v>0.1999135666916889</v>
+        <v>0.1999902301745074</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8711,7 +8711,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.2640286981955512</v>
+        <v>0.2610620836090843</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8719,22 +8719,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.232458600229768</v>
+        <v>0.2340679663963933</v>
       </c>
       <c r="C91">
-        <v>-134757.4613900729</v>
+        <v>-137549.9686216426</v>
       </c>
       <c r="D91">
-        <v>59898.79518853794</v>
+        <v>59386.76387358187</v>
       </c>
       <c r="E91">
-        <v>194952.3649172504</v>
+        <v>197232.840833864</v>
       </c>
       <c r="F91">
-        <v>202962.3565786109</v>
+        <v>205242.8324952245</v>
       </c>
       <c r="G91">
         <v>8306.1</v>
@@ -8755,37 +8755,37 @@
         <v>10954.1</v>
       </c>
       <c r="M91">
-        <v>41959.75090891683</v>
+        <v>42431.20878429792</v>
       </c>
       <c r="N91">
-        <v>-31005.65090891683</v>
+        <v>-31477.10878429793</v>
       </c>
       <c r="O91">
-        <v>-3875.706363614604</v>
+        <v>-3934.638598037241</v>
       </c>
       <c r="P91">
-        <v>-27129.94454530223</v>
+        <v>-27542.47018626069</v>
       </c>
       <c r="Q91">
-        <v>-25984.94454530223</v>
+        <v>-26397.47018626069</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.4951572306768766</v>
+        <v>0.5400929537445642</v>
       </c>
       <c r="T91">
-        <v>8.758808814065951</v>
+        <v>9.634689695472547</v>
       </c>
       <c r="U91">
         <v>0.2067366166625341</v>
       </c>
       <c r="V91">
-        <v>0.03263276045113554</v>
+        <v>0.0322701742239007</v>
       </c>
       <c r="W91">
-        <v>0.1999902301745074</v>
+        <v>0.2000651900243744</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.2610620836090843</v>
+        <v>0.2581613937912056</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8801,22 +8801,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2340679663963933</v>
+        <v>0.2356773325630187</v>
       </c>
       <c r="C92">
-        <v>-137549.9686216426</v>
+        <v>-140333.7960822947</v>
       </c>
       <c r="D92">
-        <v>59386.76387358187</v>
+        <v>58883.41232954335</v>
       </c>
       <c r="E92">
-        <v>197232.840833864</v>
+        <v>199513.3167504776</v>
       </c>
       <c r="F92">
-        <v>205242.8324952245</v>
+        <v>207523.3084118381</v>
       </c>
       <c r="G92">
         <v>8306.1</v>
@@ -8837,37 +8837,37 @@
         <v>10954.1</v>
       </c>
       <c r="M92">
-        <v>42431.20878429792</v>
+        <v>42902.66665967901</v>
       </c>
       <c r="N92">
-        <v>-31477.10878429793</v>
+        <v>-31948.56665967901</v>
       </c>
       <c r="O92">
-        <v>-3934.638598037241</v>
+        <v>-3993.570832459876</v>
       </c>
       <c r="P92">
-        <v>-27542.47018626069</v>
+        <v>-27954.99582721914</v>
       </c>
       <c r="Q92">
-        <v>-26397.47018626069</v>
+        <v>-26809.99582721914</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.5400929537445642</v>
+        <v>0.5950143930495159</v>
       </c>
       <c r="T92">
-        <v>9.634689695472547</v>
+        <v>10.70521077274728</v>
       </c>
       <c r="U92">
         <v>0.2067366166625341</v>
       </c>
       <c r="V92">
-        <v>0.0322701742239007</v>
+        <v>0.03191555692473696</v>
       </c>
       <c r="W92">
-        <v>0.2000651900243744</v>
+        <v>0.2001385024050135</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.2581613937912056</v>
+        <v>0.2553244553978956</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8883,22 +8883,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2356773325630187</v>
+        <v>0.237286698729644</v>
       </c>
       <c r="C93">
-        <v>-140333.7960822947</v>
+        <v>-143109.1626216373</v>
       </c>
       <c r="D93">
-        <v>58883.41232954335</v>
+        <v>58388.52170681443</v>
       </c>
       <c r="E93">
-        <v>199513.3167504776</v>
+        <v>201793.7926670912</v>
       </c>
       <c r="F93">
-        <v>207523.3084118381</v>
+        <v>209803.7843284517</v>
       </c>
       <c r="G93">
         <v>8306.1</v>
@@ -8919,37 +8919,37 @@
         <v>10954.1</v>
       </c>
       <c r="M93">
-        <v>42902.66665967901</v>
+        <v>43374.12453506009</v>
       </c>
       <c r="N93">
-        <v>-31948.56665967901</v>
+        <v>-32420.0245350601</v>
       </c>
       <c r="O93">
-        <v>-3993.570832459876</v>
+        <v>-4052.503066882512</v>
       </c>
       <c r="P93">
-        <v>-27954.99582721914</v>
+        <v>-28367.52146817758</v>
       </c>
       <c r="Q93">
-        <v>-26809.99582721914</v>
+        <v>-27222.52146817758</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.5950143930495159</v>
+        <v>0.6636661921807055</v>
       </c>
       <c r="T93">
-        <v>10.70521077274728</v>
+        <v>12.04336211934069</v>
       </c>
       <c r="U93">
         <v>0.2067366166625341</v>
       </c>
       <c r="V93">
-        <v>0.03191555692473696</v>
+        <v>0.03156864869729416</v>
       </c>
       <c r="W93">
-        <v>0.2001385024050135</v>
+        <v>0.2002102210382474</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8957,7 +8957,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.2553244553978956</v>
+        <v>0.2525491895783534</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8965,22 +8965,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.237286698729644</v>
+        <v>0.2388960648962694</v>
       </c>
       <c r="C94">
-        <v>-143109.1626216373</v>
+        <v>-145876.2797932381</v>
       </c>
       <c r="D94">
-        <v>58388.52170681443</v>
+        <v>57901.88045182721</v>
       </c>
       <c r="E94">
-        <v>201793.7926670912</v>
+        <v>204074.2685837048</v>
       </c>
       <c r="F94">
-        <v>209803.7843284517</v>
+        <v>212084.2602450653</v>
       </c>
       <c r="G94">
         <v>8306.1</v>
@@ -9001,37 +9001,37 @@
         <v>10954.1</v>
       </c>
       <c r="M94">
-        <v>43374.12453506009</v>
+        <v>43845.58241044118</v>
       </c>
       <c r="N94">
-        <v>-32420.0245350601</v>
+        <v>-32891.48241044118</v>
       </c>
       <c r="O94">
-        <v>-4052.503066882512</v>
+        <v>-4111.435301305148</v>
       </c>
       <c r="P94">
-        <v>-28367.52146817758</v>
+        <v>-28780.04710913603</v>
       </c>
       <c r="Q94">
-        <v>-27222.52146817758</v>
+        <v>-27635.04710913603</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.6636661921807055</v>
+        <v>0.7519327910636635</v>
       </c>
       <c r="T94">
-        <v>12.04336211934069</v>
+        <v>13.76384242210364</v>
       </c>
       <c r="U94">
         <v>0.2067366166625341</v>
       </c>
       <c r="V94">
-        <v>0.03156864869729416</v>
+        <v>0.03122920086183939</v>
       </c>
       <c r="W94">
-        <v>0.2002102210382474</v>
+        <v>0.2002803973352827</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.2525491895783534</v>
+        <v>0.2498336068947151</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9047,22 +9047,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2388960648962694</v>
+        <v>0.2405054310628947</v>
       </c>
       <c r="C95">
-        <v>-145876.2797932381</v>
+        <v>-148635.3521561576</v>
       </c>
       <c r="D95">
-        <v>57901.88045182721</v>
+        <v>57423.28400552132</v>
       </c>
       <c r="E95">
-        <v>204074.2685837048</v>
+        <v>206354.7445003184</v>
       </c>
       <c r="F95">
-        <v>212084.2602450653</v>
+        <v>214364.7361616789</v>
       </c>
       <c r="G95">
         <v>8306.1</v>
@@ -9083,37 +9083,37 @@
         <v>10954.1</v>
       </c>
       <c r="M95">
-        <v>43845.58241044118</v>
+        <v>44317.04028582227</v>
       </c>
       <c r="N95">
-        <v>-32891.48241044118</v>
+        <v>-33362.94028582227</v>
       </c>
       <c r="O95">
-        <v>-4111.435301305148</v>
+        <v>-4170.367535727784</v>
       </c>
       <c r="P95">
-        <v>-28780.04710913603</v>
+        <v>-29192.57275009449</v>
       </c>
       <c r="Q95">
-        <v>-27635.04710913603</v>
+        <v>-28047.57275009449</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.7519327910636635</v>
+        <v>0.8696215895742744</v>
       </c>
       <c r="T95">
-        <v>13.76384242210364</v>
+        <v>16.05781615912093</v>
       </c>
       <c r="U95">
         <v>0.2067366166625341</v>
       </c>
       <c r="V95">
-        <v>0.03122920086183939</v>
+        <v>0.03089697532075599</v>
       </c>
       <c r="W95">
-        <v>0.2002803973352827</v>
+        <v>0.2003490805196152</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9121,7 +9121,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.2498336068947151</v>
+        <v>0.2471758025660479</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9129,22 +9129,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2405054310628947</v>
+        <v>0.24211479722952</v>
       </c>
       <c r="C96">
-        <v>-148635.3521561576</v>
+        <v>-151386.5775616493</v>
       </c>
       <c r="D96">
-        <v>57423.28400552132</v>
+        <v>56952.53451664321</v>
       </c>
       <c r="E96">
-        <v>206354.7445003184</v>
+        <v>208635.220416932</v>
       </c>
       <c r="F96">
-        <v>214364.7361616789</v>
+        <v>216645.2120782925</v>
       </c>
       <c r="G96">
         <v>8306.1</v>
@@ -9165,37 +9165,37 @@
         <v>10954.1</v>
       </c>
       <c r="M96">
-        <v>44317.04028582227</v>
+        <v>44788.49816120336</v>
       </c>
       <c r="N96">
-        <v>-33362.94028582227</v>
+        <v>-33834.39816120336</v>
       </c>
       <c r="O96">
-        <v>-4170.367535727784</v>
+        <v>-4229.29977015042</v>
       </c>
       <c r="P96">
-        <v>-29192.57275009449</v>
+        <v>-29605.09839105294</v>
       </c>
       <c r="Q96">
-        <v>-28047.57275009449</v>
+        <v>-28460.09839105294</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.8696215895742744</v>
+        <v>1.03438590748913</v>
       </c>
       <c r="T96">
-        <v>16.05781615912093</v>
+        <v>19.26937939094512</v>
       </c>
       <c r="U96">
         <v>0.2067366166625341</v>
       </c>
       <c r="V96">
-        <v>0.03089697532075599</v>
+        <v>0.03057174400159014</v>
       </c>
       <c r="W96">
-        <v>0.2003490805196152</v>
+        <v>0.2004163177421722</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.2471758025660479</v>
+        <v>0.2445739520127211</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9211,22 +9211,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.24211479722952</v>
+        <v>0.2437241633961454</v>
       </c>
       <c r="C97">
-        <v>-151386.5775616493</v>
+        <v>-154130.1474258735</v>
       </c>
       <c r="D97">
-        <v>56952.53451664321</v>
+        <v>56489.4405690326</v>
       </c>
       <c r="E97">
-        <v>208635.220416932</v>
+        <v>210915.6963335456</v>
       </c>
       <c r="F97">
-        <v>216645.2120782925</v>
+        <v>218925.6879949061</v>
       </c>
       <c r="G97">
         <v>8306.1</v>
@@ -9247,37 +9247,37 @@
         <v>10954.1</v>
       </c>
       <c r="M97">
-        <v>44788.49816120336</v>
+        <v>45259.95603658445</v>
       </c>
       <c r="N97">
-        <v>-33834.39816120336</v>
+        <v>-34305.85603658445</v>
       </c>
       <c r="O97">
-        <v>-4229.29977015042</v>
+        <v>-4288.232004573057</v>
       </c>
       <c r="P97">
-        <v>-29605.09839105294</v>
+        <v>-30017.6240320114</v>
       </c>
       <c r="Q97">
-        <v>-28460.09839105294</v>
+        <v>-28872.6240320114</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.03438590748913</v>
+        <v>1.281532384361413</v>
       </c>
       <c r="T97">
-        <v>19.26937939094512</v>
+        <v>24.08672423868141</v>
       </c>
       <c r="U97">
         <v>0.2067366166625341</v>
       </c>
       <c r="V97">
-        <v>0.03057174400159014</v>
+        <v>0.03025328833490691</v>
       </c>
       <c r="W97">
-        <v>0.2004163177421722</v>
+        <v>0.2004821541892593</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9285,7 +9285,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.2445739520127211</v>
+        <v>0.2420263066792553</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9293,22 +9293,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2437241633961454</v>
+        <v>0.2453335295627707</v>
       </c>
       <c r="C98">
-        <v>-154130.1474258735</v>
+        <v>-156866.246989413</v>
       </c>
       <c r="D98">
-        <v>56489.44056903262</v>
+        <v>56033.81692210667</v>
       </c>
       <c r="E98">
-        <v>210915.6963335456</v>
+        <v>213196.1722501592</v>
       </c>
       <c r="F98">
-        <v>218925.6879949061</v>
+        <v>221206.1639115197</v>
       </c>
       <c r="G98">
         <v>8306.1</v>
@@ -9329,37 +9329,37 @@
         <v>10954.1</v>
       </c>
       <c r="M98">
-        <v>45259.95603658444</v>
+        <v>45731.41391196553</v>
       </c>
       <c r="N98">
-        <v>-34305.85603658445</v>
+        <v>-34777.31391196553</v>
       </c>
       <c r="O98">
-        <v>-4288.232004573056</v>
+        <v>-4347.164238995691</v>
       </c>
       <c r="P98">
-        <v>-30017.62403201139</v>
+        <v>-30430.14967296984</v>
       </c>
       <c r="Q98">
-        <v>-28872.62403201139</v>
+        <v>-29285.14967296984</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.281532384361409</v>
+        <v>1.693443179148546</v>
       </c>
       <c r="T98">
-        <v>24.08672423868135</v>
+        <v>32.11563231824179</v>
       </c>
       <c r="U98">
         <v>0.2067366166625341</v>
       </c>
       <c r="V98">
-        <v>0.03025328833490691</v>
+        <v>0.02994139876444395</v>
       </c>
       <c r="W98">
-        <v>0.2004821541892593</v>
+        <v>0.2005466331838292</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.2420263066792553</v>
+        <v>0.2395311901155517</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9375,22 +9375,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2453335295627707</v>
+        <v>0.246942895729396</v>
       </c>
       <c r="C99">
-        <v>-156866.246989413</v>
+        <v>-159595.0555643306</v>
       </c>
       <c r="D99">
-        <v>56033.81692210667</v>
+        <v>55585.4842638027</v>
       </c>
       <c r="E99">
-        <v>213196.1722501592</v>
+        <v>215476.6481667728</v>
       </c>
       <c r="F99">
-        <v>221206.1639115197</v>
+        <v>223486.6398281333</v>
       </c>
       <c r="G99">
         <v>8306.1</v>
@@ -9411,37 +9411,37 @@
         <v>10954.1</v>
       </c>
       <c r="M99">
-        <v>45731.41391196553</v>
+        <v>46202.87178734662</v>
       </c>
       <c r="N99">
-        <v>-34777.31391196553</v>
+        <v>-35248.77178734662</v>
       </c>
       <c r="O99">
-        <v>-4347.164238995691</v>
+        <v>-4406.096473418328</v>
       </c>
       <c r="P99">
-        <v>-30430.14967296984</v>
+        <v>-30842.6753139283</v>
       </c>
       <c r="Q99">
-        <v>-29285.14967296984</v>
+        <v>-29697.6753139283</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.693443179148546</v>
+        <v>2.517264768722819</v>
       </c>
       <c r="T99">
-        <v>32.11563231824179</v>
+        <v>48.17344847736269</v>
       </c>
       <c r="U99">
         <v>0.2067366166625341</v>
       </c>
       <c r="V99">
-        <v>0.02994139876444395</v>
+        <v>0.02963587428725575</v>
       </c>
       <c r="W99">
-        <v>0.2005466331838292</v>
+        <v>0.2006097962805506</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.2395311901155517</v>
+        <v>0.237086994298046</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9457,22 +9457,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.246942895729396</v>
+        <v>0.2485522618960214</v>
       </c>
       <c r="C100">
-        <v>-159595.0555643306</v>
+        <v>-162316.7467694598</v>
       </c>
       <c r="D100">
-        <v>55585.4842638027</v>
+        <v>55144.26897528708</v>
       </c>
       <c r="E100">
-        <v>215476.6481667728</v>
+        <v>217757.1240833864</v>
       </c>
       <c r="F100">
-        <v>223486.6398281333</v>
+        <v>225767.1157447469</v>
       </c>
       <c r="G100">
         <v>8306.1</v>
@@ -9493,37 +9493,37 @@
         <v>10954.1</v>
       </c>
       <c r="M100">
-        <v>46202.87178734662</v>
+        <v>46674.32966272771</v>
       </c>
       <c r="N100">
-        <v>-35248.77178734662</v>
+        <v>-35720.22966272771</v>
       </c>
       <c r="O100">
-        <v>-4406.096473418328</v>
+        <v>-4465.028707840964</v>
       </c>
       <c r="P100">
-        <v>-30842.6753139283</v>
+        <v>-31255.20095488675</v>
       </c>
       <c r="Q100">
-        <v>-29697.6753139283</v>
+        <v>-30110.20095488675</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.517264768722819</v>
+        <v>4.988729537445638</v>
       </c>
       <c r="T100">
-        <v>48.17344847736269</v>
+        <v>96.34689695472538</v>
       </c>
       <c r="U100">
         <v>0.2067366166625341</v>
       </c>
       <c r="V100">
-        <v>0.02963587428725575</v>
+        <v>0.02933652202172791</v>
       </c>
       <c r="W100">
-        <v>0.2006097962805506</v>
+        <v>0.2006716833551161</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9531,91 +9531,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.237086994298046</v>
+        <v>0.2346921761738233</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2485522618960214</v>
-      </c>
-      <c r="C101">
-        <v>-162316.7467694598</v>
-      </c>
-      <c r="D101">
-        <v>55144.26897528708</v>
-      </c>
-      <c r="E101">
-        <v>217757.1240833864</v>
-      </c>
-      <c r="F101">
-        <v>225767.1157447469</v>
-      </c>
-      <c r="G101">
-        <v>8306.1</v>
-      </c>
-      <c r="H101">
-        <v>220037.6</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>12099.1</v>
-      </c>
-      <c r="K101">
-        <v>1145</v>
-      </c>
-      <c r="L101">
-        <v>10954.1</v>
-      </c>
-      <c r="M101">
-        <v>46674.32966272771</v>
-      </c>
-      <c r="N101">
-        <v>-35720.22966272771</v>
-      </c>
-      <c r="O101">
-        <v>-4465.028707840964</v>
-      </c>
-      <c r="P101">
-        <v>-31255.20095488675</v>
-      </c>
-      <c r="Q101">
-        <v>-30110.20095488675</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>4.988729537445638</v>
-      </c>
-      <c r="T101">
-        <v>96.34689695472538</v>
-      </c>
-      <c r="U101">
-        <v>0.2067366166625341</v>
-      </c>
-      <c r="V101">
-        <v>0.02933652202172791</v>
-      </c>
-      <c r="W101">
-        <v>0.2006716833551161</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>C2/C</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.2346921761738233</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
